--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="75">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -49,202 +49,196 @@
     <t>Skip Logic</t>
   </si>
   <si>
-    <t>Answer Q6 if Q4 is Ontario</t>
-  </si>
-  <si>
-    <t>Q4, Q6</t>
+    <t>ASK d2 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d2</t>
+  </si>
+  <si>
+    <t>2.3799999999999955</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>183, 590, 615, 653</t>
+    <t>19</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>ASK d5 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d5</t>
+  </si>
+  <si>
+    <t>ASK d9 IF C2=1,2,5,6,7,8,10,9,3, OR 97]</t>
+  </si>
+  <si>
+    <t>c2, d9</t>
+  </si>
+  <si>
+    <t>ASK d10 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d10</t>
+  </si>
+  <si>
+    <t>ASK d10a IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d10a</t>
+  </si>
+  <si>
+    <t>ASK d11 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d11</t>
+  </si>
+  <si>
+    <t>ASK d13 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d13</t>
+  </si>
+  <si>
+    <t>Dynamic Piping Single-to-Single</t>
+  </si>
+  <si>
+    <t>Dynamic answer choices</t>
+  </si>
+  <si>
+    <t>ci1_r6, k1_new</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>Mandatory Logic</t>
   </si>
   <si>
-    <t>Block Q49 if Q48r97 selected</t>
-  </si>
-  <si>
-    <t>Q48r97, Q49</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Exclusive</t>
-  </si>
-  <si>
-    <t>Selecting one answer prevents the selection of any other options.</t>
-  </si>
-  <si>
-    <t>Q30r1, Q30r2, Q30r3, Q30r4, Q30r5, Q30r6, Q30r7, Q30r8, Q30r9, Q30r10, Q30r11, Q30r12, Q30r13, Q30r14, Q30r15, Q30r16, noanswerQ30_r99, noanswerQ30_r97</t>
+    <t>ASK H3 IF H1=7, 8, OR 97</t>
+  </si>
+  <si>
+    <t>h1, h3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>ASK CI10  IF B3=2</t>
+  </si>
+  <si>
+    <t>b3, ci10, ci10_codes9999999</t>
+  </si>
+  <si>
+    <t>7.140000000000001</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1, 29, 33</t>
+  </si>
+  <si>
+    <t>ASK d8 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d8_a, d8_b, d8_c, d8_d, d8_e, d8_f, d8_g, d8_h, d8_i, d8_j</t>
+  </si>
+  <si>
+    <t>ASK d13c IF D13=3 or IF D13=2]</t>
+  </si>
+  <si>
+    <t>d13, d13c_r1, d13c_r2, d13c_r3, d13c_r4, d13c_r5, d13c_r6, d13c_r97, d13c_r99</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
+    <t>ASK d14 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
+  </si>
+  <si>
+    <t>c2, d14_h, d14_a, d14_b, d14_c, d14_f, d14_i, d14_g</t>
+  </si>
+  <si>
+    <t>SHOW h7 IF B3=2</t>
+  </si>
+  <si>
+    <t>b3, h7_final, h7_final_codes99</t>
+  </si>
+  <si>
+    <t>4.760000000000005</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>29, 33</t>
+  </si>
+  <si>
+    <t>ASK l36b IF B3=2</t>
+  </si>
+  <si>
+    <t>b3, l36b_final, l36b_final_codes996, l36b_final_codes99</t>
+  </si>
+  <si>
+    <t>ASK l24 IF B3=1</t>
+  </si>
+  <si>
+    <t>b3, l24d_final, l24d_final_codes99</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>ASK K8 IF K7=2 OR 4</t>
+  </si>
+  <si>
+    <t>k7, k8_r1, k8_r2, k8_r3, k8_r4, k8_r5, k8_r6, k8_r97</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>ASK J8 IF J3=ONLY 1 OR 0</t>
+  </si>
+  <si>
+    <t>j7_final, j8_r2, j8_r10, j8_r1, j8_r7, j8_r9, j8_r3, j8_r5, j8_r6, j8_r12, j8_r8, j8_r11, j8_r97</t>
+  </si>
+  <si>
     <t>41</t>
   </si>
   <si>
-    <t>21, 99, 100, 127, 147, 163, 190, 209, 316, 319, 351, 400, 410, 452, 516, 517, 585, 591, 606, 610, 622, 627, 631, 644, 687, 689, 705, 744, 770, 798, 802, 814, 827, 831, 840, 845, 846, 858, 876, 883, 986</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Q53r1, Q53r2, Q53r3, Q53r4, Q53r5, Q53r6, Q53r7, Q53r8, Q53r9, Q53r10, Q53r11, Q53r12, Q53r13, Q53r96, Q53r98, Q53r97</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>757, 909</t>
-  </si>
-  <si>
-    <t>Q53r1, Q53r2, Q53r3, Q53r4, Q53r5, Q53r6, Q53r7, Q53r8, Q53r9, Q53r10, Q53r11, Q53r12, Q53r13, Q53r96, Q53r97, Q53r98</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44, 57, 72, 81, 84, 93, 99, 152, 155, 290, 351, 393, 396, 397, 400, 401, 431, 432, 452, 467, 489, 524, 565, 631, 646, 656, 670, 689, 691, 701, 727, 744, 766, 770, 807, 810, 824, 876, 901, 908, 940, 946, 996</t>
-  </si>
-  <si>
-    <t>Q67r1, Q67r2, Q67r3, Q67r4, Q67r5, Q67r6, Q67r7, Q67r8, Q67r96, Q67r98</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>132, 810, 946</t>
-  </si>
-  <si>
     <t>Recodes/Hidden Variables</t>
   </si>
   <si>
-    <t>Recoding from birthdate to age - many values for the same recode issue</t>
-  </si>
-  <si>
-    <t>Q2, AGENUM</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
-    <t>0, 8, 9, 11, 13, 16, 17, 19, 21, 22, 23, 30, 31, 35, 37, 39, 40, 41, 43, 44, 45, 46, 49, 55, 56, 57, 58, 59, 60, 63, 64, 66, 72, 74, 75, 80, 81, 82, 83, 84, 85, 88, 89, 91, 93, 94, 97, 99, 102, 108, 109, 110, 112, 115, 119, 123, 127, 128, 129, 130, 131, 132, 136, 147, 150, 151, 152, 153, 154, 155, 156, 157, 160, 161, 163, 165, 169, 172, 174, 176, 177, 178, 180, 183, 184, 189, 190, 191, 195, 197, 202, 204, 205, 209, 212, 215, 217, 218, 220, 221, 225, 228, 230, 231, 233, 234, 235, 238, 240, 241, 242, 245, 249, 250, 255, 259, 262, 263, 266, 268, 271, 272, 275, 277, 278, 280, 284, 285, 288, 290, 291, 295, 298, 299, 302, 304, 310, 313, 314, 316, 318, 319, 320, 324, 325, 326, 327, 329, 330, 333, 336, 339, 340, 342, 343, 345, 346, 347, 350, 351, 353, 355, 357, 358, 360, 364, 367, 369, 372, 373, 376, 379, 384, 386, 388, 392, 393, 394, 395, 396, 397, 398, 400, 401, 404, 406, 409, 410, 413, 414, 416, 417, 421, 424, 425, 426, 427, 428, 429, 431, 432, 433, 437, 438, 440, 442, 443, 444, 446, 450, 452, 454, 455, 460, 466, 467, 469, 473, 480, 482, 484, 486, 487, 488, 489, 490, 492, 494, 495, 496, 497, 498, 499, 501, 502, 503, 505, 509, 513, 514, 516, 517, 518, 521, 522, 523, 524, 525, 526, 527, 532, 534, 537, 538, 539, 541, 544, 545, 546, 547, 549, 550, 553, 555, 556, 558, 560, 564, 565, 572, 575, 578, 579, 584, 585, 589, 590, 591, 592, 595, 596, 599, 602, 604, 606, 608, 610, 614, 615, 619, 624, 626, 627, 628, 629, 630, 631, 633, 634, 635, 636, 644, 646, 647, 652, 653, 655, 656, 658, 660, 667, 669, 670, 673, 675, 678, 680, 681, 683, 685, 687, 688, 689, 691, 693, 696, 700, 701, 702, 705, 707, 708, 709, 710, 712, 714, 721, 725, 727, 728, 730, 733, 734, 735, 737, 741, 743, 744, 748, 749, 750, 751, 752, 753, 754, 755, 756, 757, 759, 765, 766, 769, 770, 773, 775, 779, 780, 782, 783, 784, 785, 786, 787, 790, 794, 797, 798, 801, 802, 803, 807, 808, 809, 810, 812, 814, 818, 819, 823, 824, 826, 827, 828, 831, 834, 835, 836, 840, 842, 843, 846, 848, 852, 855, 858, 865, 867, 869, 871, 874, 876, 881, 882, 883, 884, 885, 887, 889, 891, 894, 896, 898, 899, 901, 902, 905, 908, 909, 914, 916, 923, 927, 928, 931, 932, 935, 936, 940, 946, 949, 950, 952, 954, 956, 959, 961, 963, 964, 965, 966, 967, 972, 974, 975, 977, 978, 980, 982, 986, 988, 990, 992, 995, 996, 997, 998, 999</t>
-  </si>
-  <si>
-    <t>Recoding Age to age groups - many values for the same code issue (value 9999.0 causing the issue)</t>
-  </si>
-  <si>
-    <t>AGENUM, Q3</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>335</t>
-  </si>
-  <si>
-    <t>0, 8, 9, 11, 13, 16, 17, 21, 22, 23, 30, 31, 37, 44, 45, 49, 56, 59, 63, 64, 66, 72, 74, 75, 80, 81, 83, 88, 89, 93, 99, 102, 109, 110, 115, 119, 129, 130, 132, 147, 150, 151, 152, 153, 154, 155, 156, 157, 159, 160, 163, 165, 169, 174, 176, 177, 178, 180, 184, 189, 191, 209, 215, 217, 220, 225, 228, 230, 231, 233, 234, 235, 240, 241, 242, 245, 249, 250, 255, 259, 262, 263, 266, 268, 271, 272, 275, 277, 278, 280, 285, 288, 290, 291, 298, 299, 302, 304, 310, 313, 314, 316, 318, 320, 324, 325, 326, 327, 329, 333, 336, 337, 342, 343, 345, 346, 347, 350, 351, 355, 357, 360, 364, 367, 372, 376, 379, 384, 388, 392, 393, 396, 398, 400, 404, 406, 409, 413, 414, 416, 421, 424, 425, 426, 427, 428, 429, 432, 437, 438, 443, 444, 452, 454, 455, 460, 467, 469, 473, 480, 482, 486, 487, 488, 489, 490, 492, 494, 495, 496, 498, 501, 502, 503, 505, 513, 514, 517, 518, 523, 524, 525, 527, 534, 537, 539, 541, 544, 545, 546, 547, 550, 553, 555, 556, 564, 565, 572, 575, 584, 585, 592, 599, 602, 606, 610, 614, 615, 619, 626, 629, 631, 633, 634, 635, 636, 644, 646, 647, 652, 653, 655, 656, 658, 667, 669, 670, 673, 675, 680, 681, 683, 688, 689, 691, 693, 700, 701, 702, 705, 707, 708, 709, 710, 712, 721, 727, 730, 733, 734, 735, 737, 741, 744, 748, 749, 750, 753, 754, 755, 756, 759, 765, 766, 769, 770, 773, 775, 779, 780, 782, 783, 784, 785, 787, 790, 794, 798, 803, 808, 809, 810, 812, 818, 819, 824, 827, 828, 831, 834, 835, 836, 843, 848, 855, 869, 874, 876, 882, 883, 884, 887, 889, 894, 898, 899, 901, 908, 909, 914, 923, 931, 935, 936, 946, 949, 950, 952, 954, 956, 959, 961, 964, 967, 972, 974, 975, 978, 980, 986, 988, 990, 992, 995, 996</t>
-  </si>
-  <si>
-    <t>Grouping age groups and gender - issue cause by previous ones</t>
-  </si>
-  <si>
-    <t>GenreAge, Q3, Q1</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>6, 8, 9, 11, 13, 16, 19, 21, 22, 30, 35, 41, 43, 45, 46, 55, 56, 58, 63, 64, 72, 74, 80, 81, 82, 83, 85, 89, 91, 99, 100, 109, 110, 115, 123, 127, 130, 131, 132, 147, 151, 152, 154, 155, 157, 159, 160, 163, 169, 176, 177, 178, 180, 189, 197, 209, 212, 215, 217, 225, 231, 233, 234, 235, 241, 242, 245, 249, 250, 259, 262, 263, 266, 268, 271, 272, 275, 277, 280, 288, 304, 310, 314, 318, 320, 324, 325, 326, 327, 333, 336, 337, 346, 347, 357, 372, 376, 379, 384, 386, 388, 392, 393, 400, 410, 413, 415, 416, 421, 428, 432, 433, 437, 443, 444, 450, 454, 467, 469, 473, 482, 486, 487, 488, 489, 494, 495, 496, 498, 501, 503, 505, 506, 516, 517, 521, 522, 523, 524, 525, 526, 527, 532, 538, 539, 541, 545, 546, 547, 550, 555, 556, 560, 564, 565, 575, 578, 584, 585, 590, 599, 602, 606, 608, 615, 624, 629, 630, 633, 644, 646, 653, 656, 667, 670, 673, 675, 687, 688, 689, 693, 696, 701, 702, 707, 708, 709, 727, 730, 733, 734, 736, 737, 753, 756, 759, 765, 766, 773, 784, 785, 790, 794, 797, 801, 803, 819, 827, 828, 831, 834, 835, 838, 843, 845, 846, 869, 881, 882, 883, 887, 889, 894, 898, 908, 909, 914, 936, 952, 959, 964, 972, 974, 978, 986, 988, 992, 996</t>
-  </si>
-  <si>
-    <t>Recode ethnicity  into groups</t>
-  </si>
-  <si>
-    <t>Q14, Q13r1, Q13r2, Q13r3, Q13r4, Q13r5, Q13r6, Q13r7, Q13r8, Q13r96, Q13r99</t>
+    <t>AUTOPUNCH A3 BASED ON ZIP ENTERED AT P11. SEE ZIP CODE FILE</t>
+  </si>
+  <si>
+    <t>p11, a3</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41</t>
+  </si>
+  <si>
+    <t>Grouping continuous to categories</t>
+  </si>
+  <si>
+    <t>c21, c21rec3buckets</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>30, 37, 40, 95, 136, 172, 174, 209, 274, 343, 350, 400, 414, 484, 522, 534, 545, 683, 687, 956, 986</t>
-  </si>
-  <si>
-    <t>Recode Yes if Q13r1, r2, r4, r5, r6, r7, or r9 selected - seems like it is not a real recoding</t>
-  </si>
-  <si>
-    <t>Q16, Q13r1, Q13r2, Q13r3, Q13r4, Q13r5, Q13r6, Q13r7, Q13r8, Q13r96, Q13r99</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>30, 37, 40, 95, 127, 132, 136, 172, 174, 177, 209, 233, 274, 330, 343, 350, 373, 400, 414, 484, 522, 534, 545, 683, 687, 956, 986</t>
-  </si>
-  <si>
-    <t>Selection Limit Control</t>
-  </si>
-  <si>
-    <t>Minimum and/or maximum limits on the number of choices a respondent can select.</t>
-  </si>
-  <si>
-    <t>Q30r1, Q30r2, Q30r3, Q30r4, Q30r5, Q30r6, Q30r7, Q30r8, Q30r9, Q30r10, Q30r11, Q30r12, Q30r13, Q30r14, Q30r15, Q30r16</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>2, 6, 10, 18, 27, 40, 44, 52, 54, 62, 65, 67, 77, 79, 84, 86, 89, 93, 94, 96, 103, 104, 106, 110, 113, 116, 118, 123, 125, 135, 143, 145, 150, 159, 164, 170, 193, 207, 213, 219, 223, 226, 239, 243, 265, 269, 283, 285, 286, 288, 292, 293, 301, 305, 306, 311, 313, 322, 326, 328, 332, 337, 346, 356, 358, 361, 362, 363, 364, 370, 374, 375, 390, 396, 397, 399, 402, 405, 418, 420, 423, 431, 432, 451, 453, 456, 458, 461, 464, 470, 474, 483, 489, 493, 503, 504, 510, 511, 514, 536, 540, 548, 552, 562, 565, 566, 567, 573, 581, 582, 583, 594, 597, 605, 609, 613, 616, 618, 621, 623, 633, 637, 641, 643, 652, 656, 663, 664, 665, 670, 677, 686, 694, 695, 699, 701, 702, 703, 706, 711, 713, 716, 717, 720, 722, 723, 724, 734, 740, 741, 742, 747, 758, 760, 761, 762, 764, 774, 778, 782, 797, 799, 817, 829, 833, 839, 847, 851, 854, 861, 870, 872, 878, 889, 890, 892, 897, 900, 901, 908, 911, 912, 919, 924, 945, 947, 948, 962, 965, 969, 970, 983, 985, 989, 991, 996</t>
-  </si>
-  <si>
-    <t>Ask Q77 group if Q75 is in [”Quickly shifting towards using less cash”, “Slowing shifting towards using less cash” ] AND Q76 in [”Very good thing, “A good thing”]</t>
-  </si>
-  <si>
-    <t>Q77r1, Q77r2, Q77r3, Q77r4, Q77r5, Q77r6, Q77r7, Q77r8, Q77r96, Q77r98</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>13, 18, 19, 21, 73, 84, 93, 99, 155, 159, 174, 215, 329, 337, 353, 394, 397, 413, 424, 442, 499, 502, 539, 541, 546, 556, 606, 680, 689, 691, 748, 751, 757, 766, 801, 802, 812, 814, 824, 848, 884, 885, 898, 964</t>
-  </si>
-  <si>
-    <t>Ask Q78 group if Q75 is in [”Quickly shifting towards using less cash”, “Slowing shifting towards using less cash” ] AND Q76  NOT in [A bad thing', 'A very bad thing’]</t>
-  </si>
-  <si>
-    <t>Q78r1, Q78r2, Q78r3, Q78r4, Q78r5, Q78r6, Q78r7, Q78r8, Q78r9, Q78r10, Q78r96, Q78r98</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>50, 63, 72, 80, 91, 129, 131, 165, 184, 209, 228, 235, 266, 274, 301, 319, 353, 360, 391, 398, 400, 406, 429, 440, 442, 454, 495, 498, 517, 524, 525, 527, 538, 585, 596, 630, 644, 693, 730, 749, 769, 780, 785, 827, 858, 865, 871, 894, 899, 914, 978, 982, 986</t>
-  </si>
-  <si>
-    <t>Number of rows affected: 636</t>
+    <t>Number of rows affected: 42</t>
   </si>
 </sst>
 </file>
@@ -643,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -701,7 +695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20" customHeight="1">
+    <row r="9" spans="2:8" ht="30" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
@@ -724,308 +718,446 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20" customHeight="1">
+    <row r="10" spans="2:8" ht="30" customHeight="1">
       <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="30" customHeight="1">
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" ht="90" customHeight="1">
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="30" customHeight="1">
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="30" customHeight="1">
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="E13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="30" customHeight="1">
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="30" customHeight="1">
+      <c r="B15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="60" customHeight="1">
-      <c r="B12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="30" customHeight="1">
+      <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="60" customHeight="1">
-      <c r="B13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="20" customHeight="1">
+      <c r="B17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="45" customHeight="1">
-      <c r="B14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="E17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="45" customHeight="1">
-      <c r="B15" s="4" t="s">
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="20" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="45" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="60" customHeight="1">
-      <c r="B16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="45" customHeight="1">
+      <c r="B20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="E20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="45" customHeight="1">
-      <c r="B17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="45" customHeight="1">
-      <c r="B18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="60" customHeight="1">
-      <c r="B19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="60" customHeight="1">
-      <c r="B20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="90" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="30" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="20" customHeight="1">
+      <c r="B22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="30" customHeight="1">
+      <c r="B23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="30" customHeight="1">
+      <c r="B24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="30" customHeight="1">
+      <c r="B25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="60" customHeight="1">
+      <c r="B26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="30" customHeight="1">
+      <c r="B27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="90" customHeight="1">
-      <c r="B22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="30" customHeight="1">
+      <c r="B28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="H28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="F30" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="F24" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="140">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -46,199 +46,394 @@
     <t>Supported</t>
   </si>
   <si>
+    <t>Mandatory Logic</t>
+  </si>
+  <si>
+    <t>ask if Q8_1_6</t>
+  </si>
+  <si>
+    <t>Q8_1_6, Q9_1_6_115, Q9_1_6_116, Q9_1_6_117, Q9_1_6_118, Q9_1_6_119, Q9_1_6_695, Q9_1_6_98</t>
+  </si>
+  <si>
+    <t>1.3900000000000006</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>ask if Q8_1_9</t>
+  </si>
+  <si>
+    <t>Q8_1_9, Q9_1_9_119, Q9_1_9_120, Q9_1_9_121, Q9_1_9_1095, Q9_1_9_1096, Q9_1_9_99</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>Skip Logic</t>
   </si>
   <si>
-    <t>ASK d2 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d2</t>
-  </si>
-  <si>
-    <t>2.3799999999999955</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>ASK d5 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d5</t>
-  </si>
-  <si>
-    <t>ASK d9 IF C2=1,2,5,6,7,8,10,9,3, OR 97]</t>
-  </si>
-  <si>
-    <t>c2, d9</t>
-  </si>
-  <si>
-    <t>ASK d10 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d10</t>
-  </si>
-  <si>
-    <t>ASK d10a IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d10a</t>
-  </si>
-  <si>
-    <t>ASK d11 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d11</t>
-  </si>
-  <si>
-    <t>ASK d13 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d13</t>
-  </si>
-  <si>
-    <t>Dynamic Piping Single-to-Single</t>
-  </si>
-  <si>
-    <t>Dynamic answer choices</t>
-  </si>
-  <si>
-    <t>ci1_r6, k1_new</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Mandatory Logic</t>
-  </si>
-  <si>
-    <t>ASK H3 IF H1=7, 8, OR 97</t>
-  </si>
-  <si>
-    <t>h1, h3</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>ASK CI10  IF B3=2</t>
-  </si>
-  <si>
-    <t>b3, ci10, ci10_codes9999999</t>
-  </si>
-  <si>
-    <t>7.140000000000001</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1, 29, 33</t>
-  </si>
-  <si>
-    <t>ASK d8 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d8_a, d8_b, d8_c, d8_d, d8_e, d8_f, d8_g, d8_h, d8_i, d8_j</t>
-  </si>
-  <si>
-    <t>ASK d13c IF D13=3 or IF D13=2]</t>
-  </si>
-  <si>
-    <t>d13, d13c_r1, d13c_r2, d13c_r3, d13c_r4, d13c_r5, d13c_r6, d13c_r97, d13c_r99</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>ASK d14 IF C2=1,2,5,6,7,8,10,9,3, OR 97</t>
-  </si>
-  <si>
-    <t>c2, d14_h, d14_a, d14_b, d14_c, d14_f, d14_i, d14_g</t>
-  </si>
-  <si>
-    <t>SHOW h7 IF B3=2</t>
-  </si>
-  <si>
-    <t>b3, h7_final, h7_final_codes99</t>
-  </si>
-  <si>
-    <t>4.760000000000005</t>
+    <t>ask if Q8_1_16</t>
+  </si>
+  <si>
+    <t>Q8_1_16, Q9_1_16_133, Q9_1_16_18, Q9_1_16_8, Q9_1_16_1695, Q9_1_16_1696, Q9_1_16_99</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>ask if Q8_1_18</t>
+  </si>
+  <si>
+    <t>Q8_1_18, Q9_1_18_134, Q9_1_18_135, Q9_1_18_136, Q9_1_18_137, Q9_1_18_138, Q9_1_18_139, Q9_1_18_140, Q9_1_18_141, Q9_1_18_1895, Q9_1_18_1896, Q9_1_18_99</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ask if Q8_1_19</t>
+  </si>
+  <si>
+    <t>Q8_1_19, Q9_1_19_142, Q9_1_19_143, Q9_1_19_144, Q9_1_19_145, Q9_1_19_146, Q9_1_19_1995, Q9_1_19_1996, Q9_1_19_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_122</t>
+  </si>
+  <si>
+    <t>Q8_2_122, Q9_2_122_9, Q9_2_122_11, Q9_2_122_12, Q9_2_122_19, Q9_2_122_28, Q9_2_122_32, Q9_2_122_33, Q9_2_122_49, Q9_2_122_12295, Q9_2_122_12296, Q9_2_122_99</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_123</t>
+  </si>
+  <si>
+    <t>Q8_2_123, Q9_2_123_22, Q9_2_123_32, Q9_2_123_36, Q9_2_123_41, Q9_2_123_12395, Q9_2_123_12396, Q9_2_123_99</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_125</t>
+  </si>
+  <si>
+    <t>Q8_2_125, Q9_2_125_1, Q9_2_125_2, Q9_2_125_10, Q9_2_125_15, Q9_2_125_20, Q9_2_125_44, Q9_2_125_12595, Q9_2_125_12596, Q9_2_125_99</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_126</t>
+  </si>
+  <si>
+    <t>Q8_2_126, Q9_2_126_6, Q9_2_126_11, Q9_2_126_48, Q9_2_126_49, Q9_2_126_12695, Q9_2_126_12696, Q9_2_126_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_127</t>
+  </si>
+  <si>
+    <t>Q8_2_127, Q9_2_127_1, Q9_2_127_3, Q9_2_127_16, Q9_2_127_37, Q9_2_127_39, Q9_2_127_41, Q9_2_127_45, Q9_2_127_12795, Q9_2_127_12796, Q9_2_127_99</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_128</t>
+  </si>
+  <si>
+    <t>Q8_2_128, Q9_2_128_11, Q9_2_128_16, Q9_2_128_26, Q9_2_128_39, Q9_2_128_40, Q9_2_128_49, Q9_2_128_12895, Q9_2_128_12896, Q9_2_128_99</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_131</t>
+  </si>
+  <si>
+    <t>Q8_2_131, Q9_2_131_7, Q9_2_131_14, Q9_2_131_17, Q9_2_131_27, Q9_2_131_45, Q9_2_131_49, Q9_2_131_13195, Q9_2_131_13196, Q9_2_131_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_15</t>
+  </si>
+  <si>
+    <t>Q8_2_15, Q9_2_15_8, Q9_2_15_18, Q9_2_15_23, Q9_2_15_24, Q9_2_15_42, Q9_2_15_46, Q9_2_15_1595, Q9_2_15_1596, Q9_2_15_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_17</t>
+  </si>
+  <si>
+    <t>Q8_2_17, Q9_2_17_2, Q9_2_17_14, Q9_2_17_42, Q9_2_17_47, Q9_2_17_1795, Q9_2_17_1796, Q9_2_17_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_3</t>
+  </si>
+  <si>
+    <t>Q8_2_3, Q9_2_3_100, Q9_2_3_101, Q9_2_3_102, Q9_2_3_103, Q9_2_3_104, Q9_2_3_105, Q9_2_3_106, Q9_2_3_399</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_4</t>
+  </si>
+  <si>
+    <t>Q8_2_4, Q9_2_4_107, Q9_2_4_108, Q9_2_4_109, Q9_2_4_110, Q9_2_4_111, Q9_2_4_112, Q9_2_4_113, Q9_2_4_114, Q9_2_4_499</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_9</t>
+  </si>
+  <si>
+    <t>Q8_2_9, Q9_2_9_119, Q9_2_9_120, Q9_2_9_121, Q9_2_9_1095, Q9_2_9_1096, Q9_2_9_99</t>
+  </si>
+  <si>
+    <t>2.780000000000001</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>29, 33</t>
-  </si>
-  <si>
-    <t>ASK l36b IF B3=2</t>
-  </si>
-  <si>
-    <t>b3, l36b_final, l36b_final_codes996, l36b_final_codes99</t>
-  </si>
-  <si>
-    <t>ASK l24 IF B3=1</t>
-  </si>
-  <si>
-    <t>b3, l24d_final, l24d_final_codes99</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>ASK K8 IF K7=2 OR 4</t>
-  </si>
-  <si>
-    <t>k7, k8_r1, k8_r2, k8_r3, k8_r4, k8_r5, k8_r6, k8_r97</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>ASK J8 IF J3=ONLY 1 OR 0</t>
-  </si>
-  <si>
-    <t>j7_final, j8_r2, j8_r10, j8_r1, j8_r7, j8_r9, j8_r3, j8_r5, j8_r6, j8_r12, j8_r8, j8_r11, j8_r97</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Recodes/Hidden Variables</t>
-  </si>
-  <si>
-    <t>AUTOPUNCH A3 BASED ON ZIP ENTERED AT P11. SEE ZIP CODE FILE</t>
-  </si>
-  <si>
-    <t>p11, a3</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41</t>
-  </si>
-  <si>
-    <t>Grouping continuous to categories</t>
-  </si>
-  <si>
-    <t>c21, c21rec3buckets</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Number of rows affected: 42</t>
+    <t>16, 53</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_10</t>
+  </si>
+  <si>
+    <t>Q8_2_10, Q9_2_10_122, Q9_2_10_123, Q9_2_10_124, Q9_2_10_125, Q9_2_10_126, Q9_2_10_1095, Q9_2_10_1096, Q9_2_10_99</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_11</t>
+  </si>
+  <si>
+    <t>Q8_2_11, Q9_2_11_124, Q9_2_11_127, Q9_2_11_128, Q9_2_11_129, Q9_2_11_130, Q9_2_11_131, Q9_2_11_132, Q9_2_11_1195, Q9_2_11_1196, Q9_2_11_99</t>
+  </si>
+  <si>
+    <t>35, 62</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_18</t>
+  </si>
+  <si>
+    <t>Q8_2_18, Q9_2_18_134, Q9_2_18_135, Q9_2_18_136, Q9_2_18_137, Q9_2_18_138, Q9_2_18_139, Q9_2_18_140, Q9_2_18_141, Q9_2_18_1895, Q9_2_18_1896, Q9_2_18_99</t>
+  </si>
+  <si>
+    <t>5.560000000000002</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>18, 52, 65, 67</t>
+  </si>
+  <si>
+    <t>53, 62</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_19</t>
+  </si>
+  <si>
+    <t>Q8_2_19, Q9_2_19_142, Q9_2_19_143, Q9_2_19_144, Q9_2_19_145, Q9_2_19_146, Q9_2_19_1995, Q9_2_19_1996, Q9_2_19_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_2_21</t>
+  </si>
+  <si>
+    <t>Q8_2_21, Q9_2_21_147, Q9_2_21_148, Q9_2_21_149, Q9_2_21_150, Q9_2_21_151, Q9_2_21_152, Q9_2_21_153, Q9_2_21_154, Q9_2_21_2095, Q9_2_21_2096, Q9_2_21_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_3_121</t>
+  </si>
+  <si>
+    <t>Q8_3_121, Q9_3_121_2, Q9_3_121_4, Q9_3_121_11, Q9_3_121_13, Q9_3_121_17, Q9_3_121_19, Q9_3_121_21, Q9_3_121_29, Q9_3_121_38, Q9_3_121_12195, Q9_3_121_12196, Q9_3_121_99</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>ask if Q8_3_125</t>
+  </si>
+  <si>
+    <t>Q8_3_125, Q9_3_125_1, Q9_3_125_2, Q9_3_125_10, Q9_3_125_15, Q9_3_125_20, Q9_3_125_44, Q9_3_125_12595, Q9_3_125_12596, Q9_3_125_99</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ask if Q8_3_130</t>
+  </si>
+  <si>
+    <t>Q8_3_130, Q9_3_130_11, Q9_3_130_34, Q9_3_130_13095, Q9_3_130_13096, Q9_3_130_99</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>ask if Q8_3_15</t>
+  </si>
+  <si>
+    <t>Q8_3_15, Q9_3_15_8, Q9_3_15_18, Q9_3_15_23, Q9_3_15_24, Q9_3_15_42, Q9_3_15_46, Q9_3_15_1595, Q9_3_15_1596, Q9_3_15_99</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>ask if Q8_3_10</t>
+  </si>
+  <si>
+    <t>Q8_3_10, Q9_3_10_122, Q9_3_10_123, Q9_3_10_124, Q9_3_10_125, Q9_3_10_126, Q9_3_10_1095, Q9_3_10_1096, Q9_3_10_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_4_121</t>
+  </si>
+  <si>
+    <t>Q8_4_121, Q9_4_121_2, Q9_4_121_4, Q9_4_121_11, Q9_4_121_13, Q9_4_121_17, Q9_4_121_19, Q9_4_121_21, Q9_4_121_29, Q9_4_121_38, Q9_4_121_12195, Q9_4_121_12196, Q9_4_121_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_4_123</t>
+  </si>
+  <si>
+    <t>Q8_4_123, Q9_4_123_22, Q9_4_123_32, Q9_4_123_36, Q9_4_123_41, Q9_4_123_12395, Q9_4_123_12396, Q9_4_123_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_4_128</t>
+  </si>
+  <si>
+    <t>Q8_4_128, Q9_4_128_11, Q9_4_128_16, Q9_4_128_26, Q9_4_128_39, Q9_4_128_40, Q9_4_128_49, Q9_4_128_12895, Q9_4_128_12896, Q9_4_128_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_4_16</t>
+  </si>
+  <si>
+    <t>Q8_4_16, Q9_4_16_133, Q9_4_16_18, Q9_4_16_8, Q9_4_16_1695, Q9_4_16_1696, Q9_4_16_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_5_16</t>
+  </si>
+  <si>
+    <t>Q8_5_16, Q9_5_16_133, Q9_5_16_18, Q9_5_16_8, Q9_5_16_1695, Q9_5_16_1696, Q9_5_16_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_123</t>
+  </si>
+  <si>
+    <t>Q8_9_123, Q9_9_123_22, Q9_9_123_32, Q9_9_123_36, Q9_9_123_41, Q9_9_123_12395, Q9_9_123_12396, Q9_9_123_99</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_125</t>
+  </si>
+  <si>
+    <t>Q8_9_125, Q9_9_125_1, Q9_9_125_2, Q9_9_125_10, Q9_9_125_15, Q9_9_125_20, Q9_9_125_44, Q9_9_125_12595, Q9_9_125_12596, Q9_9_125_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_126</t>
+  </si>
+  <si>
+    <t>Q8_9_126, Q9_9_126_6, Q9_9_126_11, Q9_9_126_48, Q9_9_126_49, Q9_9_126_12695, Q9_9_126_12696, Q9_9_126_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_129</t>
+  </si>
+  <si>
+    <t>Q8_9_129, Q9_9_129_16, Q9_9_129_40, Q9_9_129_43, Q9_9_129_49, Q9_9_129_12995, Q9_9_129_12996, Q9_9_129_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_130</t>
+  </si>
+  <si>
+    <t>Q8_9_130, Q9_9_130_11, Q9_9_130_34, Q9_9_130_13095, Q9_9_130_13096, Q9_9_130_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_17</t>
+  </si>
+  <si>
+    <t>Q8_9_17, Q9_9_17_2, Q9_9_17_14, Q9_9_17_42, Q9_9_17_47, Q9_9_17_1795, Q9_9_17_1796, Q9_9_17_99</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_3</t>
+  </si>
+  <si>
+    <t>Q8_9_3, Q9_9_3_100, Q9_9_3_101, Q9_9_3_102, Q9_9_3_103, Q9_9_3_104, Q9_9_3_105, Q9_9_3_106, Q9_9_3_399</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_4</t>
+  </si>
+  <si>
+    <t>Q8_9_4, Q9_9_4_107, Q9_9_4_108, Q9_9_4_109, Q9_9_4_110, Q9_9_4_111, Q9_9_4_112, Q9_9_4_113, Q9_9_4_114, Q9_9_4_499</t>
+  </si>
+  <si>
+    <t>47, 57</t>
+  </si>
+  <si>
+    <t>ask if Q8_9_21</t>
+  </si>
+  <si>
+    <t>Q8_9_21, Q9_9_21_147, Q9_9_21_148, Q9_9_21_149, Q9_9_21_150, Q9_9_21_151, Q9_9_21_152, Q9_9_21_153, Q9_9_21_154, Q9_9_21_2095, Q9_9_21_2096, Q9_9_21_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_10_127</t>
+  </si>
+  <si>
+    <t>Q8_10_127, Q9_10_127_1, Q9_10_127_3, Q9_10_127_16, Q9_10_127_37, Q9_10_127_39, Q9_10_127_41, Q9_10_127_45, Q9_10_127_12795, Q9_10_127_12796, Q9_10_127_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_10_130</t>
+  </si>
+  <si>
+    <t>Q8_10_130, Q9_10_130_11, Q9_10_130_34, Q9_10_130_13095, Q9_10_130_13096, Q9_10_130_99</t>
+  </si>
+  <si>
+    <t>ask if Q8_10_4</t>
+  </si>
+  <si>
+    <t>Q8_10_4, Q9_10_4_107, Q9_10_4_108, Q9_10_4_109, Q9_10_4_110, Q9_10_4_111, Q9_10_4_112, Q9_10_4_113, Q9_10_4_114, Q9_10_4_499</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>Selecting one answer prevents the selection of any other options.</t>
+  </si>
+  <si>
+    <t>Q9_7_19_142, Q9_7_19_143, Q9_7_19_144, Q9_7_19_145, Q9_7_19_146, Q9_7_19_1995, Q9_7_19_1996, Q9_7_19_99</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Q9_11_130_11, Q9_11_130_34, Q9_11_130_13095, Q9_11_130_13096, Q9_11_130_99</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Q9_11_129_16, Q9_11_129_40, Q9_11_129_43, Q9_11_129_49, Q9_11_129_12995, Q9_11_129_99, Q9_11_129_12996</t>
+  </si>
+  <si>
+    <t>Number of rows affected: 26</t>
   </si>
 </sst>
 </file>
@@ -637,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -695,7 +890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="30" customHeight="1">
+    <row r="9" spans="2:8" ht="45" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
@@ -718,7 +913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="30" customHeight="1">
+    <row r="10" spans="2:8" ht="45" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
@@ -735,90 +930,90 @@
         <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="30" customHeight="1">
+    <row r="11" spans="2:8" ht="45" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="90" customHeight="1">
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="60" customHeight="1">
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="90" customHeight="1">
+      <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="30" customHeight="1">
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="30" customHeight="1">
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="30" customHeight="1">
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="C14" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>13</v>
@@ -827,21 +1022,21 @@
         <v>14</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="30" customHeight="1">
+    <row r="15" spans="2:8" ht="60" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>13</v>
@@ -850,21 +1045,21 @@
         <v>14</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="30" customHeight="1">
+    <row r="16" spans="2:8" ht="75" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>13</v>
@@ -873,21 +1068,21 @@
         <v>14</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="20" customHeight="1">
+    <row r="17" spans="2:8" ht="60" customHeight="1">
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>13</v>
@@ -896,61 +1091,61 @@
         <v>14</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="20" customHeight="1">
+    <row r="18" spans="2:8" ht="75" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="75" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="45" customHeight="1">
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="H19" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="45" customHeight="1">
+    <row r="20" spans="2:8" ht="75" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>44</v>
@@ -971,116 +1166,116 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="30" customHeight="1">
+    <row r="21" spans="2:8" ht="75" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="H21" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="75" customHeight="1">
+      <c r="B22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="20" customHeight="1">
-      <c r="B22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="60" customHeight="1">
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="E23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="60" customHeight="1">
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="30" customHeight="1">
-      <c r="B23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="E24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="60" customHeight="1">
+      <c r="B25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="30" customHeight="1">
-      <c r="B24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="E25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="30" customHeight="1">
-      <c r="B25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>16</v>
@@ -1088,76 +1283,927 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="60" customHeight="1">
+      <c r="B27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="60" customHeight="1">
+      <c r="B28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="45" customHeight="1">
+      <c r="B29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="30" customHeight="1">
-      <c r="B27" s="4" t="s">
+      <c r="H29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="60" customHeight="1">
+      <c r="B30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="H30" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="75" customHeight="1">
+      <c r="B31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="30" customHeight="1">
-      <c r="B28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="H31" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="75" customHeight="1">
+      <c r="B32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="90" customHeight="1">
+      <c r="B33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="F30" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>74</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="90" customHeight="1">
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="60" customHeight="1">
+      <c r="B35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="60" customHeight="1">
+      <c r="B36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="90" customHeight="1">
+      <c r="B37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="90" customHeight="1">
+      <c r="B38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="90" customHeight="1">
+      <c r="B39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="90" customHeight="1">
+      <c r="B40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="75" customHeight="1">
+      <c r="B41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="45" customHeight="1">
+      <c r="B42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="60" customHeight="1">
+      <c r="B43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="60" customHeight="1">
+      <c r="B44" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="60" customHeight="1">
+      <c r="B45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="90" customHeight="1">
+      <c r="B46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="60" customHeight="1">
+      <c r="B47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="75" customHeight="1">
+      <c r="B48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="45" customHeight="1">
+      <c r="B49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="45" customHeight="1">
+      <c r="B50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="60" customHeight="1">
+      <c r="B51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="75" customHeight="1">
+      <c r="B52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="60" customHeight="1">
+      <c r="B53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="60" customHeight="1">
+      <c r="B54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="45" customHeight="1">
+      <c r="B55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="60" customHeight="1">
+      <c r="B56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="60" customHeight="1">
+      <c r="B57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="60" customHeight="1">
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="90" customHeight="1">
+      <c r="B59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="90" customHeight="1">
+      <c r="B60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="45" customHeight="1">
+      <c r="B61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="75" customHeight="1">
+      <c r="B62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="60" customHeight="1">
+      <c r="B63" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="45" customHeight="1">
+      <c r="B64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="60" customHeight="1">
+      <c r="B65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="F67" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -46,28 +46,154 @@
     <t>Supported</t>
   </si>
   <si>
-    <t>Dynamic Piping Single-to-Single</t>
-  </si>
-  <si>
-    <t>Dynamic answer choices</t>
-  </si>
-  <si>
-    <t>QD1, QD2A</t>
-  </si>
-  <si>
-    <t>93.95</t>
-  </si>
-  <si>
-    <t>2067</t>
-  </si>
-  <si>
-    <t>0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 28, 29, 30, 31, 32, 33, 34, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 100, 101, 102, 103, 104, 105, 106, 107, 109, 110, 111, 112, 114, 115, 116, 117, 118, 119, 120, 121, 122, 123, 124, 125, 126, 127, 128, 129, 130, 131, 132, 133, 134, 135, 136, 137, 138, 139, 140, 141, 142, 143, 144, 145, 146, 147, 149, 150, 151, 152, 153, 154, 155, 156, 157, 158, 159, 160, 162, 164, 165, 166, 167, 168, 169, 170, 171, 172, 173, 174, 175, 176, 177, 178, 179, 180, 181, 182, 183, 184, 185, 186, 188, 189, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 221, 222, 223, 224, 225, 226, 227, 228, 229, 230, 231, 232, 233, 234, 235, 236, 237, 238, 239, 240, 241, 242, 243, 244, 245, 247, 248, 249, 250, 251, 252, 253, 254, 255, 256, 257, 258, 259, 260, 261, 262, 263, 264, 265, 266, 267, 268, 269, 270, 271, 272, 273, 274, 276, 277, 280, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 297, 298, 299, 300, 301, 302, 303, 304, 305, 306, 307, 308, 309, 310, 311, 312, 313, 314, 315, 316, 317, 318, 319, 320, 321, 323, 324, 325, 327, 328, 329, 330, 331, 332, 333, 334, 335, 336, 337, 338, 339, 340, 341, 344, 345, 346, 347, 348, 349, 350, 351, 352, 353, 354, 355, 356, 357, 358, 359, 360, 361, 362, 363, 364, 365, 366, 367, 368, 369, 370, 371, 373, 374, 375, 376, 377, 378, 379, 380, 381, 382, 383, 384, 385, 386, 387, 388, 389, 390, 391, 392, 393, 394, 395, 396, 397, 398, 399, 400, 401, 402, 403, 404, 405, 406, 407, 408, 409, 410, 411, 412, 413, 414, 415, 416, 417, 419, 420, 421, 422, 423, 424, 425, 426, 427, 428, 429, 430, 431, 432, 433, 435, 436, 437, 438, 439, 440, 441, 442, 443, 444, 445, 446, 447, 448, 449, 450, 451, 452, 453, 454, 455, 456, 457, 458, 459, 460, 461, 462, 463, 464, 465, 466, 467, 469, 470, 472, 473, 474, 475, 476, 478, 479, 480, 481, 482, 483, 484, 485, 486, 487, 488, 489, 490, 491, 492, 493, 494, 495, 496, 497, 498, 499, 500, 501, 502, 503, 504, 505, 506, 507, 508, 509, 510, 511, 512, 514, 515, 516, 517, 518, 520, 521, 522, 523, 524, 525, 526, 527, 528, 529, 530, 531, 532, 533, 534, 535, 536, 537, 538, 539, 540, 541, 542, 543, 544, 545, 546, 547, 548, 550, 551, 552, 553, 554, 555, 557, 558, 559, 560, 561, 562, 563, 564, 565, 566, 567, 568, 569, 570, 571, 572, 573, 574, 575, 576, 577, 579, 580, 581, 582, 583, 584, 585, 586, 587, 588, 589, 591, 592, 593, 594, 595, 596, 597, 598, 599, 600, 601, 602, 603, 604, 605, 606, 607, 608, 609, 610, 611, 612, 613, 614, 615, 616, 617, 618, 619, 620, 621, 622, 623, 624, 625, 626, 627, 628, 629, 630, 631, 633, 634, 636, 637, 638, 639, 640, 641, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 653, 654, 655, 656, 657, 658, 659, 660, 661, 662, 663, 665, 666, 667, 668, 669, 670, 672, 673, 674, 675, 676, 677, 678, 679, 680, 681, 682, 683, 684, 685, 686, 687, 688, 689, 690, 691, 692, 693, 694, 695, 696, 697, 698, 699, 700, 701, 702, 703, 704, 705, 706, 707, 708, 709, 710, 711, 712, 713, 714, 715, 716, 717, 718, 719, 720, 721, 722, 723, 724, 725, 726, 727, 728, 729, 730, 731, 732, 733, 734, 735, 736, 737, 738, 739, 740, 742, 743, 744, 746, 747, 749, 750, 751, 752, 753, 754, 755, 756, 757, 758, 759, 760, 761, 762, 763, 764, 765, 766, 768, 769, 770, 771, 772, 773, 774, 776, 777, 778, 779, 781, 782, 783, 784, 785, 786, 788, 789, 790, 791, 792, 793, 794, 795, 797, 798, 799, 800, 801, 802, 803, 805, 806, 807, 808, 809, 810, 811, 812, 813, 814, 815, 818, 819, 820, 821, 822, 823, 824, 825, 827, 828, 829, 830, 831, 832, 833, 834, 835, 836, 837, 838, 839, 840, 842, 843, 844, 845, 846, 847, 848, 849, 850, 851, 852, 853, 854, 855, 856, 857, 859, 860, 861, 862, 863, 864, 865, 866, 867, 868, 870, 871, 872, 873, 874, 875, 876, 877, 878, 879, 880, 881, 882, 884, 885, 886, 887, 888, 889, 890, 891, 892, 893, 894, 895, 896, 897, 898, 899, 900, 901, 902, 903, 904, 905, 906, 907, 908, 909, 910, 911, 912, 913, 914, 915, 916, 918, 919, 920, 921, 922, 923, 924, 925, 926, 927, 929, 930, 931, 933, 934, 935, 936, 937, 938, 939, 940, 941, 942, 943, 944, 945, 946, 947, 948, 951, 952, 953, 954, 955, 956, 957, 958, 959, 960, 961, 962, 963, 964, 965, 967, 968, 969, 970, 972, 973, 974, 975, 976, 977, 978, 979, 980, 981, 982, 983, 984, 985, 986, 987, 988, 989, 990, 991, 992, 993, 994, 995, 996, 997, 998, 999, 1000, 1001, 1002, 1003, 1006, 1007, 1008, 1009, 1010, 1011, 1013, 1014, 1015, 1016, 1017, 1018, 1019, 1020, 1021, 1022, 1023, 1024, 1025, 1026, 1027, 1028, 1029, 1030, 1031, 1033, 1034, 1035, 1036, 1037, 1038, 1039, 1040, 1041, 1042, 1043, 1044, 1045, 1046, 1047, 1048, 1050, 1051, 1052, 1053, 1054, 1055, 1056, 1057, 1058, 1059, 1060, 1061, 1062, 1064, 1066, 1067, 1068, 1069, 1070, 1071, 1072, 1073, 1075, 1076, 1077, 1078, 1079, 1080, 1081, 1082, 1083, 1084, 1085, 1086, 1087, 1088, 1089, 1090, 1091, 1092, 1093, 1094, 1095, 1097, 1098, 1099, 1100, 1101, 1102, 1103, 1104, 1105, 1106, 1107, 1108, 1109, 1110, 1111, 1112, 1113, 1114, 1115, 1116, 1117, 1118, 1119, 1120, 1121, 1122, 1123, 1124, 1125, 1126, 1127, 1128, 1129, 1130, 1131, 1132, 1133, 1134, 1135, 1137, 1139, 1140, 1141, 1142, 1143, 1144, 1145, 1146, 1147, 1148, 1149, 1151, 1152, 1154, 1155, 1156, 1157, 1158, 1159, 1160, 1161, 1162, 1163, 1164, 1165, 1166, 1167, 1168, 1169, 1170, 1171, 1173, 1174, 1175, 1177, 1178, 1179, 1180, 1181, 1183, 1184, 1185, 1186, 1187, 1189, 1190, 1191, 1192, 1193, 1194, 1195, 1196, 1197, 1198, 1199, 1200, 1201, 1202, 1203, 1204, 1205, 1206, 1207, 1208, 1209, 1210, 1211, 1212, 1213, 1214, 1215, 1217, 1219, 1221, 1222, 1223, 1225, 1226, 1227, 1228, 1229, 1230, 1231, 1232, 1233, 1234, 1238, 1239, 1240, 1241, 1242, 1243, 1244, 1245, 1246, 1247, 1248, 1250, 1251, 1252, 1253, 1254, 1255, 1256, 1257, 1258, 1259, 1260, 1261, 1262, 1263, 1264, 1265, 1266, 1267, 1268, 1269, 1270, 1271, 1272, 1273, 1274, 1275, 1277, 1278, 1280, 1281, 1282, 1283, 1284, 1285, 1286, 1287, 1288, 1289, 1290, 1291, 1293, 1294, 1295, 1296, 1297, 1298, 1299, 1300, 1301, 1302, 1303, 1304, 1305, 1306, 1307, 1308, 1310, 1311, 1312, 1313, 1314, 1315, 1316, 1317, 1318, 1319, 1320, 1321, 1322, 1323, 1324, 1325, 1326, 1327, 1328, 1329, 1330, 1331, 1332, 1333, 1335, 1336, 1337, 1338, 1339, 1340, 1341, 1342, 1343, 1344, 1346, 1347, 1348, 1349, 1350, 1351, 1352, 1353, 1354, 1355, 1356, 1357, 1358, 1359, 1360, 1361, 1362, 1363, 1364, 1365, 1366, 1367, 1368, 1369, 1370, 1371, 1373, 1374, 1375, 1377, 1378, 1379, 1380, 1381, 1382, 1383, 1384, 1385, 1387, 1388, 1390, 1391, 1392, 1393, 1394, 1395, 1396, 1397, 1399, 1400, 1401, 1402, 1403, 1404, 1405, 1406, 1407, 1408, 1409, 1410, 1411, 1412, 1413, 1414, 1415, 1416, 1417, 1418, 1419, 1420, 1421, 1422, 1423, 1424, 1425, 1426, 1428, 1429, 1430, 1431, 1432, 1433, 1434, 1435, 1437, 1438, 1439, 1440, 1441, 1442, 1443, 1444, 1445, 1446, 1447, 1448, 1449, 1450, 1451, 1452, 1453, 1454, 1455, 1456, 1457, 1458, 1459, 1460, 1461, 1462, 1463, 1464, 1465, 1467, 1468, 1469, 1470, 1471, 1472, 1474, 1475, 1476, 1477, 1478, 1479, 1480, 1481, 1482, 1483, 1484, 1485, 1486, 1487, 1489, 1490, 1491, 1493, 1494, 1496, 1497, 1498, 1499, 1500, 1501, 1502, 1503, 1505, 1506, 1507, 1508, 1509, 1510, 1512, 1513, 1514, 1515, 1516, 1517, 1518, 1519, 1520, 1522, 1523, 1524, 1525, 1526, 1527, 1528, 1529, 1530, 1531, 1532, 1533, 1534, 1535, 1536, 1537, 1538, 1539, 1540, 1541, 1542, 1543, 1544, 1545, 1546, 1547, 1548, 1549, 1550, 1551, 1552, 1553, 1554, 1555, 1556, 1557, 1558, 1559, 1560, 1561, 1563, 1564, 1565, 1566, 1567, 1568, 1569, 1570, 1571, 1572, 1573, 1574, 1576, 1577, 1578, 1579, 1580, 1581, 1582, 1583, 1584, 1585, 1586, 1587, 1588, 1589, 1590, 1591, 1592, 1593, 1594, 1596, 1597, 1598, 1599, 1600, 1601, 1602, 1603, 1604, 1605, 1606, 1607, 1608, 1609, 1610, 1612, 1613, 1614, 1615, 1616, 1617, 1618, 1619, 1620, 1621, 1622, 1623, 1624, 1625, 1626, 1627, 1628, 1629, 1630, 1631, 1632, 1633, 1634, 1635, 1636, 1637, 1638, 1639, 1641, 1642, 1643, 1644, 1645, 1646, 1647, 1649, 1650, 1651, 1652, 1653, 1654, 1656, 1657, 1659, 1660, 1661, 1662, 1663, 1664, 1665, 1666, 1667, 1668, 1669, 1670, 1671, 1672, 1673, 1674, 1675, 1676, 1677, 1678, 1679, 1680, 1681, 1682, 1683, 1684, 1685, 1686, 1687, 1688, 1689, 1691, 1692, 1693, 1694, 1695, 1696, 1697, 1698, 1699, 1700, 1701, 1702, 1704, 1705, 1706, 1707, 1708, 1709, 1710, 1711, 1712, 1713, 1714, 1715, 1716, 1717, 1718, 1719, 1720, 1721, 1722, 1723, 1724, 1725, 1726, 1727, 1728, 1729, 1730, 1731, 1732, 1733, 1735, 1736, 1737, 1738, 1739, 1740, 1741, 1742, 1744, 1745, 1746, 1747, 1748, 1749, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1758, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1767, 1768, 1769, 1770, 1771, 1772, 1773, 1774, 1775, 1776, 1778, 1779, 1780, 1781, 1782, 1783, 1784, 1785, 1786, 1787, 1788, 1789, 1790, 1791, 1792, 1793, 1794, 1795, 1796, 1797, 1798, 1799, 1800, 1801, 1802, 1803, 1804, 1805, 1806, 1807, 1808, 1809, 1810, 1812, 1813, 1814, 1815, 1816, 1817, 1818, 1819, 1820, 1821, 1822, 1823, 1824, 1825, 1826, 1827, 1828, 1829, 1830, 1831, 1832, 1833, 1834, 1835, 1836, 1837, 1838, 1839, 1840, 1841, 1842, 1843, 1844, 1845, 1846, 1847, 1848, 1849, 1850, 1851, 1852, 1853, 1854, 1855, 1856, 1857, 1858, 1859, 1860, 1861, 1862, 1863, 1864, 1865, 1866, 1868, 1869, 1870, 1871, 1872, 1873, 1874, 1875, 1876, 1877, 1878, 1879, 1880, 1882, 1883, 1884, 1885, 1886, 1888, 1889, 1890, 1891, 1892, 1893, 1894, 1895, 1896, 1897, 1898, 1899, 1900, 1901, 1902, 1903, 1904, 1905, 1906, 1907, 1908, 1909, 1910, 1911, 1912, 1914, 1915, 1916, 1917, 1918, 1919, 1920, 1921, 1922, 1923, 1924, 1925, 1926, 1927, 1928, 1929, 1930, 1931, 1932, 1933, 1934, 1935, 1936, 1937, 1938, 1939, 1940, 1941, 1942, 1943, 1944, 1945, 1946, 1947, 1948, 1949, 1950, 1951, 1952, 1953, 1954, 1955, 1956, 1957, 1958, 1959, 1960, 1962, 1963, 1964, 1965, 1966, 1967, 1969, 1970, 1971, 1972, 1973, 1974, 1975, 1976, 1977, 1978, 1979, 1980, 1981, 1982, 1983, 1984, 1985, 1986, 1987, 1988, 1989, 1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, 2026, 2027, 2028, 2029, 2030, 2031, 2032, 2033, 2034, 2035, 2036, 2037, 2038, 2039, 2040, 2041, 2042, 2043, 2044, 2045, 2046, 2047, 2048, 2049, 2050, 2051, 2053, 2054, 2055, 2057, 2058, 2059, 2060, 2061, 2062, 2063, 2064, 2065, 2066, 2067, 2068, 2069, 2070, 2071, 2072, 2073, 2074, 2075, 2076, 2077, 2078, 2079, 2080, 2081, 2082, 2083, 2084, 2085, 2086, 2087, 2088, 2089, 2090, 2091, 2092, 2093, 2094, 2095, 2096, 2097, 2098, 2099, 2100, 2101, 2102, 2103, 2104, 2105, 2106, 2107, 2108, 2109, 2110, 2111, 2112, 2113, 2114, 2115, 2117, 2118, 2119, 2120, 2121, 2122, 2123, 2124, 2125, 2126, 2127, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2137, 2138, 2139, 2140, 2141, 2142, 2143, 2144, 2145, 2146, 2147, 2148, 2149, 2150, 2151, 2152, 2153, 2154, 2155, 2156, 2157, 2158, 2159, 2160, 2161, 2162, 2163, 2164, 2165, 2166, 2167, 2168, 2169, 2171, 2172, 2173, 2174, 2175, 2176, 2177, 2178, 2179, 2180, 2181, 2182, 2183, 2184, 2185, 2186, 2187, 2188, 2189, 2190, 2191, 2192, 2193, 2194, 2195, 2196, 2197, 2199</t>
+    <t>Skip Logic</t>
+  </si>
+  <si>
+    <t>Skip if R15=5</t>
+  </si>
+  <si>
+    <t>R15, R20</t>
+  </si>
+  <si>
+    <t>3.3299999999999983</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Number of rows affected: 2067</t>
+    <t>R15, R21</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>Selecting one answer prevents the selection of any other options.</t>
+  </si>
+  <si>
+    <t>A06r1, A06r2, A06r3, A06r4, A06r5, A06r6, A06r7, A06r8, A06r9, A06r10, noanswerA06_r99</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Recodes/Hidden Variables</t>
+  </si>
+  <si>
+    <t>Recode single to single</t>
+  </si>
+  <si>
+    <t>D15r4, hD15r4</t>
+  </si>
+  <si>
+    <t>16.67</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>13, 19, 22, 23, 25</t>
+  </si>
+  <si>
+    <t>D15r5, hD15r5</t>
+  </si>
+  <si>
+    <t>26.67</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>11, 16, 17, 18, 19, 20, 22, 26</t>
+  </si>
+  <si>
+    <t>Selection Limit Control</t>
+  </si>
+  <si>
+    <t>Minimum and/or maximum limits on the number of choices a respondent can select.</t>
+  </si>
+  <si>
+    <t>T38r1, T38r2, T38r3, T38r4, T38r5, T38r6, T38r7, T38r8, T38r9</t>
+  </si>
+  <si>
+    <t>33.33</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10, 16, 18, 19, 20, 21, 22, 24, 26, 27</t>
+  </si>
+  <si>
+    <t>Calculation Logic</t>
+  </si>
+  <si>
+    <t>A13r1, A13r2, A13r3, A13r4, A13r5, A13r6, A13r98</t>
+  </si>
+  <si>
+    <t>13.329999999999998</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10, 14, 22, 23</t>
+  </si>
+  <si>
+    <t>A14r1, A14r2, A14r3, A14r4, A14r5, A14r6, A14r7, A14r8, A14r9, A14r98</t>
+  </si>
+  <si>
+    <t>6.670000000000002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>11, 17</t>
+  </si>
+  <si>
+    <t>Norm check</t>
+  </si>
+  <si>
+    <t>F10r2, F10_normr2_l, F10_normr2_r</t>
+  </si>
+  <si>
+    <t>18, 25</t>
+  </si>
+  <si>
+    <t>F10r1, F10_normr1_l, F10_normr1_r</t>
+  </si>
+  <si>
+    <t>D15r2b, D15_normr2b_l, D15_normr2b_r</t>
+  </si>
+  <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 25, 26, 27, 28, 29</t>
+  </si>
+  <si>
+    <t>D15r2a, D15_normr2a_l, D15_normr2a_r</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10, 12, 24</t>
+  </si>
+  <si>
+    <t>Number of rows affected: 30</t>
   </si>
 </sst>
 </file>
@@ -466,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -524,7 +650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="30" customHeight="1">
+    <row r="9" spans="2:8" ht="20" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
@@ -547,9 +673,258 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="F11" s="5" t="s">
+    <row r="10" spans="2:8" ht="20" customHeight="1">
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="45" customHeight="1">
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="20" customHeight="1">
+      <c r="B12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="20" customHeight="1">
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="45" customHeight="1">
+      <c r="B14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="30" customHeight="1">
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="45" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="30" customHeight="1">
+      <c r="B17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="30" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="30" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="30" customHeight="1">
+      <c r="B20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="F22" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -46,154 +46,43 @@
     <t>Supported</t>
   </si>
   <si>
-    <t>Skip Logic</t>
-  </si>
-  <si>
-    <t>Skip if R15=5</t>
-  </si>
-  <si>
-    <t>R15, R20</t>
-  </si>
-  <si>
-    <t>3.3299999999999983</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>Dynamic Piping Single-to-Single</t>
+  </si>
+  <si>
+    <t>Dynamic answer choices</t>
+  </si>
+  <si>
+    <t>REGION_Demographic, GROSSREG</t>
+  </si>
+  <si>
+    <t>1.6500000000000057</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>45, 48, 70, 73, 83, 192, 249, 334, 342, 492, 514, 602, 625, 641, 652, 861, 901, 916, 1040</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>R15, R21</t>
-  </si>
-  <si>
-    <t>Exclusive</t>
-  </si>
-  <si>
-    <t>Selecting one answer prevents the selection of any other options.</t>
-  </si>
-  <si>
-    <t>A06r1, A06r2, A06r3, A06r4, A06r5, A06r6, A06r7, A06r8, A06r9, A06r10, noanswerA06_r99</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Recodes/Hidden Variables</t>
-  </si>
-  <si>
-    <t>Recode single to single</t>
-  </si>
-  <si>
-    <t>D15r4, hD15r4</t>
-  </si>
-  <si>
-    <t>16.67</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>13, 19, 22, 23, 25</t>
-  </si>
-  <si>
-    <t>D15r5, hD15r5</t>
-  </si>
-  <si>
-    <t>26.67</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>11, 16, 17, 18, 19, 20, 22, 26</t>
-  </si>
-  <si>
-    <t>Selection Limit Control</t>
-  </si>
-  <si>
-    <t>Minimum and/or maximum limits on the number of choices a respondent can select.</t>
-  </si>
-  <si>
-    <t>T38r1, T38r2, T38r3, T38r4, T38r5, T38r6, T38r7, T38r8, T38r9</t>
-  </si>
-  <si>
-    <t>33.33</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10, 16, 18, 19, 20, 21, 22, 24, 26, 27</t>
-  </si>
-  <si>
-    <t>Calculation Logic</t>
-  </si>
-  <si>
-    <t>A13r1, A13r2, A13r3, A13r4, A13r5, A13r6, A13r98</t>
-  </si>
-  <si>
-    <t>13.329999999999998</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10, 14, 22, 23</t>
-  </si>
-  <si>
-    <t>A14r1, A14r2, A14r3, A14r4, A14r5, A14r6, A14r7, A14r8, A14r9, A14r98</t>
-  </si>
-  <si>
-    <t>6.670000000000002</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>11, 17</t>
-  </si>
-  <si>
-    <t>Norm check</t>
-  </si>
-  <si>
-    <t>F10r2, F10_normr2_l, F10_normr2_r</t>
-  </si>
-  <si>
-    <t>18, 25</t>
-  </si>
-  <si>
-    <t>F10r1, F10_normr1_l, F10_normr1_r</t>
-  </si>
-  <si>
-    <t>D15r2b, D15_normr2b_l, D15_normr2b_r</t>
-  </si>
-  <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 25, 26, 27, 28, 29</t>
-  </si>
-  <si>
-    <t>D15r2a, D15_normr2a_l, D15_normr2a_r</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10, 12, 24</t>
-  </si>
-  <si>
-    <t>Number of rows affected: 30</t>
+    <t>GROSSREG, Kanton</t>
+  </si>
+  <si>
+    <t>5.280000000000001</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>45, 48, 52, 70, 84, 104, 109, 192, 203, 234, 244, 287, 291, 293, 296, 297, 300, 308, 334, 338, 342, 376, 387, 391, 392, 394, 398, 401, 418, 477, 484, 498, 506, 514, 516, 517, 530, 543, 548, 549, 561, 602, 625, 629, 635, 641, 652, 668, 734, 736, 765, 856, 870, 916, 924, 1000, 1026, 1030, 1040, 1053, 1122</t>
+  </si>
+  <si>
+    <t>Number of rows affected: 67</t>
+  </si>
+  <si>
+    <t>Percentage of rows affected: 5.8</t>
   </si>
 </sst>
 </file>
@@ -592,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -650,7 +539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20" customHeight="1">
+    <row r="9" spans="2:8" ht="30" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
@@ -673,7 +562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20" customHeight="1">
+    <row r="10" spans="2:8" ht="30" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
@@ -684,247 +573,26 @@
         <v>17</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="45" customHeight="1">
-      <c r="B11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="4" t="s">
+    <row r="12" spans="2:8">
+      <c r="F12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="20" customHeight="1">
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13" spans="2:8">
+      <c r="F13" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="20" customHeight="1">
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" ht="45" customHeight="1">
-      <c r="B14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="30" customHeight="1">
-      <c r="B15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="45" customHeight="1">
-      <c r="B16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="30" customHeight="1">
-      <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="30" customHeight="1">
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="30" customHeight="1">
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="30" customHeight="1">
-      <c r="B20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="F22" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="378">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -46,43 +46,1124 @@
     <t>Supported</t>
   </si>
   <si>
-    <t>Dynamic Piping Single-to-Single</t>
-  </si>
-  <si>
-    <t>Dynamic answer choices</t>
-  </si>
-  <si>
-    <t>REGION_Demographic, GROSSREG</t>
-  </si>
-  <si>
-    <t>1.6500000000000057</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>45, 48, 70, 73, 83, 192, 249, 334, 342, 492, 514, 602, 625, 641, 652, 861, 901, 916, 1040</t>
+    <t>Skip Logic</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr1c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr1c3, Q_JourneyPerfPSr1</t>
+  </si>
+  <si>
+    <t>0.9200000000000017</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>71, 91, 122</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>GROSSREG, Kanton</t>
-  </si>
-  <si>
-    <t>5.280000000000001</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>45, 48, 52, 70, 84, 104, 109, 192, 203, 234, 244, 287, 291, 293, 296, 297, 300, 308, 334, 338, 342, 376, 387, 391, 392, 394, 398, 401, 418, 477, 484, 498, 506, 514, 516, 517, 530, 543, 548, 549, 561, 602, 625, 629, 635, 641, 652, 668, 734, 736, 765, 856, 870, 916, 924, 1000, 1026, 1030, 1040, 1053, 1122</t>
-  </si>
-  <si>
-    <t>Number of rows affected: 67</t>
-  </si>
-  <si>
-    <t>Percentage of rows affected: 5.8</t>
+    <t>Mandatory Logic</t>
+  </si>
+  <si>
+    <t>194, 221, 281</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr2c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c3, Q_JourneyPerfPSr2</t>
+  </si>
+  <si>
+    <t>2.450000000000003</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>115, 124, 133, 229, 276, 317, 325, 326</t>
+  </si>
+  <si>
+    <t>1.2199999999999989</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>68, 110, 180, 298</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr3c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c3, Q_JourneyPerfPSr3</t>
+  </si>
+  <si>
+    <t>0.6099999999999994</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>276, 283</t>
+  </si>
+  <si>
+    <t>46, 218</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr4c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c3, Q_JourneyPerfPSr4</t>
+  </si>
+  <si>
+    <t>3.3599999999999994</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>51, 71, 73, 97, 115, 135, 185, 191, 233, 276, 283</t>
+  </si>
+  <si>
+    <t>3.980000000000004</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>67, 110, 112, 129, 175, 195, 207, 221, 284, 295, 298, 303, 309</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr5c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c3, Q_JourneyPerfPSr5</t>
+  </si>
+  <si>
+    <t>4.890000000000001</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>67, 84, 88, 97, 108, 122, 124, 136, 194, 198, 215, 222, 276, 280, 317, 326</t>
+  </si>
+  <si>
+    <t>52, 70, 91, 115, 134, 190, 210, 211, 214, 236, 275</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr6c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c3, Q_JourneyPerfPSr6</t>
+  </si>
+  <si>
+    <t>6.420000000000002</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>54, 76, 97, 115, 117, 126, 131, 187, 190, 195, 214, 217, 223, 236, 242, 283, 288, 292, 299, 313, 319</t>
+  </si>
+  <si>
+    <t>46, 67, 83, 104, 110, 181, 185, 188, 197, 213, 226, 306, 310</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr7c3 &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c3, Q_JourneyPerfPSr7</t>
+  </si>
+  <si>
+    <t>7.030000000000001</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>50, 61, 67, 86, 98, 104, 110, 120, 125, 188, 192, 194, 200, 205, 213, 219, 225, 233, 237, 276, 301, 310, 323</t>
+  </si>
+  <si>
+    <t>228, 309, 326</t>
+  </si>
+  <si>
+    <t>ask if Q_Journey3Pr &gt; 0 and S_ServicesUsedr3=1</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr3, Q_JourneyPSOE1</t>
+  </si>
+  <si>
+    <t>13.459999999999994</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>53, 55, 58, 64, 69, 80, 85, 89, 90, 93, 100, 111, 118, 121, 127, 130, 132, 137, 173, 174, 176, 177, 178, 182, 186, 189, 193, 196, 201, 208, 212, 216, 224, 235, 272, 274, 283, 289, 290, 293, 305, 307, 320, 324</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr3, Q_JourneyPSOE2</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr1if Q_Journey3Pr1c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr1c4, Q_JourneyPerfGCr1</t>
+  </si>
+  <si>
+    <t>0.3100000000000023</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>1.5300000000000011</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>97, 133, 182, 218, 308</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr2if
+  Q_Journey3Pr2c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c4, Q_JourneyPerfGCr2</t>
+  </si>
+  <si>
+    <t>2.1400000000000006</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>52, 68, 226, 230, 294, 298, 306</t>
+  </si>
+  <si>
+    <t>80, 199, 207, 313</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr3if
+  Q_Journey3Pr3c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c4, Q_JourneyPerfGCr3</t>
+  </si>
+  <si>
+    <t>62, 79, 131</t>
+  </si>
+  <si>
+    <t>129, 174, 218, 307, 310</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr4if
+  Q_Journey3Pr4c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c4, Q_JourneyPerfGCr4</t>
+  </si>
+  <si>
+    <t>8.560000000000002</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>47, 54, 58, 62, 68, 72, 75, 76, 92, 97, 99, 103, 117, 119, 121, 125, 127, 174, 182, 193, 203, 230, 239, 283, 306, 310, 319, 321</t>
+  </si>
+  <si>
+    <t>2.75</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>49, 63, 105, 118, 123, 179, 183, 284, 302</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr5if
+  Q_Journey3Pr5c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c4, Q_JourneyPerfGCr5</t>
+  </si>
+  <si>
+    <t>6.730000000000004</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>54, 58, 64, 71, 79, 84, 97, 103, 107, 125, 133, 135, 182, 193, 194, 218, 225, 239, 288, 308, 310, 321</t>
+  </si>
+  <si>
+    <t>88, 92, 180, 230, 233, 237, 274, 294, 319</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr6if
+  Q_Journey3Pr6c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c4, Q_JourneyPerfGCr6</t>
+  </si>
+  <si>
+    <t>5.200000000000003</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>58, 75, 88, 94, 129, 131, 178, 187, 203, 206, 217, 230, 274, 294, 299, 304, 323</t>
+  </si>
+  <si>
+    <t>46, 52, 64, 76, 79, 80, 96, 99, 103, 107, 111, 119, 121, 182, 199, 209, 226, 283, 284, 290, 310, 315, 321</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfGCr7if
+  Q_Journey3Pr7c4&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c4, Q_JourneyPerfGCr7</t>
+  </si>
+  <si>
+    <t>46, 52, 71, 76, 96, 111, 113, 119, 194, 290, 321</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr1if Q_Journey3Pr1c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr1c5, Q_JourneyPerfSSr1</t>
+  </si>
+  <si>
+    <t>173, 198, 229, 294, 296</t>
+  </si>
+  <si>
+    <t>66, 79, 110, 115, 128, 183, 227, 228, 277, 287, 299, 314, 326</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr2if Q_Journey3Pr2c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c5, Q_JourneyPerfSSr2</t>
+  </si>
+  <si>
+    <t>1.8299999999999983</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>65, 86, 95, 192, 316, 317</t>
+  </si>
+  <si>
+    <t>74, 79, 100, 120, 173, 188, 227, 278, 286, 287, 299, 312, 325</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr3if
+  Q_Journey3Pr3c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c5, Q_JourneyPerfSSr3</t>
+  </si>
+  <si>
+    <t>57, 89, 212, 283, 315</t>
+  </si>
+  <si>
+    <t>70, 74, 79, 106, 110, 115, 120, 173, 227, 236, 278, 286, 287, 299, 312, 314, 316</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr4if
+  Q_Journey3Pr4c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c5, Q_JourneyPerfSSr4</t>
+  </si>
+  <si>
+    <t>50, 66, 118, 130, 132, 137, 179, 183, 188, 201, 281, 286, 300, 302, 315, 316</t>
+  </si>
+  <si>
+    <t>10.090000000000003</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>47, 54, 62, 73, 74, 90, 96, 103, 112, 119, 120, 126, 175, 185, 186, 196, 197, 202, 203, 210, 214, 220, 227, 240, 273, 277, 290, 292, 293, 294, 295, 310, 314</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr5if
+  Q_Journey3Pr5c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c5, Q_JourneyPerfSSr5</t>
+  </si>
+  <si>
+    <t>105, 287, 299</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr6if
+  Q_Journey3Pr6c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c5, Q_JourneyPerfSSr6</t>
+  </si>
+  <si>
+    <t>48, 56, 95, 108, 186, 190, 198, 228, 229, 279, 311</t>
+  </si>
+  <si>
+    <t>4.590000000000003</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>50, 74, 79, 82, 86, 128, 130, 173, 179, 188, 204, 227, 305, 314, 317</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfSSr7if
+  Q_Journey3Pr7c5&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c5, Q_JourneyPerfSSr7</t>
+  </si>
+  <si>
+    <t>3.6700000000000017</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>66, 77, 100, 130, 176, 192, 201, 212, 234, 296, 315, 320</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr1if Q_Journey3Pr1c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr1c6, Q_JourneyPerfICr1</t>
+  </si>
+  <si>
+    <t>77, 207, 209</t>
+  </si>
+  <si>
+    <t>87, 123, 177, 200, 293, 324</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr2if
+  Q_Journey3Pr2c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c6, Q_JourneyPerfICr2</t>
+  </si>
+  <si>
+    <t>65, 83, 89</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr3if
+  Q_Journey3Pr3c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c6, Q_JourneyPerfICr3</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>4.280000000000001</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>47, 53, 56, 59, 65, 72, 89, 99, 177, 196, 233, 293, 308, 315</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr4if
+  Q_Journey3Pr4c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c6, Q_JourneyPerfICr4</t>
+  </si>
+  <si>
+    <t>47, 53, 56, 59, 69, 77, 83, 87, 90, 109, 114, 123, 129, 134, 175, 177, 183, 196, 200, 207, 209, 220, 227, 277, 293, 295, 303, 309</t>
+  </si>
+  <si>
+    <t>62, 74, 75, 92, 97, 103, 106, 180, 186, 199, 234, 281, 305, 319</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr5if
+  Q_Journey3Pr5c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c6, Q_JourneyPerfICr5</t>
+  </si>
+  <si>
+    <t>109, 134, 220</t>
+  </si>
+  <si>
+    <t>65, 123, 196</t>
+  </si>
+  <si>
+    <t>ask Q_JourneyPerfICr7if
+  Q_Journey3Pr7c6&gt;0</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c6, Q_JourneyPerfICr7</t>
+  </si>
+  <si>
+    <t>69, 123, 129, 134, 183, 200, 277, 324</t>
+  </si>
+  <si>
+    <t>only show if r7 NOT selected in S_SFProduct</t>
+  </si>
+  <si>
+    <t>S_SFProductr7, Q_AFDCInterestr1</t>
+  </si>
+  <si>
+    <t>83, 98, 110, 277</t>
+  </si>
+  <si>
+    <t>49, 130, 274</t>
+  </si>
+  <si>
+    <t>only show if r8 NOT selected in S_SFProduct</t>
+  </si>
+  <si>
+    <t>S_SFProductr8, Q_AFDCInterestr2</t>
+  </si>
+  <si>
+    <t>176, 182, 189, 192, 214, 223, 232</t>
+  </si>
+  <si>
+    <t>230, 326</t>
+  </si>
+  <si>
+    <t>ask if S_ServicesUsedr4=1</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr4, Q_MethodGC</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>ask if S_ServicesUsedr5=1</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr5, Q_MethodSS</t>
+  </si>
+  <si>
+    <t>89, 117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base: r1-r3 selected in Q_SPUsed (aware of org’s SuccessPlan)]   </t>
+  </si>
+  <si>
+    <t>Q_SPUsed, Q_SPFeaturesr1, Q_SPFeaturesr2, Q_SPFeaturesr3, Q_SPFeaturesr4, Q_SPFeaturesr5, Q_SPFeaturesr6, Q_SPFeaturesr7, Q_SPFeaturesr8, Q_SPFeaturesr9, Q_SPFeaturesr10, Q_SPFeaturesr11, Q_SPFeaturesr12, Q_SPFeaturesr13, Q_SPFeaturesr14, Q_SPFeaturesr15, Q_SPFeaturesr16, Q_SPFeaturesr17, Q_SPFeaturesr18</t>
+  </si>
+  <si>
+    <t>59, 83, 92, 174, 316</t>
+  </si>
+  <si>
+    <t>Base: r17 or r18 NOT selected in Q_SPFeatures (used SP features)</t>
+  </si>
+  <si>
+    <t>Q_SPFeaturesr17, Q_SPValuer1, Q_SPValuer2, Q_SPValuer3, Q_SPValuer4, Q_SPValuer5, Q_SPValuer6, Q_SPValuer7, Q_SPValuer8, Q_SPValuer9, Q_SPValuer10, Q_SPValuer11, Q_SPValuer12, Q_SPValuer13, Q_SPValuer14, Q_SPValuer15, Q_SPValuer16</t>
+  </si>
+  <si>
+    <t>Q_SPFeaturesr18, Q_SPValuer1, Q_SPValuer2, Q_SPValuer3, Q_SPValuer4, Q_SPValuer5, Q_SPValuer6, Q_SPValuer7, Q_SPValuer8, Q_SPValuer9, Q_SPValuer10, Q_SPValuer11, Q_SPValuer12, Q_SPValuer13, Q_SPValuer14, Q_SPValuer15, Q_SPValuer16</t>
+  </si>
+  <si>
+    <t>Q_SPUsed, Q_SPUsersr1, Q_SPUsersr2, Q_SPUsersr3, Q_SPUsersr4, Q_SPUsersr5, Q_SPUsersr6, Q_SPUsersr7, Q_SPUsersr8, Q_SPUsersr9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Base: selected r4 in S_ServicesUsed (used Global Consulting)]  Show Q_Journey3P rows where at least 1% was entered in c4    </t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr4, Q_JourneyPerfGCr1, Q_JourneyPerfGCr2, Q_JourneyPerfGCr3, Q_JourneyPerfGCr4, Q_JourneyPerfGCr5, Q_JourneyPerfGCr6, Q_JourneyPerfGCr7</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base: selected r5 in S_ServicesUsed (used Small Specialists)] </t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr5, Q_JourneyPerfSSr1, Q_JourneyPerfSSr2, Q_JourneyPerfSSr3, Q_JourneyPerfSSr4, Q_JourneyPerfSSr5, Q_JourneyPerfSSr6, Q_JourneyPerfSSr7</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>[Base: selected r6 in S_ServicesUsed (used Independent Contractors)]</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr6, Q_JourneyPerfICr1, Q_JourneyPerfICr2, Q_JourneyPerfICr3, Q_JourneyPerfICr4, Q_JourneyPerfICr5, Q_JourneyPerfICr6, Q_JourneyPerfICr7</t>
+  </si>
+  <si>
+    <t>65, 89, 105, 112, 202, 233</t>
+  </si>
+  <si>
+    <t>Only show if c5 selected in S_SFStage</t>
+  </si>
+  <si>
+    <t>S_SFStage1r5, Q_Journey3Pr5c1, Q_Journey3Pr5c2, Q_Journey3Pr5c3, Q_Journey3Pr5c4, Q_Journey3Pr5c5, Q_Journey3Pr5c6</t>
+  </si>
+  <si>
+    <t>211, 239, 299</t>
+  </si>
+  <si>
+    <t>Piping</t>
+  </si>
+  <si>
+    <t>Number of columns mismatch between ['S_SFTimingr1', 'S_SFTimingr2', 'S_SFTimingr3', 'S_SFTimingr4', 'S_SFTimingr5', 'S_SFTimingr6', 'S_SFTimingr7', 'S_SFTimingr8'] and ['S_SFInvolvementr1', 'S_SFInvolvementr2', 'S_SFInvolvementr3', 'S_SFInvolvementr4', 'S_SFInvolvementr5', 'S_SFInvolvementr6', 'S_SFInvolvementr7', 'S_SFInvolvementr8', 'S_SFInvolvementr9'].</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Parallel Piping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base: Multiple rows selected in S_ServicesUsed. If one row selected, fill 100% in all rows for that column   </t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr1, S_ServicesUsedr2, S_ServicesUsedr3, S_ServicesUsedr4, S_ServicesUsedr5, S_ServicesUsedr6, Q_Journey3Pr4c1, Q_Journey3Pr4c2, Q_Journey3Pr4c3, Q_Journey3Pr4c4, Q_Journey3Pr4c5, Q_Journey3Pr4c6</t>
+  </si>
+  <si>
+    <t>17.430000000000007</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>49, 63, 118, 123, 179, 183, 302, 47, 54, 58, 59, 62, 68, 73, 89, 90, 91, 96, 103, 112, 117, 119, 126, 174, 185, 193, 196, 197, 202, 203, 210, 214, 220, 221, 273, 280, 290, 292, 293, 295, 310, 62, 74, 75, 92, 97, 103, 106, 122, 173, 180, 186, 199, 234, 281, 305, 319</t>
+  </si>
+  <si>
+    <t>25.989999999999995</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>47, 54, 58, 62, 68, 72, 75, 76, 92, 97, 99, 103, 117, 119, 121, 125, 127, 174, 175, 182, 193, 203, 230, 239, 283, 306, 310, 313, 319, 321, 50, 66, 79, 86, 105, 118, 130, 132, 179, 183, 188, 201, 284, 286, 287, 299, 300, 302, 312, 316, 47, 53, 56, 59, 65, 69, 77, 83, 87, 89, 90, 105, 109, 112, 114, 123, 129, 134, 175, 177, 183, 196, 200, 202, 207, 209, 220, 227, 233, 277, 284, 293, 295, 303, 309</t>
+  </si>
+  <si>
+    <t>Recodes/Hidden Variables</t>
+  </si>
+  <si>
+    <t>recode LicenseChoice and Hidden User</t>
+  </si>
+  <si>
+    <t>H_HiddenPipe, S_LicenseChoice, H_HiddenUserr2, H_HiddenUserr3</t>
+  </si>
+  <si>
+    <t>53.82</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 120, 121, 122, 123, 124, 125, 126, 127, 128, 129, 130, 131, 132, 133, 134, 135, 136, 137, 173, 174, 175, 176, 177, 178, 179, 180, 181, 182, 183, 184, 185, 186, 187, 188, 189, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 221, 222, 223, 224, 225, 226, 227, 228, 229, 230, 231, 232, 233, 234, 235, 236, 237, 238, 239, 240, 241, 242, 272, 274, 278, 281, 283, 284, 289, 293, 299, 305, 307, 318, 321, 324</t>
+  </si>
+  <si>
+    <t>recode final</t>
+  </si>
+  <si>
+    <t>hQuestions_Final, hQuestions_Eligibler1, hQuestions_Eligibler2, hQuestions_Eligibler3, hQuestions_Eligibler4</t>
+  </si>
+  <si>
+    <t>23.849999999999994</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>48, 53, 55, 56, 57, 58, 59, 64, 66, 69, 75, 77, 80, 82, 85, 89, 90, 93, 100, 103, 106, 109, 111, 113, 116, 118, 121, 123, 127, 130, 132, 137, 173, 174, 176, 177, 178, 182, 186, 189, 193, 196, 201, 204, 208, 212, 216, 220, 224, 228, 231, 235, 238, 241, 272, 274, 276, 278, 279, 283, 286, 289, 290, 293, 294, 297, 300, 302, 305, 307, 311, 312, 314, 316, 320, 321, 322, 324</t>
+  </si>
+  <si>
+    <t>recode hQuestionMethod_Finalr2</t>
+  </si>
+  <si>
+    <t>hQuestionMethod_Eligibler2, hQuestionMethod_Finalr2</t>
+  </si>
+  <si>
+    <t>recode hQuestionMethod_Finalr3</t>
+  </si>
+  <si>
+    <t>hQuestionMethod_Eligibler3, hQuestionMethod_Finalr3</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c2, Q_Journey3P_Sort_C2r2</t>
+  </si>
+  <si>
+    <t>52, 59, 89, 126, 210, 221, 240</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c2, Q_Journey3P_Sort_C2r3</t>
+  </si>
+  <si>
+    <t>13.150000000000006</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>52, 55, 62, 68, 71, 83, 85, 91, 95, 98, 112, 115, 121, 126, 127, 130, 133, 137, 180, 198, 202, 203, 204, 205, 210, 212, 216, 221, 229, 230, 233, 239, 272, 280, 292, 293, 300, 306, 311, 313, 319, 322, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c2, Q_Journey3P_Sort_C2r4</t>
+  </si>
+  <si>
+    <t>21.409999999999997</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>52, 54, 55, 57, 59, 62, 66, 69, 71, 73, 75, 81, 83, 85, 89, 91, 93, 95, 98, 102, 103, 107, 109, 112, 115, 117, 118, 121, 125, 126, 130, 133, 137, 174, 179, 180, 182, 183, 188, 191, 193, 196, 199, 202, 203, 212, 214, 221, 222, 226, 227, 230, 233, 234, 238, 239, 240, 272, 277, 280, 281, 289, 292, 293, 300, 302, 306, 311, 313, 316</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c2, Q_Journey3P_Sort_C2r5</t>
+  </si>
+  <si>
+    <t>10.700000000000003</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>52, 54, 55, 57, 62, 73, 78, 81, 91, 92, 100, 107, 115, 117, 125, 130, 182, 188, 191, 204, 214, 216, 227, 230, 233, 239, 272, 287, 292, 298, 300, 306, 316, 319, 322</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c2, Q_Journey3P_Sort_C2r6</t>
+  </si>
+  <si>
+    <t>52, 57, 66, 78, 80, 85, 95, 97, 102, 105, 107, 117, 121, 127, 135, 137, 174, 175, 180, 182, 188, 199, 204, 205, 209, 210, 212, 222, 226, 228, 230, 240, 272, 279, 280, 284, 289, 302, 306, 313, 315, 322, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C2r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c2, Q_Journey3P_Sort_C2r7</t>
+  </si>
+  <si>
+    <t>7.340000000000003</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>58, 69, 80, 89, 98, 109, 112, 117, 126, 127, 133, 178, 193, 196, 202, 203, 221, 228, 281, 289, 293, 298, 313, 319</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c3, Q_Journey3P_Sort_C3r2</t>
+  </si>
+  <si>
+    <t>51, 60, 79, 91, 122, 187, 190, 195, 210, 211, 215, 233, 280, 298, 301, 306</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c3, Q_Journey3P_Sort_C3r3</t>
+  </si>
+  <si>
+    <t>46, 49, 50, 51, 52, 60, 61, 63, 67, 70, 71, 73, 74, 76, 79, 87, 91, 95, 96, 98, 102, 104, 107, 108, 110, 112, 115, 122, 124, 126, 128, 129, 131, 134, 136, 184, 185, 187, 191, 198, 199, 202, 213, 214, 215, 217, 218, 219, 221, 223, 225, 226, 234, 236, 237, 239, 240, 280, 281, 285, 288, 292, 295, 296, 303, 304, 310, 317, 318, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c3, Q_Journey3P_Sort_C3r4</t>
+  </si>
+  <si>
+    <t>33.33</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>50, 51, 52, 54, 60, 62, 63, 65, 67, 71, 72, 73, 74, 76, 81, 83, 84, 86, 87, 91, 92, 94, 97, 98, 99, 101, 102, 104, 105, 107, 108, 110, 112, 115, 119, 120, 122, 124, 126, 128, 131, 133, 135, 136, 175, 179, 181, 183, 184, 185, 188, 190, 191, 192, 194, 195, 197, 198, 200, 202, 203, 205, 206, 207, 209, 210, 211, 213, 214, 215, 218, 219, 221, 222, 226, 229, 230, 232, 234, 239, 240, 242, 273, 275, 277, 280, 281, 282, 284, 285, 287, 291, 292, 295, 296, 298, 301, 303, 304, 306, 308, 309, 310, 313, 315, 317, 318, 323, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c3, Q_Journey3P_Sort_C3r5</t>
+  </si>
+  <si>
+    <t>14.370000000000005</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>47, 52, 62, 68, 70, 73, 84, 86, 88, 91, 97, 102, 110, 112, 115, 117, 126, 129, 134, 185, 191, 192, 194, 198, 199, 202, 207, 209, 214, 219, 230, 233, 236, 239, 271, 285, 287, 292, 296, 298, 301, 308, 313, 317, 318, 319, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c3, Q_Journey3P_Sort_C3r6</t>
+  </si>
+  <si>
+    <t>14.069999999999993</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>46, 47, 52, 67, 76, 78, 86, 95, 96, 99, 102, 104, 107, 108, 110, 119, 124, 131, 135, 179, 185, 188, 190, 194, 197, 199, 206, 213, 214, 215, 218, 221, 223, 226, 233, 234, 237, 240, 280, 281, 288, 291, 304, 306, 310, 315</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C3r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c3, Q_Journey3P_Sort_C3r7</t>
+  </si>
+  <si>
+    <t>7.950000000000003</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>49, 50, 54, 61, 81, 94, 96, 98, 117, 184, 195, 205, 210, 211, 213, 217, 226, 228, 232, 233, 275, 296, 299, 323, 325, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c4, Q_Journey3P_Sort_C4r2</t>
+  </si>
+  <si>
+    <t>46, 52, 72, 76, 79, 111, 117, 133, 217, 237, 288, 295, 298, 306, 321</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c4, Q_Journey3P_Sort_C4r3</t>
+  </si>
+  <si>
+    <t>46, 54, 62, 64, 71, 75, 79, 80, 84, 85, 96, 97, 104, 111, 113, 117, 121, 129, 133, 178, 180, 182, 193, 203, 206, 207, 213, 218, 226, 230, 235, 237, 273, 275, 276, 283, 288, 290, 294, 295, 298, 306, 310, 313, 319, 321, 323</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c4, Q_Journey3P_Sort_C4r4</t>
+  </si>
+  <si>
+    <t>21.709999999999994</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>46, 47, 49, 52, 54, 58, 62, 64, 68, 71, 72, 75, 76, 79, 80, 84, 85, 88, 92, 94, 96, 97, 99, 103, 104, 105, 107, 111, 117, 118, 119, 121, 123, 125, 127, 129, 174, 178, 180, 182, 183, 187, 193, 194, 199, 203, 207, 209, 217, 218, 219, 222, 225, 226, 233, 237, 239, 273, 275, 276, 283, 284, 288, 290, 295, 302, 306, 310, 313, 319, 321</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c4, Q_Journey3P_Sort_C4r5</t>
+  </si>
+  <si>
+    <t>49, 52, 54, 58, 63, 64, 68, 79, 88, 92, 97, 107, 117, 118, 119, 121, 123, 179, 180, 182, 183, 187, 199, 206, 207, 209, 213, 219, 225, 226, 230, 233, 235, 237, 239, 274, 276, 284, 288, 294, 295, 298, 302, 307, 313, 319</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c4, Q_Journey3P_Sort_C4r6</t>
+  </si>
+  <si>
+    <t>46, 47, 52, 64, 71, 79, 80, 84, 85, 96, 99, 104, 111, 113, 119, 121, 127, 131, 135, 178, 182, 194, 199, 209, 213, 218, 226, 233, 235, 237, 273, 275, 276, 283, 284, 288, 290, 295, 304, 306, 310, 315, 321, 323</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C4r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c4, Q_Journey3P_Sort_C4r7</t>
+  </si>
+  <si>
+    <t>75, 76, 94, 111, 121, 133, 193, 222, 233, 283, 306, 321</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c5, Q_Journey3P_Sort_C5r2</t>
+  </si>
+  <si>
+    <t>57, 63, 70, 93, 122, 137, 186, 238, 278, 281, 287, 300, 322</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c5, Q_Journey3P_Sort_C5r3</t>
+  </si>
+  <si>
+    <t>15.900000000000006</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>50, 56, 57, 63, 70, 74, 77, 81, 82, 93, 95, 98, 100, 106, 115, 116, 128, 132, 173, 176, 179, 186, 188, 190, 191, 192, 195, 198, 201, 208, 212, 216, 224, 272, 278, 281, 283, 286, 287, 289, 296, 297, 299, 300, 305, 312, 316, 317, 320, 322, 325, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c5, Q_Journey3P_Sort_C5r4</t>
+  </si>
+  <si>
+    <t>22.939999999999998</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>50, 55, 56, 57, 63, 66, 70, 73, 74, 77, 79, 82, 93, 95, 96, 98, 100, 106, 108, 110, 115, 116, 118, 119, 122, 128, 130, 132, 134, 137, 173, 176, 179, 186, 188, 189, 191, 192, 195, 196, 201, 204, 208, 210, 212, 216, 227, 229, 234, 236, 238, 240, 272, 277, 281, 283, 286, 289, 290, 294, 295, 296, 299, 300, 302, 303, 305, 309, 310, 311, 312, 317, 320, 325, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c5, Q_Journey3P_Sort_C5r5</t>
+  </si>
+  <si>
+    <t>18.349999999999994</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>47, 48, 54, 55, 57, 62, 65, 70, 73, 79, 81, 87, 89, 90, 93, 96, 98, 100, 103, 105, 106, 112, 115, 116, 122, 126, 128, 130, 134, 137, 175, 179, 183, 185, 188, 190, 196, 197, 202, 203, 204, 210, 214, 216, 220, 227, 236, 273, 277, 278, 287, 289, 290, 293, 294, 299, 300, 310, 316, 320</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c5, Q_Journey3P_Sort_C5r6</t>
+  </si>
+  <si>
+    <t>14.980000000000004</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>48, 50, 61, 66, 74, 79, 81, 82, 86, 90, 95, 96, 106, 126, 128, 130, 173, 175, 176, 179, 185, 186, 188, 189, 191, 195, 196, 201, 204, 208, 214, 220, 228, 229, 236, 279, 281, 286, 289, 293, 296, 297, 302, 305, 310, 316, 317, 322, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C5r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c5, Q_Journey3P_Sort_C5r7</t>
+  </si>
+  <si>
+    <t>56, 61, 77, 93, 132, 173, 190, 228, 287, 305, 309, 311, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c6, Q_Journey3P_Sort_C6r2</t>
+  </si>
+  <si>
+    <t>77, 89, 90, 109, 177, 220, 293, 312</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c6, Q_Journey3P_Sort_C6r3</t>
+  </si>
+  <si>
+    <t>56, 69, 72, 77, 89, 90, 109, 129, 177, 196, 200, 207, 233, 241, 295, 308</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c6, Q_Journey3P_Sort_C6r4</t>
+  </si>
+  <si>
+    <t>11.010000000000005</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>53, 56, 59, 62, 65, 69, 72, 83, 87, 90, 94, 99, 103, 109, 114, 123, 129, 134, 177, 183, 196, 200, 207, 209, 220, 227, 231, 234, 241, 277, 281, 293, 295, 303, 308, 312</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c6, Q_Journey3P_Sort_C6r5</t>
+  </si>
+  <si>
+    <t>65, 90, 196, 209, 220</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c6, Q_Journey3P_Sort_C6r6</t>
+  </si>
+  <si>
+    <t>53, 59, 69, 72, 75, 83, 87, 90, 97, 106, 123, 129, 177, 186, 196, 207, 209, 220, 227, 231, 234, 241, 295, 305, 308, 309, 312, 319</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C6r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c6, Q_Journey3P_Sort_C6r7</t>
+  </si>
+  <si>
+    <t>65, 94, 109, 183, 277, 293, 315</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r2</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr2c1, Q_Journey3P_Sort_C1r2</t>
+  </si>
+  <si>
+    <t>51, 57, 77, 91, 173, 185, 199, 211, 224, 225, 297, 311, 318, 322</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r3</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr3c1, Q_Journey3P_Sort_C1r3</t>
+  </si>
+  <si>
+    <t>27.519999999999996</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>49, 51, 54, 57, 64, 68, 70, 71, 75, 77, 80, 82, 87, 88, 89, 90, 91, 92, 93, 95, 96, 97, 100, 107, 108, 109, 110, 112, 113, 114, 115, 116, 124, 126, 127, 129, 134, 137, 177, 178, 185, 186, 187, 188, 191, 192, 193, 198, 201, 202, 212, 215, 223, 224, 226, 229, 230, 231, 232, 235, 237, 238, 240, 272, 273, 276, 280, 283, 285, 286, 287, 291, 294, 295, 297, 300, 301, 303, 306, 308, 310, 312, 313, 316, 317, 318, 319, 322, 323, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r4</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr4c1, Q_Journey3P_Sort_C1r4</t>
+  </si>
+  <si>
+    <t>38.23</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>47, 49, 50, 51, 52, 53, 55, 56, 57, 60, 61, 64, 65, 68, 71, 72, 74, 75, 77, 78, 79, 80, 82, 83, 85, 86, 87, 88, 89, 90, 91, 92, 93, 95, 96, 97, 100, 102, 104, 106, 107, 109, 110, 111, 113, 115, 124, 126, 128, 131, 134, 137, 173, 176, 177, 178, 179, 183, 184, 185, 186, 187, 191, 192, 193, 195, 196, 197, 198, 199, 200, 202, 204, 205, 206, 207, 211, 212, 214, 215, 216, 218, 220, 223, 225, 226, 230, 231, 233, 236, 237, 238, 239, 272, 273, 276, 280, 283, 285, 286, 289, 290, 292, 293, 294, 295, 297, 300, 301, 303, 304, 305, 306, 308, 309, 310, 311, 312, 313, 317, 318, 321, 322, 323, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r5</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr5c1, Q_Journey3P_Sort_C1r5</t>
+  </si>
+  <si>
+    <t>29.049999999999997</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>47, 51, 52, 54, 56, 57, 59, 60, 65, 67, 68, 71, 74, 75, 79, 80, 81, 82, 85, 86, 87, 90, 91, 92, 97, 100, 104, 105, 106, 110, 112, 115, 116, 117, 121, 122, 123, 124, 127, 134, 136, 137, 175, 179, 180, 183, 184, 185, 186, 191, 196, 198, 200, 202, 205, 206, 209, 213, 214, 216, 219, 220, 223, 229, 230, 231, 232, 235, 236, 237, 239, 240, 272, 273, 274, 276, 278, 285, 286, 287, 291, 294, 295, 298, 299, 300, 304, 306, 310, 316, 317, 319, 322, 323, 326</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r6</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr6c1, Q_Journey3P_Sort_C1r6</t>
+  </si>
+  <si>
+    <t>28.75</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>46, 47, 50, 52, 53, 55, 58, 61, 63, 64, 71, 74, 77, 78, 79, 80, 82, 86, 87, 88, 91, 95, 96, 99, 104, 105, 107, 108, 109, 110, 111, 112, 113, 114, 119, 121, 125, 126, 127, 128, 130, 137, 173, 175, 176, 178, 179, 182, 185, 187, 188, 192, 193, 194, 195, 197, 202, 204, 209, 213, 220, 225, 226, 232, 233, 235, 237, 238, 240, 272, 276, 278, 280, 283, 287, 289, 292, 295, 297, 300, 303, 305, 306, 309, 310, 311, 312, 315, 316, 317, 318, 321, 322, 325</t>
+  </si>
+  <si>
+    <t>recode Q_Journey3P_Sort_C1r7</t>
+  </si>
+  <si>
+    <t>Q_Journey3Pr7c1, Q_Journey3P_Sort_C1r7</t>
+  </si>
+  <si>
+    <t>11.310000000000002</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>54, 64, 65, 69, 81, 87, 96, 107, 114, 117, 123, 128, 131, 132, 183, 188, 195, 201, 209, 214, 215, 219, 221, 224, 226, 271, 275, 277, 281, 283, 293, 308, 309, 313, 315, 320, 326</t>
+  </si>
+  <si>
+    <t>Selection Limit Control</t>
+  </si>
+  <si>
+    <t>Minimum and/or maximum limits on the number of choices a respondent can select.</t>
+  </si>
+  <si>
+    <t>S_ServicesUsedr3, S_ServicesUsedr4, S_ServicesUsedr5, S_ServicesUsedr6</t>
+  </si>
+  <si>
+    <t>52.29</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>1, 3, 6, 7, 8, 10, 11, 12, 15, 16, 18, 19, 21, 22, 24, 25, 27, 29, 32, 33, 34, 37, 38, 39, 40, 42, 46, 47, 50, 52, 54, 56, 61, 62, 63, 65, 68, 70, 71, 72, 74, 76, 77, 79, 81, 83, 84, 86, 87, 88, 92, 94, 95, 96, 97, 98, 99, 104, 105, 107, 108, 110, 112, 114, 115, 117, 119, 120, 122, 124, 125, 128, 129, 131, 133, 134, 135, 140, 141, 143, 144, 146, 149, 151, 152, 153, 158, 159, 160, 161, 163, 168, 170, 171, 175, 179, 180, 183, 187, 188, 190, 191, 192, 194, 195, 198, 199, 200, 202, 203, 206, 207, 209, 213, 217, 218, 219, 222, 225, 226, 227, 229, 230, 233, 234, 236, 237, 239, 240, 243, 247, 249, 250, 251, 252, 253, 260, 263, 264, 267, 268, 269, 270, 271, 273, 275, 277, 281, 283, 284, 287, 288, 294, 295, 296, 298, 299, 303, 304, 306, 308, 309, 310, 312, 313, 315, 317, 319, 323, 325, 326</t>
+  </si>
+  <si>
+    <t>Number of rows affected: 275</t>
+  </si>
+  <si>
+    <t>Percentage of rows affected: 84.1</t>
   </si>
 </sst>
 </file>
@@ -481,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -564,35 +1645,2530 @@
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="30" customHeight="1">
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="30" customHeight="1">
+      <c r="B12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="30" customHeight="1">
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="30" customHeight="1">
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="30" customHeight="1">
+      <c r="B15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="30" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="30" customHeight="1">
+      <c r="B17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="30" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="30" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="30" customHeight="1">
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="30" customHeight="1">
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="30" customHeight="1">
+      <c r="B22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="30" customHeight="1">
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="30" customHeight="1">
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="30" customHeight="1">
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="30" customHeight="1">
+      <c r="B26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="30" customHeight="1">
+      <c r="B27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="30" customHeight="1">
+      <c r="B28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="30" customHeight="1">
+      <c r="B29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="30" customHeight="1">
+      <c r="B30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="30" customHeight="1">
+      <c r="B31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="30" customHeight="1">
+      <c r="B32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="30" customHeight="1">
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="30" customHeight="1">
+      <c r="B34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="30" customHeight="1">
+      <c r="B35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="30" customHeight="1">
+      <c r="B36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="30" customHeight="1">
+      <c r="B37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" ht="30" customHeight="1">
+      <c r="B38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="30" customHeight="1">
+      <c r="B39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="30" customHeight="1">
+      <c r="B40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="30" customHeight="1">
+      <c r="B41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="30" customHeight="1">
+      <c r="B42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" ht="30" customHeight="1">
+      <c r="B43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="30" customHeight="1">
+      <c r="B44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="30" customHeight="1">
+      <c r="B45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="30" customHeight="1">
+      <c r="B46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="30" customHeight="1">
+      <c r="B47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="30" customHeight="1">
+      <c r="B48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="30" customHeight="1">
+      <c r="B49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="30" customHeight="1">
+      <c r="B50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="30" customHeight="1">
+      <c r="B51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="30" customHeight="1">
+      <c r="B52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="30" customHeight="1">
+      <c r="B53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="30" customHeight="1">
+      <c r="B54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="30" customHeight="1">
+      <c r="B55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="30" customHeight="1">
+      <c r="B56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="30" customHeight="1">
+      <c r="B57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="30" customHeight="1">
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="30" customHeight="1">
+      <c r="B59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="30" customHeight="1">
+      <c r="B60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="F13" s="5" t="s">
+      <c r="F60" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="30" customHeight="1">
+      <c r="B61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="30" customHeight="1">
+      <c r="B62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="30" customHeight="1">
+      <c r="B63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="30" customHeight="1">
+      <c r="B64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="20" customHeight="1">
+      <c r="B65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="20" customHeight="1">
+      <c r="B66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="165" customHeight="1">
+      <c r="B67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="120" customHeight="1">
+      <c r="B68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="120" customHeight="1">
+      <c r="B69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="75" customHeight="1">
+      <c r="B70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="75" customHeight="1">
+      <c r="B71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="75" customHeight="1">
+      <c r="B72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="75" customHeight="1">
+      <c r="B73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="60" customHeight="1">
+      <c r="B74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" ht="180" customHeight="1">
+      <c r="B75" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" ht="180" customHeight="1">
+      <c r="B76" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="105" customHeight="1">
+      <c r="B77" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="105" customHeight="1">
+      <c r="B78" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="45" customHeight="1">
+      <c r="B79" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" ht="60" customHeight="1">
+      <c r="B80" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" ht="30" customHeight="1">
+      <c r="B81" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" ht="30" customHeight="1">
+      <c r="B82" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="30" customHeight="1">
+      <c r="B83" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="30" customHeight="1">
+      <c r="B84" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="30" customHeight="1">
+      <c r="B85" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="30" customHeight="1">
+      <c r="B86" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" ht="30" customHeight="1">
+      <c r="B87" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" ht="30" customHeight="1">
+      <c r="B88" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" ht="30" customHeight="1">
+      <c r="B89" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" ht="30" customHeight="1">
+      <c r="B90" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" ht="30" customHeight="1">
+      <c r="B91" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" ht="30" customHeight="1">
+      <c r="B92" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" ht="30" customHeight="1">
+      <c r="B93" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" ht="30" customHeight="1">
+      <c r="B94" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="30" customHeight="1">
+      <c r="B95" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" ht="30" customHeight="1">
+      <c r="B96" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" ht="30" customHeight="1">
+      <c r="B97" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" ht="30" customHeight="1">
+      <c r="B98" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" ht="30" customHeight="1">
+      <c r="B99" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" ht="30" customHeight="1">
+      <c r="B100" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" ht="30" customHeight="1">
+      <c r="B101" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" ht="30" customHeight="1">
+      <c r="B102" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="30" customHeight="1">
+      <c r="B103" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="30" customHeight="1">
+      <c r="B104" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" ht="30" customHeight="1">
+      <c r="B105" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" ht="30" customHeight="1">
+      <c r="B106" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" ht="30" customHeight="1">
+      <c r="B107" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" ht="30" customHeight="1">
+      <c r="B108" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" ht="30" customHeight="1">
+      <c r="B109" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" ht="30" customHeight="1">
+      <c r="B110" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" ht="30" customHeight="1">
+      <c r="B111" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" ht="30" customHeight="1">
+      <c r="B112" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" ht="30" customHeight="1">
+      <c r="B113" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" ht="30" customHeight="1">
+      <c r="B114" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" ht="30" customHeight="1">
+      <c r="B115" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" ht="30" customHeight="1">
+      <c r="B116" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" ht="30" customHeight="1">
+      <c r="B117" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" ht="30" customHeight="1">
+      <c r="B118" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" ht="45" customHeight="1">
+      <c r="B119" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8">
+      <c r="F121" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8">
+      <c r="F122" s="5" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/template.xlsx
+++ b/outputs/template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="282">
   <si>
     <t>Logic Attainement</t>
   </si>
@@ -511,13 +511,13 @@
     <t>SK12_6, SK12_13, SK12_15, SK12_18, SK12_22, SK12_27, SK12_41, SK12_43, SK12_45, SK12_46, SK12_49, SK12_65, SK12_68, SK12_77, SK12_78, SK12_84, SK12_102, SK12_108, SK12_116, SK12_119, SK12_120, SK12_122, SK12_131, SK12_146, SK12_148, SK12_155, SK12_161, SK12_201, SK12_205, SK12_206, SK12_210, SK12_213, SK12_217, SK12_226, SK12_237, SK12_239, SK12_245, SK12_265, SK12_298, SK12_306, SK12_315, SK12_321, SK12_323, SK12_333, SK12_335, SK12_353, SK12_371, SK12_378, SK12_381, SK12_431, SK17_6, SK17_13, SK17_15, SK17_18, SK17_22, SK17_27, SK17_41, SK17_43, SK17_45, SK17_46, SK17_49, SK17_65, SK17_68, SK17_77, SK17_78, SK17_84, SK17_102, SK17_108, SK17_116, SK17_119, SK17_120, SK17_122, SK17_131, SK17_146, SK17_148, SK17_155, SK17_161, SK17_201, SK17_205, SK17_206, SK17_210, SK17_213, SK17_217, SK17_226, SK17_237, SK17_239, SK17_245, SK17_265, SK17_298, SK17_306, SK17_315, SK17_321, SK17_323, SK17_333, SK17_335, SK17_353, SK17_371, SK17_378, SK17_381, SK17_431</t>
   </si>
   <si>
-    <t>234.51</t>
-  </si>
-  <si>
-    <t>12131</t>
-  </si>
-  <si>
-    <t>13, 15, 20, 28, 32, 33, 45, 48, 70, 76, 94, 104, 105, 117, 121, 131, 136, 139, 153, 155, 163, 164, 173, 175, 186, 188, 203, 205, 216, 232, 235, 236, 240, 248, 250, 252, 256, 260, 263, 272, 277, 285, 286, 289, 291, 304, 316, 326, 328, 330, 332, 336, 340, 351, 361, 371, 375, 380, 382, 384, 388, 399, 402, 405, 409, 419, 420, 425, 431, 436, 439, 440, 441, 445, 453, 458, 483, 485, 500, 512, 514, 530, 535, 541, 542, 558, 561, 577, 583, 584, 594, 597, 599, 605, 607, 618, 629, 636, 647, 649, 650, 656, 660, 668, 675, 676, 684, 686, 690, 701, 703, 712, 715, 721, 724, 725, 729, 732, 743, 754, 760, 762, 763, 774, 776, 784, 787, 788, 790, 804, 830, 839, 840, 841, 863, 866, 877, 881, 889, 905, 911, 919, 920, 941, 942, 954, 964, 965, 976, 977, 1004, 1007, 1011, 1016, 1030, 1031, 1050, 1053, 1054, 1056, 1066, 1080, 1082, 1083, 1087, 1096, 1105, 1110, 1112, 1116, 1119, 1145, 1154, 1159, 1164, 1165, 1170, 1180, 1186, 1191, 1194, 1197, 1207, 1220, 1222, 1223, 1235, 1240, 1246, 1248, 1249, 1262, 1263, 1264, 1267, 1269, 1276, 1288, 1298, 1301, 1302, 1315, 1326, 1332, 1351, 1354, 1368, 1371, 1389, 1397, 1401, 1413, 1417, 1420, 1431, 1439, 1443, 1446, 1447, 1455, 1459, 1461, 1463, 1464, 1467, 1472, 1491, 1494, 1495, 1496, 1499, 1522, 1534, 1552, 1569, 1581, 1583, 1588, 1595, 1613, 1625, 1628, 1630, 1634, 1636, 1643, 1647, 1654, 1657, 1675, 1677, 1680, 1697, 1705, 1708, 1716, 1717, 1719, 1726, 1737, 1747, 1748, 1759, 1767, 1770, 1772, 1781, 1783, 1787, 1798, 1807, 1808, 1810, 1814, 1815, 1822, 1832, 1838, 1839, 1844, 1848, 1852, 1854, 1859, 1868, 1877, 1878, 1883, 1884, 1888, 1889, 1891, 1892, 1896, 1903, 1904, 1905, 1906, 1911, 1912, 1915, 1916, 1918, 1919, 1922, 1928, 1933, 1938, 1943, 1955, 1968, 1980, 1981, 1986, 1993, 1995, 1996, 2003, 2007, 2008, 2026, 2027, 2029, 2030, 2032, 2048, 2050, 2063, 2068, 2070, 2073, 2079, 2097, 2106, 2107, 2112, 2116, 2121, 2124, 2125, 2126, 2131, 2133, 2137, 2139, 2163, 2165, 2166, 2168, 2175, 2178, 2181, 2185, 2187, 2191, 2192, 2223, 2229, 2241, 2256, 2261, 2262, 2265, 2266, 2269, 2273, 2276, 2279, 2282, 2284, 2291, 2292, 2297, 2298, 2313, 2315, 2316, 2319, 2320, 2322, 2323, 2324, 2328, 2332, 2334, 2337, 2338, 2340, 2341, 2347, 2354, 2355, 2356, 2368, 2372, 2374, 2375, 2376, 2383, 2385, 2397, 2404, 2406, 2411, 2412, 2416, 2433, 2463, 2471, 2476, 2478, 2483, 2485, 2499, 2500, 2502, 2503, 2504, 2505, 2507, 2545, 2551, 2552, 2556, 2560, 2562, 2567, 2568, 2572, 2589, 2593, 2597, 2601, 2615, 2617, 2624, 2627, 2642, 2659, 2660, 2672, 2678, 2683, 2686, 2690, 2693, 2696, 2701, 2706, 2710, 2748, 2753, 2771, 2772, 2780, 2801, 2804, 2813, 2814, 2815, 2819, 2821, 2825, 2828, 2833, 2837, 2843, 2847, 2857, 2863, 2868, 2874, 2878, 2882, 2888, 2902, 2911, 2917, 2931, 2935, 2948, 2953, 2955, 2956, 2964, 2979, 2983, 2985, 2986, 2987, 2988, 2993, 3025, 3032, 3040, 3043, 3051, 3054, 3071, 3072, 3079, 3085, 3095, 3102, 3105, 3109, 3113, 3121, 3126, 3127, 3130, 3135, 3136, 3155, 3167, 3172, 3174, 3175, 3177, 3178, 3181, 3185, 3194, 3195, 3197, 3200, 3208, 3216, 3219, 3220, 3223, 3228, 3232, 3233, 3236, 3246, 3249, 3253, 3263, 3280, 3293, 3302, 3307, 3314, 3326, 3332, 3333, 3335, 3346, 3350, 3352, 3353, 3359, 3360, 3366, 3367, 3371, 3377, 3378, 3382, 3399, 3404, 3410, 3414, 3416, 3425, 3428, 3435, 3438, 3442, 3452, 3458, 3461, 3463, 3465, 3487, 3502, 3519, 3521, 3530, 3540, 3542, 3561, 3569, 3582, 3586, 3590, 3595, 3597, 3603, 3608, 3618, 3621, 3622, 3629, 3632, 3633, 3641, 3649, 3659, 3661, 3663, 3665, 3666, 3677, 3679, 3686, 3687, 3689, 3694, 3701, 3710, 3720, 3721, 3725, 3728, 3733, 3734, 3743, 3760, 3769, 3783, 3785, 3786, 3801, 3803, 3819, 3827, 3829, 3834, 3851, 3858, 3859, 3860, 3864, 3867, 3876, 3877, 3885, 3894, 3895, 3909, 3912, 3914, 3915, 3917, 3921, 3925, 3927, 3933, 3936, 3945, 3952, 3955, 3980, 3987, 4003, 4018, 4021, 4024, 4026, 4038, 4051, 4057, 4058, 4064, 4066, 4067, 4076, 4084, 4088, 4092, 4096, 4114, 4117, 4120, 4123, 4139, 4142, 4145, 4151, 4152, 4159, 4162, 4169, 4180, 4184, 4185, 4186, 4193, 4198, 4209, 4216, 4219, 4237, 4243, 4250, 4251, 4263, 4265, 4272, 4273, 4282, 4289, 4329, 4331, 4333, 4338, 4339, 4345, 4346, 4347, 4352, 4354, 4355, 4356, 4373, 4388, 4389, 4393, 4396, 4408, 4410, 4415, 4430, 4433, 4436, 4439, 4449, 4451, 4455, 4458, 4468, 4491, 4501, 4505, 4514, 4515, 4527, 4534, 4538, 4540, 4542, 4544, 4555, 4558, 4560, 4564, 4565, 4569, 4573, 4579, 4583, 4593, 4597, 4602, 4613, 4618, 4624, 4626, 4628, 4632, 4633, 4636, 4637, 4638, 4645, 4656, 4667, 4672, 4679, 4681, 4682, 4693, 4699, 4721, 4729, 4732, 4734, 4736, 4758, 4759, 4765, 4778, 4779, 4780, 4782, 4785, 4787, 4792, 4797, 4799, 4803, 4828, 4832, 4841, 4856, 4884, 4892, 4925, 4936, 4947, 4953, 4956, 4957, 4964, 4965, 4971, 4974, 4979, 4980, 4989, 5007, 5008, 5014, 5018, 5020, 5033, 5037, 5042, 5055, 5063, 5075, 5076, 5079, 5081, 5084, 5085, 5087, 5089, 5097, 5102, 5107, 5111, 5113, 5115, 5126, 5129, 5149, 5150, 5158, 5160, 5163, 5167, 15, 26, 28, 38, 56, 62, 79, 104, 106, 121, 123, 125, 171, 174, 175, 260, 278, 320, 394, 432, 433, 487, 512, 536, 538, 543, 562, 581, 590, 605, 633, 644, 666, 688, 725, 735, 748, 763, 793, 804, 815, 866, 905, 913, 925, 926, 933, 987, 990, 1053, 1106, 1123, 1138, 1145, 1196, 1218, 1225, 1255, 1256, 1265, 1293, 1307, 1337, 1356, 1364, 1378, 1419, 1422, 1450, 1494, 1529, 1549, 1628, 1633, 1649, 1659, 1683, 1686, 1744, 1747, 1765, 1774, 1778, 1788, 1809, 1822, 1826, 1843, 1849, 1859, 1880, 1894, 1907, 1910, 1996, 2049, 2058, 2062, 2115, 2155, 2198, 2236, 2282, 2296, 2305, 2336, 2346, 2350, 2385, 2426, 2516, 2557, 2610, 2644, 2660, 2709, 2725, 2748, 2821, 2873, 2902, 2912, 2938, 2946, 2964, 2984, 2997, 3020, 3034, 3035, 3051, 3065, 3068, 3083, 3089, 3154, 3168, 3200, 3207, 3223, 3236, 3273, 3292, 3325, 3335, 3370, 3371, 3387, 3404, 3414, 3423, 3451, 3513, 3521, 3587, 3595, 3598, 3608, 3619, 3637, 3646, 3653, 3667, 3675, 3739, 3752, 3758, 3774, 3775, 3829, 3862, 3904, 3914, 3915, 3921, 3928, 3934, 3948, 3967, 3990, 4005, 4038, 4049, 4061, 4094, 4107, 4114, 4157, 4179, 4202, 4220, 4222, 4259, 4264, 4270, 4274, 4288, 4312, 4337, 4351, 4393, 4424, 4426, 4449, 4479, 4506, 4540, 4550, 4555, 4564, 4569, 4590, 4619, 4630, 4635, 4640, 4654, 4656, 4672, 4710, 4711, 4723, 4740, 4745, 4927, 4929, 4952, 4989, 5037, 5042, 5065, 5082, 5112, 5143, 5144, 5148, 1, 8, 13, 15, 24, 25, 31, 32, 37, 38, 43, 68, 75, 76, 79, 85, 86, 87, 94, 103, 111, 113, 126, 128, 130, 131, 133, 135, 139, 143, 145, 154, 155, 166, 171, 172, 173, 174, 178, 185, 188, 198, 203, 206, 212, 221, 250, 252, 256, 265, 271, 272, 277, 279, 285, 286, 296, 301, 311, 326, 327, 336, 337, 340, 349, 350, 352, 361, 365, 380, 386, 405, 406, 410, 424, 425, 432, 436, 439, 441, 445, 451, 454, 460, 469, 473, 476, 477, 480, 484, 485, 490, 504, 506, 512, 514, 515, 520, 521, 524, 526, 528, 539, 541, 542, 545, 547, 555, 558, 563, 566, 570, 574, 577, 581, 588, 594, 598, 604, 615, 623, 627, 629, 640, 660, 672, 675, 679, 681, 686, 700, 707, 717, 724, 728, 731, 732, 736, 741, 754, 759, 760, 767, 768, 771, 774, 776, 784, 787, 790, 796, 823, 826, 827, 829, 831, 837, 840, 841, 842, 844, 851, 856, 860, 862, 863, 868, 873, 877, 881, 885, 890, 897, 899, 900, 914, 915, 925, 930, 941, 950, 956, 960, 964, 965, 971, 974, 977, 979, 983, 987, 988, 998, 1003, 1004, 1039, 1044, 1045, 1054, 1062, 1081, 1082, 1087, 1090, 1111, 1112, 1116, 1135, 1138, 1142, 1148, 1156, 1164, 1168, 1172, 1182, 1185, 1186, 1207, 1208, 1214, 1215, 1219, 1223, 1224, 1230, 1239, 1241, 1243, 1246, 1248, 1252, 1255, 1256, 1259, 1262, 1263, 1276, 1301, 1312, 1320, 1324, 1337, 1342, 1351, 1353, 1363, 1366, 1367, 1375, 1386, 1388, 1389, 1394, 1397, 1401, 1403, 1410, 1413, 1417, 1426, 1428, 1439, 1444, 1446, 1447, 1449, 1455, 1459, 1463, 1464, 1475, 1483, 1493, 1494, 1495, 1498, 1499, 1504, 1510, 1519, 1520, 1528, 1534, 1540, 1541, 1544, 1552, 1558, 1569, 1572, 1574, 1581, 1583, 1596, 1601, 1603, 1608, 1618, 1623, 1625, 1630, 1636, 1639, 1644, 1646, 1649, 1655, 1656, 1660, 1665, 1666, 1670, 1675, 1676, 1677, 1680, 1681, 1682, 1683, 1693, 1698, 1708, 1711, 1717, 1722, 1727, 1730, 1737, 1742, 1749, 1752, 1757, 1759, 1762, 1767, 1772, 1776, 1779, 1782, 1787, 1792, 1797, 1805, 1806, 1808, 1816, 1844, 1849, 1854, 1857, 1864, 1867, 1868, 1871, 1873, 1877, 1884, 1889, 1890, 1892, 1896, 1904, 1906, 1912, 1917, 1921, 1922, 1924, 1930, 1934, 1937, 1944, 1954, 1958, 1962, 1975, 1976, 1980, 1981, 1990, 1993, 1996, 2008, 2012, 2013, 2016, 2023, 2030, 2037, 2038, 2040, 2043, 2051, 2054, 2056, 2066, 2067, 2074, 2079, 2083, 2090, 2103, 2104, 2105, 2106, 2107, 2112, 2113, 2114, 2115, 2124, 2126, 2133, 2141, 2145, 2148, 2156, 2163, 2167, 2170, 2171, 2185, 2192, 2198, 2204, 2218, 2227, 2234, 2241, 2243, 2246, 2266, 2271, 2273, 2276, 2280, 2284, 2288, 2292, 2298, 2301, 2303, 2308, 2316, 2320, 2322, 2323, 2332, 2334, 2335, 2338, 2341, 2346, 2347, 2348, 2352, 2365, 2368, 2372, 2376, 2385, 2391, 2417, 2419, 2435, 2436, 2439, 2447, 2450, 2452, 2454, 2456, 2458, 2468, 2469, 2471, 2477, 2478, 2482, 2485, 2486, 2488, 2491, 2492, 2494, 2495, 2499, 2515, 2521, 2522, 2531, 2535, 2545, 2550, 2553, 2554, 2559, 2560, 2562, 2563, 2567, 2568, 2570, 2588, 2604, 2608, 2609, 2610, 2613, 2617, 2624, 2625, 2627, 2630, 2633, 2634, 2636, 2641, 2648, 2650, 2654, 2658, 2659, 2660, 2662, 2665, 2674, 2678, 2679, 2683, 2685, 2686, 2687, 2689, 2696, 2701, 2706, 2709, 2711, 2722, 2723, 2724, 2734, 2739, 2744, 2745, 2747, 2749, 2753, 2764, 2766, 2768, 2772, 2775, 2777, 2780, 2781, 2785, 2787, 2795, 2815, 2818, 2819, 2820, 2829, 2837, 2846, 2848, 2850, 2856, 2863, 2865, 2866, 2875, 2878, 2881, 2905, 2911, 2913, 2921, 2935, 2936, 2940, 2948, 2973, 2975, 2978, 2983, 2985, 2998, 2999, 3008, 3010, 3026, 3030, 3035, 3038, 3044, 3045, 3057, 3069, 3071, 3076, 3079, 3090, 3092, 3097, 3098, 3102, 3108, 3109, 3110, 3113, 3119, 3127, 3130, 3131, 3134, 3136, 3138, 3155, 3161, 3168, 3174, 3180, 3181, 3182, 3187, 3197, 3198, 3200, 3208, 3213, 3219, 3222, 3235, 3236, 3246, 3251, 3261, 3263, 3264, 3265, 3279, 3280, 3286, 3302, 3305, 3308, 3309, 3314, 3321, 3326, 3329, 3332, 3333, 3340, 3343, 3350, 3353, 3356, 3371, 3381, 3391, 3399, 3403, 3414, 3423, 3424, 3425, 3431, 3432, 3435, 3438, 3442, 3449, 3453, 3456, 3465, 3466, 3471, 3474, 3476, 3482, 3483, 3484, 3497, 3506, 3508, 3521, 3541, 3551, 3567, 3569, 3575, 3577, 3582, 3585, 3587, 3595, 3596, 3597, 3601, 3605, 3608, 3618, 3619, 3626, 3628, 3631, 3632, 3648, 3649, 3656, 3657, 3660, 3666, 3673, 3677, 3682, 3685, 3686, 3687, 3693, 3708, 3710, 3718, 3720, 3722, 3724, 3732, 3758, 3759, 3764, 3771, 3777, 3790, 3815, 3827, 3834, 3838, 3840, 3851, 3852, 3853, 3859, 3865, 3880, 3884, 3887, 3889, 3892, 3894, 3895, 3896, 3899, 3904, 3907, 3912, 3915, 3917, 3925, 3926, 3932, 3937, 3949, 3953, 3958, 3962, 3970, 3971, 3972, 3975, 3980, 3984, 3985, 3987, 3988, 3990, 3998, 4011, 4012, 4018, 4022, 4026, 4030, 4037, 4051, 4055, 4056, 4061, 4064, 4066, 4073, 4077, 4082, 4084, 4096, 4097, 4098, 4105, 4113, 4114, 4116, 4119, 4120, 4122, 4123, 4124, 4136, 4138, 4139, 4140, 4162, 4163, 4166, 4171, 4173, 4179, 4180, 4185, 4192, 4199, 4209, 4216, 4223, 4238, 4246, 4259, 4262, 4270, 4277, 4289, 4290, 4297, 4301, 4306, 4310, 4316, 4321, 4329, 4331, 4337, 4338, 4339, 4343, 4345, 4348, 4351, 4354, 4356, 4357, 4360, 4378, 4393, 4395, 4396, 4401, 4409, 4412, 4428, 4429, 4433, 4438, 4442, 4446, 4468, 4475, 4484, 4488, 4501, 4502, 4504, 4505, 4507, 4508, 4515, 4520, 4525, 4526, 4532, 4540, 4541, 4542, 4544, 4546, 4552, 4561, 4564, 4573, 4577, 4582, 4602, 4612, 4616, 4624, 4626, 4627, 4628, 4629, 4632, 4638, 4649, 4652, 4667, 4679, 4688, 4691, 4692, 4712, 4728, 4731, 4734, 4744, 4759, 4763, 4770, 4778, 4782, 4783, 4785, 4787, 4790, 4792, 4796, 4797, 4798, 4805, 4812, 4815, 4816, 4839, 4841, 4847, 4850, 4861, 4862, 4864, 4866, 4868, 4872, 4874, 4880, 4883, 4892, 4913, 4919, 4922, 4927, 4928, 4929, 4942, 4951, 4954, 4957, 4962, 4964, 4966, 4981, 4984, 4986, 4988, 5018, 5020, 5030, 5031, 5033, 5036, 5037, 5041, 5044, 5047, 5060, 5062, 5063, 5072, 5075, 5077, 5084, 5113, 5118, 5121, 5133, 5144, 5155, 5160, 5161, 5169, 5172, 15, 18, 26, 37, 48, 57, 80, 86, 92, 102, 104, 116, 131, 135, 139, 146, 148, 154, 157, 173, 188, 216, 218, 231, 237, 252, 265, 269, 295, 333, 335, 340, 358, 365, 368, 374, 375, 380, 385, 387, 406, 413, 425, 436, 441, 444, 445, 455, 461, 468, 477, 480, 482, 491, 498, 511, 527, 547, 583, 588, 591, 603, 612, 618, 627, 629, 636, 657, 661, 662, 669, 682, 695, 717, 748, 754, 762, 764, 776, 795, 825, 846, 848, 856, 857, 862, 863, 865, 866, 874, 884, 901, 913, 915, 1008, 1020, 1025, 1033, 1049, 1054, 1068, 1093, 1100, 1124, 1133, 1146, 1168, 1185, 1186, 1190, 1191, 1194, 1196, 1204, 1207, 1208, 1221, 1233, 1248, 1249, 1278, 1300, 1312, 1315, 1346, 1350, 1371, 1374, 1377, 1412, 1443, 1464, 1466, 1513, 1535, 1544, 1574, 1584, 1602, 1625, 1628, 1631, 1640, 1653, 1692, 1696, 1697, 1699, 1702, 1718, 1738, 1746, 1753, 1757, 1813, 1838, 1851, 1864, 1865, 1881, 1885, 1890, 1897, 1900, 1902, 1904, 1909, 1917, 1918, 1939, 1944, 1958, 1971, 1978, 1984, 1986, 2000, 2011, 2016, 2018, 2068, 2083, 2087, 2116, 2133, 2144, 2162, 2165, 2171, 2172, 2176, 2185, 2195, 2207, 2221, 2223, 2256, 2260, 2268, 2271, 2302, 2303, 2313, 2331, 2359, 2362, 2366, 2384, 2435, 2445, 2447, 2449, 2458, 2483, 2499, 2508, 2525, 2531, 2558, 2560, 2583, 2586, 2587, 2614, 2624, 2634, 2636, 2654, 2662, 2684, 2696, 2701, 2707, 2719, 2727, 2745, 2749, 2772, 2787, 2789, 2795, 2804, 2812, 2818, 2820, 2839, 2840, 2852, 2855, 2856, 2857, 2863, 2866, 2876, 2921, 2947, 2961, 2974, 2975, 2980, 2993, 3012, 3016, 3026, 3050, 3061, 3062, 3078, 3081, 3083, 3117, 3121, 3129, 3134, 3158, 3183, 3187, 3192, 3200, 3216, 3221, 3232, 3241, 3245, 3246, 3264, 3294, 3301, 3313, 3322, 3327, 3336, 3355, 3356, 3360, 3364, 3378, 3379, 3399, 3404, 3405, 3409, 3426, 3449, 3458, 3468, 3484, 3496, 3503, 3506, 3508, 3511, 3520, 3521, 3525, 3534, 3554, 3572, 3580, 3582, 3598, 3617, 3633, 3679, 3748, 3752, 3769, 3789, 3796, 3809, 3832, 3833, 3844, 3865, 3868, 3875, 3884, 3893, 3905, 3926, 3929, 3936, 3952, 3959, 3974, 3987, 3991, 4003, 4008, 4023, 4064, 4075, 4076, 4082, 4095, 4097, 4102, 4108, 4110, 4122, 4131, 4139, 4143, 4155, 4162, 4169, 4172, 4173, 4234, 4238, 4241, 4262, 4265, 4274, 4296, 4301, 4309, 4311, 4323, 4362, 4389, 4393, 4394, 4400, 4406, 4461, 4485, 4492, 4501, 4502, 4505, 4526, 4542, 4547, 4552, 4560, 4580, 4594, 4599, 4607, 4611, 4616, 4624, 4642, 4648, 4660, 4685, 4697, 4712, 4723, 4773, 4774, 4775, 4784, 4787, 4812, 4822, 4841, 4869, 4872, 4925, 4935, 4948, 4964, 4970, 4977, 4983, 4988, 5005, 5006, 5018, 5034, 5045, 5051, 5075, 5079, 5085, 5088, 5090, 5115, 5122, 5126, 5164, 5169, 5170, 111, 187, 281, 294, 300, 349, 384, 515, 584, 608, 851, 899, 1010, 1152, 1153, 1552, 1897, 2245, 2250, 2359, 2721, 2786, 2935, 3127, 3136, 3164, 3201, 3208, 3232, 3293, 3302, 3418, 3441, 3612, 4048, 4061, 4065, 4066, 4096, 4245, 4252, 4486, 4526, 4672, 4956, 5020, 5126, 5136, 29, 49, 66, 93, 98, 120, 124, 184, 187, 205, 220, 238, 245, 257, 263, 287, 345, 349, 360, 442, 457, 564, 584, 627, 657, 672, 775, 799, 818, 852, 898, 979, 1008, 1011, 1024, 1041, 1057, 1061, 1126, 1140, 1153, 1159, 1194, 1196, 1200, 1228, 1263, 1277, 1296, 1375, 1397, 1404, 1457, 1483, 1495, 1528, 1531, 1533, 1570, 1584, 1592, 1666, 1689, 1699, 1747, 1762, 1857, 1868, 1887, 1905, 1926, 1936, 1951, 1954, 1956, 1962, 1972, 1973, 2032, 2054, 2101, 2127, 2140, 2145, 2148, 2155, 2192, 2237, 2265, 2315, 2346, 2350, 2367, 2454, 2468, 2477, 2568, 2601, 2699, 2768, 2825, 2828, 2835, 2839, 2862, 2880, 2881, 2930, 3044, 3082, 3123, 3127, 3164, 3165, 3178, 3305, 3333, 3345, 3361, 3404, 3418, 3452, 3544, 3584, 3605, 3610, 3663, 3666, 3672, 3703, 3723, 3728, 3785, 3837, 3862, 3863, 3929, 3949, 3964, 4034, 4127, 4144, 4154, 4186, 4200, 4243, 4252, 4339, 4348, 4387, 4424, 4429, 4446, 4473, 4486, 4535, 4577, 4588, 4637, 4640, 4647, 4661, 4672, 4690, 4728, 4734, 4796, 4804, 4816, 4825, 4890, 4901, 4918, 4924, 4948, 4959, 5037, 5046, 5094, 5117, 5124, 5157, 38, 41, 56, 84, 89, 99, 112, 133, 136, 141, 152, 228, 257, 281, 294, 295, 321, 346, 347, 363, 424, 433, 468, 541, 544, 548, 582, 611, 631, 657, 711, 721, 760, 826, 848, 906, 988, 1028, 1034, 1052, 1061, 1071, 1107, 1113, 1131, 1138, 1145, 1150, 1153, 1186, 1188, 1191, 1210, 1250, 1281, 1292, 1300, 1324, 1353, 1384, 1393, 1414, 1417, 1438, 1443, 1482, 1510, 1530, 1589, 1632, 1652, 1707, 1747, 1749, 1774, 1782, 1810, 1835, 1861, 1877, 1903, 1912, 1928, 1940, 1954, 1975, 1991, 2044, 2094, 2118, 2147, 2166, 2226, 2231, 2261, 2266, 2303, 2342, 2364, 2369, 2390, 2429, 2436, 2437, 2449, 2483, 2539, 2556, 2560, 2608, 2614, 2634, 2651, 2652, 2685, 2699, 2715, 2722, 2742, 2759, 2764, 2771, 2784, 2816, 2838, 2840, 2889, 2916, 2919, 2938, 2941, 2944, 2957, 2960, 2972, 3025, 3057, 3077, 3089, 3124, 3126, 3159, 3161, 3167, 3175, 3183, 3248, 3327, 3341, 3345, 3390, 3396, 3409, 3431, 3451, 3452, 3456, 3515, 3517, 3551, 3559, 3561, 3569, 3610, 3617, 3627, 3669, 3685, 3693, 3694, 3698, 3739, 3741, 3827, 3859, 3863, 3873, 3874, 3919, 4003, 4083, 4118, 4128, 4150, 4177, 4220, 4316, 4343, 4410, 4412, 4426, 4446, 4483, 4486, 4492, 4500, 4520, 4527, 4535, 4569, 4579, 4589, 4602, 4616, 4645, 4667, 4689, 4690, 4697, 4717, 4732, 4734, 4790, 4803, 4849, 4853, 4872, 4873, 4878, 4887, 4890, 4919, 4964, 4992, 5018, 5027, 5031, 5035, 5047, 5051, 5059, 5163, 101, 125, 146, 225, 258, 419, 447, 528, 533, 582, 583, 712, 799, 919, 927, 940, 1066, 1201, 1223, 1531, 1569, 1586, 1692, 1875, 1919, 1976, 2002, 2032, 2092, 2133, 2191, 2193, 2244, 2325, 2342, 2440, 2518, 2533, 2549, 2613, 2652, 2668, 2692, 2702, 2704, 2828, 2873, 2887, 2999, 3017, 3044, 3062, 3231, 3302, 3388, 3452, 3821, 3877, 3901, 3910, 3964, 3965, 4004, 4049, 4112, 4175, 4283, 4384, 4586, 4709, 4810, 4817, 4888, 4997, 5016, 5098, 101, 121, 455, 538, 1073, 1183, 1555, 1659, 2078, 2121, 2402, 2539, 2582, 2620, 3079, 3095, 3167, 3390, 3452, 3529, 3541, 3597, 3919, 3935, 4085, 4135, 4378, 4624, 4677, 4887, 4908, 810, 1889, 1954, 2005, 1, 59, 70, 249, 350, 448, 537, 643, 666, 718, 761, 775, 798, 866, 873, 927, 963, 1028, 1069, 1200, 1231, 1307, 1358, 1360, 1618, 1651, 1664, 1711, 1722, 1749, 1766, 1780, 1795, 1827, 1831, 1895, 1904, 1914, 1973, 2077, 2083, 2211, 2254, 2272, 2337, 2348, 2391, 2422, 2433, 2515, 2545, 2569, 2627, 2664, 2677, 2679, 2693, 2873, 2886, 2916, 3059, 3062, 3081, 3212, 3236, 3246, 3395, 3405, 3450, 3490, 3725, 3808, 3921, 3962, 3996, 4015, 4037, 4106, 4143, 4274, 4327, 4404, 4484, 4619, 4678, 4712, 4736, 4814, 4881, 4900, 4940, 5013, 5091, 5108, 5111, 5126, 25, 101, 144, 171, 180, 186, 189, 206, 228, 276, 280, 281, 300, 327, 329, 380, 560, 582, 600, 606, 699, 763, 764, 777, 792, 815, 885, 898, 983, 997, 1041, 1189, 1231, 1256, 1274, 1280, 1305, 1362, 1393, 1415, 1438, 1458, 1475, 1493, 1495, 1621, 1680, 1698, 1733, 1774, 1775, 1802, 1812, 1827, 1835, 1861, 1883, 1954, 2111, 2127, 2150, 2158, 2162, 2166, 2234, 2343, 2364, 2422, 2439, 2474, 2504, 2513, 2539, 2587, 2662, 2664, 2693, 2771, 2777, 2782, 2785, 2806, 2816, 2835, 2860, 2953, 3006, 3015, 3020, 3135, 3159, 3249, 3280, 3302, 3315, 3345, 3355, 3420, 3448, 3531, 3551, 3610, 3625, 3638, 3640, 3663, 3689, 3694, 3724, 3728, 3744, 3837, 3877, 3891, 3900, 3934, 3944, 3966, 4034, 4048, 4093, 4149, 4164, 4169, 4333, 4378, 4392, 4429, 4442, 4451, 4579, 4602, 4607, 4624, 4717, 4742, 4749, 4763, 4786, 4798, 4830, 4872, 4906, 5001, 5013, 5023, 5126, 5156, 5159, 13, 71, 93, 94, 304, 312, 373, 413, 422, 534, 544, 595, 642, 681, 693, 721, 806, 809, 841, 1148, 1208, 1232, 1241, 1361, 1476, 1586, 1616, 1642, 1654, 1695, 1777, 1854, 1917, 1967, 1969, 1971, 1976, 1997, 2256, 2275, 2345, 2381, 2492, 2561, 2563, 2594, 2618, 2625, 2683, 2702, 2768, 2792, 2860, 2865, 2889, 3039, 3104, 3185, 3193, 3215, 3245, 3266, 3274, 3294, 3303, 3322, 3326, 3333, 3339, 3352, 3474, 3520, 3539, 3648, 3663, 3672, 3673, 3754, 3904, 3953, 3963, 4023, 4035, 4131, 4165, 4195, 4209, 4332, 4338, 4409, 4467, 4585, 4684, 4761, 4783, 4832, 4856, 4970, 4995, 5063, 5140, 58, 109, 121, 125, 146, 172, 182, 210, 258, 311, 319, 325, 375, 381, 409, 419, 422, 447, 455, 462, 485, 563, 583, 693, 810, 927, 940, 954, 1061, 1066, 1073, 1093, 1291, 1338, 1435, 1467, 1535, 1555, 1569, 1600, 1614, 1666, 1898, 1917, 1919, 1923, 1954, 2002, 2007, 2028, 2053, 2058, 2089, 2092, 2099, 2121, 2133, 2221, 2270, 2289, 2291, 2325, 2374, 2421, 2440, 2533, 2613, 2614, 2619, 2668, 2699, 2731, 2828, 2838, 2846, 2886, 2896, 2967, 3095, 3105, 3124, 3185, 3194, 3197, 3198, 3228, 3260, 3380, 3388, 3404, 3451, 3460, 3521, 3529, 3642, 3651, 3684, 3740, 3801, 3823, 3935, 3952, 3970, 3990, 4077, 4135, 4304, 4333, 4369, 4400, 4540, 4586, 4627, 4711, 4721, 4778, 4810, 4817, 4879, 4888, 5005, 349, 422, 627, 661, 927, 932, 952, 1124, 1311, 1351, 1366, 1440, 1512, 1532, 1702, 1886, 1895, 1923, 1997, 2072, 2133, 2404, 2450, 2531, 2990, 3006, 3030, 3197, 3354, 3448, 3838, 3948, 4213, 4585, 84, 116, 205, 2634, 10, 18, 37, 41, 45, 48, 49, 75, 84, 85, 105, 109, 111, 131, 140, 146, 161, 167, 172, 173, 175, 176, 179, 180, 184, 207, 211, 215, 220, 269, 279, 290, 292, 299, 311, 312, 314, 315, 320, 329, 340, 354, 358, 368, 369, 370, 372, 384, 385, 396, 400, 419, 422, 425, 433, 434, 435, 438, 440, 458, 476, 479, 514, 517, 537, 555, 563, 583, 589, 627, 631, 642, 660, 665, 669, 671, 672, 673, 686, 699, 700, 714, 716, 718, 720, 724, 737, 761, 766, 809, 831, 833, 841, 844, 846, 850, 852, 873, 874, 903, 905, 906, 918, 929, 937, 941, 955, 963, 988, 997, 1008, 1017, 1029, 1034, 1057, 1060, 1061, 1064, 1070, 1079, 1117, 1119, 1123, 1133, 1142, 1162, 1163, 1177, 1189, 1190, 1191, 1215, 1225, 1229, 1263, 1281, 1307, 1315, 1346, 1352, 1353, 1355, 1374, 1383, 1395, 1435, 1436, 1443, 1445, 1453, 1455, 1458, 1474, 1480, 1492, 1500, 1525, 1535, 1542, 1549, 1555, 1568, 1578, 1579, 1605, 1608, 1627, 1634, 1636, 1637, 1642, 1653, 1658, 1663, 1677, 1721, 1725, 1741, 1744, 1753, 1761, 1764, 1778, 1787, 1801, 1809, 1814, 1816, 1826, 1831, 1850, 1852, 1863, 1868, 1878, 1886, 1940, 1954, 1969, 1972, 1996, 2005, 2011, 2019, 2023, 2050, 2086, 2088, 2090, 2104, 2116, 2121, 2133, 2151, 2175, 2176, 2180, 2206, 2218, 2222, 2230, 2241, 2268, 2273, 2275, 2279, 2291, 2292, 2297, 2309, 2315, 2324, 2326, 2348, 2351, 2356, 2358, 2366, 2373, 2406, 2413, 2415, 2417, 2418, 2421, 2445, 2449, 2461, 2470, 2483, 2485, 2491, 2492, 2518, 2538, 2540, 2547, 2551, 2553, 2557, 2576, 2596, 2641, 2675, 2680, 2688, 2696, 2703, 2706, 2711, 2733, 2741, 2745, 2747, 2757, 2784, 2785, 2787, 2793, 2806, 2822, 2831, 2833, 2837, 2839, 2845, 2896, 2897, 2903, 2907, 2910, 2911, 2916, 2930, 2932, 2936, 2937, 2942, 2953, 2960, 2973, 2975, 2980, 2985, 2987, 2998, 3010, 3021, 3023, 3029, 3043, 3051, 3061, 3069, 3095, 3124, 3126, 3127, 3150, 3176, 3180, 3184, 3186, 3193, 3202, 3210, 3223, 3232, 3263, 3273, 3274, 3276, 3298, 3317, 3322, 3331, 3343, 3374, 3382, 3388, 3400, 3414, 3425, 3448, 3453, 3460, 3466, 3468, 3469, 3471, 3479, 3484, 3488, 3507, 3517, 3521, 3529, 3533, 3538, 3569, 3571, 3588, 3602, 3605, 3611, 3617, 3633, 3645, 3663, 3667, 3669, 3683, 3693, 3698, 3708, 3715, 3717, 3730, 3732, 3737, 3738, 3740, 3766, 3790, 3793, 3805, 3828, 3837, 3841, 3845, 3849, 3852, 3862, 3870, 3890, 3914, 3922, 3935, 3947, 3952, 3953, 3965, 3969, 3981, 3985, 3996, 4000, 4028, 4029, 4032, 4034, 4037, 4056, 4069, 4070, 4071, 4081, 4084, 4088, 4096, 4119, 4120, 4129, 4140, 4149, 4157, 4162, 4168, 4169, 4184, 4202, 4209, 4246, 4253, 4262, 4263, 4276, 4279, 4293, 4301, 4310, 4312, 4317, 4320, 4323, 4331, 4338, 4340, 4356, 4360, 4372, 4375, 4393, 4405, 4412, 4421, 4423, 4424, 4426, 4434, 4441, 4446, 4452, 4485, 4486, 4507, 4572, 4589, 4619, 4626, 4636, 4644, 4645, 4651, 4671, 4681, 4693, 4717, 4731, 4732, 4735, 4745, 4750, 4751, 4752, 4755, 4756, 4759, 4775, 4778, 4787, 4790, 4800, 4801, 4802, 4803, 4811, 4828, 4851, 4853, 4881, 4897, 4900, 4908, 4919, 4924, 4926, 4937, 4938, 4942, 4944, 4950, 4955, 4957, 4964, 4970, 4976, 4977, 4986, 4989, 5005, 5030, 5040, 5045, 5060, 5071, 5089, 5090, 5097, 5104, 5115, 5118, 5131, 5147, 5150, 5162, 5164, 5165, 5172, 7, 24, 30, 43, 45, 49, 65, 77, 90, 93, 98, 100, 118, 123, 134, 143, 147, 149, 151, 162, 163, 172, 173, 179, 180, 191, 202, 205, 208, 212, 230, 231, 241, 245, 261, 265, 267, 276, 277, 283, 286, 289, 300, 319, 330, 335, 357, 389, 390, 415, 420, 426, 432, 441, 450, 462, 474, 485, 494, 504, 514, 542, 544, 548, 563, 567, 574, 585, 588, 590, 606, 607, 627, 631, 636, 654, 662, 665, 666, 682, 707, 710, 717, 732, 736, 737, 741, 766, 771, 791, 804, 805, 808, 810, 814, 817, 824, 834, 839, 840, 842, 846, 848, 852, 864, 866, 873, 884, 891, 895, 905, 915, 919, 926, 930, 932, 933, 944, 960, 961, 965, 970, 977, 982, 989, 990, 992, 997, 1001, 1007, 1009, 1040, 1052, 1055, 1065, 1066, 1075, 1080, 1090, 1105, 1112, 1113, 1115, 1120, 1130, 1137, 1138, 1166, 1176, 1179, 1184, 1185, 1190, 1195, 1209, 1212, 1213, 1218, 1220, 1223, 1224, 1231, 1236, 1240, 1251, 1259, 1260, 1265, 1272, 1280, 1304, 1306, 1312, 1320, 1328, 1337, 1354, 1362, 1383, 1386, 1388, 1397, 1410, 1412, 1435, 1438, 1439, 1442, 1448, 1466, 1467, 1475, 1490, 1492, 1499, 1510, 1530, 1534, 1541, 1542, 1549, 1551, 1552, 1554, 1560, 1569, 1581, 1590, 1618, 1625, 1627, 1628, 1635, 1639, 1640, 1659, 1661, 1670, 1673, 1689, 1692, 1697, 1699, 1707, 1715, 1724, 1732, 1737, 1757, 1768, 1769, 1782, 1785, 1798, 1802, 1805, 1810, 1815, 1859, 1869, 1870, 1886, 1888, 1889, 1890, 1911, 1922, 1924, 1929, 1934, 1940, 1941, 1944, 1955, 1971, 1975, 1976, 1977, 1980, 1984, 1995, 2007, 2010, 2018, 2028, 2030, 2047, 2048, 2049, 2051, 2054, 2063, 2064, 2079, 2093, 2112, 2131, 2133, 2162, 2175, 2178, 2198, 2213, 2221, 2230, 2231, 2232, 2233, 2234, 2236, 2237, 2243, 2256, 2271, 2272, 2287, 2288, 2295, 2309, 2313, 2344, 2345, 2346, 2348, 2364, 2371, 2402, 2414, 2417, 2426, 2433, 2437, 2443, 2444, 2447, 2458, 2464, 2479, 2486, 2487, 2492, 2494, 2501, 2515, 2518, 2533, 2539, 2545, 2555, 2560, 2564, 2568, 2570, 2573, 2576, 2580, 2581, 2597, 2599, 2602, 2608, 2611, 2613, 2616, 2621, 2634, 2665, 2668, 2678, 2690, 2692, 2699, 2703, 2706, 2707, 2710, 2725, 2730, 2736, 2748, 2756, 2772, 2782, 2785, 2786, 2790, 2809, 2835, 2836, 2842, 2850, 2858, 2861, 2866, 2868, 2872, 2873, 2875, 2878, 2882, 2893, 2896, 2903, 2909, 2915, 2931, 2947, 2951, 2957, 2960, 2961, 2964, 2968, 2972, 2985, 2986, 2997, 3000, 3017, 3022, 3030, 3039, 3050, 3055, 3068, 3071, 3087, 3093, 3095, 3107, 3109, 3112, 3126, 3127, 3132, 3138, 3159, 3168, 3207, 3208, 3212, 3228, 3236, 3238, 3241, 3247, 3255, 3258, 3287, 3298, 3300, 3302, 3321, 3326, 3339, 3352, 3359, 3375, 3380, 3397, 3401, 3404, 3417, 3427, 3433, 3462, 3469, 3471, 3485, 3487, 3496, 3516, 3518, 3519, 3521, 3529, 3530, 3557, 3559, 3562, 3609, 3610, 3613, 3619, 3633, 3642, 3662, 3664, 3665, 3682, 3698, 3702, 3703, 3721, 3731, 3735, 3740, 3743, 3754, 3769, 3812, 3833, 3834, 3840, 3842, 3846, 3849, 3857, 3882, 3885, 3887, 3896, 3914, 3915, 3918, 3920, 3925, 3934, 3953, 3961, 3962, 3966, 3967, 3968, 3973, 3979, 4021, 4023, 4036, 4041, 4048, 4050, 4058, 4061, 4065, 4092, 4094, 4115, 4118, 4126, 4133, 4138, 4139, 4141, 4142, 4149, 4152, 4156, 4170, 4180, 4210, 4216, 4222, 4225, 4234, 4240, 4278, 4291, 4292, 4293, 4301, 4308, 4320, 4327, 4328, 4334, 4342, 4345, 4355, 4361, 4370, 4382, 4385, 4393, 4394, 4400, 4402, 4408, 4411, 4450, 4456, 4458, 4476, 4505, 4506, 4507, 4524, 4531, 4541, 4550, 4551, 4561, 4569, 4580, 4582, 4586, 4592, 4597, 4599, 4602, 4617, 4634, 4646, 4650, 4653, 4656, 4665, 4668, 4677, 4697, 4714, 4717, 4722, 4727, 4734, 4749, 4761, 4763, 4768, 4779, 4787, 4802, 4805, 4809, 4825, 4844, 4849, 4888, 4907, 4929, 4931, 4932, 4937, 4942, 4952, 4959, 4971, 5007, 5030, 5032, 5035, 5039, 5046, 5050, 5066, 5072, 5075, 5079, 5134, 5148, 5149, 5165, 809, 1954, 2270, 2898, 3190, 3604, 4137, 4329, 4520, 5151, 205, 534, 539, 611, 1519, 314, 457, 566, 912, 1030, 1181, 1409, 1459, 1467, 1630, 1797, 1967, 2084, 2099, 2164, 2207, 2239, 2364, 2433, 2483, 2495, 2665, 2765, 2941, 2945, 3061, 3088, 3132, 3192, 3199, 3352, 3807, 3824, 3867, 4034, 4193, 4201, 4498, 4741, 4773, 4805, 5126, 281, 554, 610, 764, 979, 1012, 1185, 1194, 1383, 1517, 1528, 1541, 1620, 1774, 1980, 2178, 2221, 2226, 2369, 2538, 2583, 2614, 2737, 2768, 2770, 2847, 3063, 3088, 3354, 3498, 3564, 3625, 3638, 3867, 3952, 3972, 4536, 4803, 4852, 5008, 1, 58, 210, 0, 14, 17, 18, 24, 29, 54, 56, 58, 64, 70, 83, 136, 161, 180, 186, 188, 200, 216, 237, 251, 256, 257, 277, 278, 280, 281, 321, 334, 346, 352, 354, 379, 439, 478, 485, 520, 524, 529, 530, 566, 606, 611, 621, 624, 638, 650, 668, 670, 704, 712, 723, 771, 834, 848, 890, 919, 938, 966, 1007, 1010, 1029, 1060, 1063, 1065, 1070, 1078, 1081, 1085, 1093, 1109, 1160, 1185, 1208, 1214, 1223, 1242, 1261, 1262, 1263, 1269, 1272, 1274, 1312, 1333, 1350, 1351, 1352, 1366, 1374, 1378, 1383, 1390, 1398, 1439, 1441, 1449, 1463, 1467, 1480, 1482, 1492, 1517, 1527, 1572, 1601, 1652, 1660, 1682, 1687, 1702, 1720, 1728, 1768, 1777, 1790, 1791, 1801, 1826, 1827, 1828, 1834, 1847, 1850, 1858, 1861, 1863, 1870, 1877, 1885, 1889, 1897, 1910, 1915, 1922, 1929, 1951, 1971, 2048, 2059, 2062, 2108, 2123, 2190, 2227, 2235, 2244, 2250, 2255, 2274, 2281, 2350, 2352, 2368, 2373, 2376, 2387, 2391, 2394, 2404, 2413, 2458, 2459, 2477, 2483, 2487, 2488, 2545, 2547, 2568, 2570, 2589, 2616, 2627, 2631, 2654, 2669, 2672, 2700, 2702, 2703, 2704, 2718, 2731, 2747, 2775, 2789, 2818, 2845, 2855, 2865, 2874, 2881, 2930, 2949, 2952, 2967, 2988, 3006, 3014, 3029, 3030, 3055, 3063, 3064, 3089, 3098, 3120, 3126, 3127, 3130, 3154, 3166, 3176, 3178, 3197, 3257, 3292, 3299, 3309, 3345, 3354, 3387, 3389, 3390, 3392, 3401, 3431, 3435, 3439, 3472, 3487, 3531, 3534, 3555, 3559, 3568, 3598, 3603, 3611, 3645, 3674, 3683, 3687, 3695, 3699, 3705, 3708, 3727, 3730, 3762, 3786, 3787, 3812, 3824, 3831, 3832, 3875, 3876, 3885, 3909, 3918, 3932, 3933, 3946, 3959, 3972, 3985, 4029, 4034, 4061, 4068, 4076, 4080, 4081, 4113, 4117, 4128, 4144, 4156, 4176, 4202, 4228, 4229, 4274, 4279, 4290, 4293, 4303, 4306, 4315, 4332, 4360, 4365, 4371, 4375, 4392, 4420, 4424, 4440, 4442, 4476, 4506, 4535, 4566, 4569, 4586, 4589, 4593, 4606, 4607, 4610, 4613, 4619, 4623, 4626, 4629, 4633, 4645, 4650, 4688, 4704, 4717, 4721, 4737, 4745, 4755, 4776, 4777, 4779, 4782, 4785, 4790, 4810, 4814, 4816, 4825, 4842, 4853, 4863, 4874, 4878, 4903, 4904, 4929, 4935, 4940, 4947, 4955, 4964, 4984, 5006, 5017, 5027, 5034, 5038, 5039, 5058, 5063, 5081, 5098, 5132, 5140, 5157, 5164, 5166, 5169, 42, 60, 122, 180, 189, 320, 329, 357, 410, 455, 506, 514, 517, 557, 582, 615, 637, 752, 753, 800, 808, 898, 944, 983, 1139, 1189, 1204, 1213, 1274, 1370, 1375, 1387, 1393, 1438, 1505, 1601, 1695, 1699, 1745, 1759, 1773, 1814, 1886, 1971, 2082, 2088, 2092, 2150, 2203, 2221, 2272, 2296, 2359, 2415, 2487, 2500, 2543, 2587, 2693, 2716, 2777, 2806, 2844, 2857, 2885, 2890, 2994, 3004, 3010, 3012, 3025, 3026, 3038, 3059, 3113, 3125, 3280, 3302, 3340, 3377, 3386, 3423, 3441, 3474, 3517, 3572, 3596, 3610, 3663, 3726, 3750, 3761, 3780, 3795, 3796, 3809, 3832, 3843, 3864, 3891, 3915, 3969, 3989, 4048, 4129, 4138, 4151, 4215, 4251, 4302, 4327, 4349, 4404, 4424, 4460, 4497, 4570, 4576, 4579, 4589, 4607, 4667, 4723, 4763, 4768, 4779, 4786, 4862, 5023, 5047, 5079, 5083, 5167, 0, 19, 37, 56, 59, 86, 90, 92, 98, 117, 118, 119, 131, 136, 141, 164, 167, 173, 187, 189, 190, 202, 214, 217, 227, 236, 249, 256, 263, 286, 287, 289, 291, 307, 308, 324, 326, 332, 334, 336, 347, 363, 371, 382, 389, 402, 409, 411, 425, 434, 440, 482, 507, 512, 517, 535, 561, 566, 567, 572, 577, 580, 581, 582, 597, 599, 608, 637, 642, 650, 656, 691, 692, 694, 698, 700, 703, 721, 729, 732, 743, 751, 754, 762, 777, 781, 787, 790, 831, 840, 873, 874, 877, 888, 889, 904, 905, 906, 908, 911, 923, 932, 938, 942, 944, 946, 954, 968, 976, 989, 1001, 1003, 1007, 1011, 1016, 1018, 1030, 1050, 1053, 1057, 1083, 1101, 1110, 1157, 1161, 1162, 1163, 1168, 1187, 1202, 1212, 1220, 1240, 1246, 1249, 1262, 1276, 1298, 1301, 1302, 1331, 1354, 1384, 1389, 1428, 1442, 1444, 1447, 1452, 1455, 1459, 1460, 1463, 1465, 1476, 1499, 1512, 1514, 1518, 1522, 1529, 1534, 1560, 1595, 1597, 1604, 1605, 1628, 1636, 1641, 1643, 1651, 1677, 1681, 1697, 1700, 1719, 1726, 1748, 1764, 1787, 1808, 1810, 1819, 1822, 1848, 1854, 1896, 1897, 1902, 1903, 1905, 1906, 1911, 1919, 1922, 1923, 1938, 1947, 1968, 1973, 1975, 1980, 1981, 1984, 1987, 1990, 1993, 2003, 2020, 2029, 2030, 2031, 2039, 2077, 2089, 2095, 2097, 2106, 2112, 2113, 2117, 2121, 2133, 2139, 2148, 2159, 2165, 2167, 2178, 2192, 2196, 2213, 2231, 2241, 2243, 2251, 2255, 2260, 2261, 2283, 2298, 2315, 2319, 2321, 2328, 2332, 2337, 2341, 2353, 2365, 2374, 2397, 2403, 2404, 2412, 2424, 2433, 2450, 2460, 2471, 2476, 2483, 2491, 2502, 2503, 2505, 2515, 2520, 2532, 2563, 2568, 2572, 2591, 2597, 2602, 2614, 2616, 2617, 2627, 2628, 2636, 2640, 2649, 2685, 2690, 2693, 2753, 2759, 2766, 2771, 2789, 2814, 2820, 2841, 2861, 2863, 2871, 2881, 2888, 2897, 2902, 2903, 2911, 2928, 2935, 2956, 2</t>
+    <t>234.6</t>
+  </si>
+  <si>
+    <t>12136</t>
+  </si>
+  <si>
+    <t>13, 15, 20, 28, 32, 33, 45, 48, 70, 76, 94, 104, 105, 117, 121, 131, 136, 139, 153, 155, 163, 164, 173, 175, 186, 188, 203, 205, 216, 232, 235, 236, 240, 248, 250, 252, 256, 260, 263, 272, 277, 285, 286, 289, 291, 304, 316, 326, 328, 330, 332, 336, 340, 351, 361, 371, 375, 380, 382, 384, 388, 399, 402, 405, 409, 419, 420, 425, 431, 436, 439, 440, 441, 445, 453, 458, 483, 485, 500, 512, 514, 530, 535, 541, 542, 558, 561, 577, 583, 584, 594, 597, 599, 605, 607, 618, 629, 636, 647, 649, 650, 656, 660, 668, 675, 676, 684, 686, 690, 701, 703, 712, 715, 721, 724, 725, 729, 732, 743, 754, 760, 762, 763, 774, 776, 784, 787, 788, 790, 804, 830, 839, 840, 841, 863, 866, 877, 881, 889, 905, 911, 919, 920, 941, 942, 954, 964, 965, 976, 977, 1004, 1007, 1011, 1016, 1030, 1031, 1050, 1053, 1054, 1056, 1066, 1080, 1082, 1083, 1087, 1096, 1105, 1110, 1112, 1116, 1119, 1145, 1154, 1159, 1164, 1165, 1170, 1180, 1186, 1191, 1194, 1197, 1207, 1220, 1222, 1223, 1235, 1240, 1246, 1248, 1249, 1262, 1263, 1264, 1267, 1269, 1276, 1288, 1298, 1301, 1302, 1315, 1326, 1332, 1351, 1354, 1368, 1371, 1389, 1397, 1401, 1413, 1417, 1420, 1431, 1439, 1443, 1446, 1447, 1455, 1459, 1461, 1463, 1464, 1467, 1472, 1491, 1494, 1495, 1496, 1499, 1522, 1534, 1552, 1569, 1581, 1583, 1588, 1595, 1613, 1625, 1628, 1630, 1634, 1636, 1643, 1647, 1654, 1657, 1675, 1677, 1680, 1697, 1705, 1708, 1716, 1717, 1719, 1726, 1737, 1747, 1748, 1759, 1767, 1770, 1772, 1781, 1783, 1787, 1798, 1807, 1808, 1810, 1814, 1815, 1822, 1832, 1838, 1839, 1844, 1848, 1852, 1854, 1859, 1868, 1877, 1878, 1883, 1884, 1888, 1889, 1891, 1892, 1896, 1903, 1904, 1905, 1906, 1911, 1912, 1915, 1916, 1918, 1919, 1922, 1928, 1933, 1938, 1943, 1955, 1968, 1980, 1981, 1986, 1993, 1995, 1996, 2003, 2007, 2008, 2026, 2027, 2029, 2030, 2032, 2048, 2050, 2063, 2068, 2070, 2073, 2079, 2097, 2106, 2107, 2112, 2116, 2121, 2124, 2125, 2126, 2131, 2133, 2137, 2139, 2163, 2165, 2166, 2168, 2175, 2178, 2181, 2185, 2187, 2191, 2192, 2223, 2229, 2241, 2256, 2261, 2262, 2265, 2266, 2269, 2273, 2276, 2279, 2282, 2284, 2291, 2292, 2297, 2298, 2313, 2315, 2316, 2319, 2320, 2322, 2323, 2324, 2328, 2332, 2334, 2337, 2338, 2340, 2341, 2347, 2354, 2355, 2356, 2368, 2372, 2374, 2375, 2376, 2383, 2385, 2397, 2404, 2406, 2411, 2412, 2416, 2433, 2463, 2471, 2476, 2478, 2483, 2485, 2499, 2500, 2502, 2503, 2504, 2505, 2507, 2545, 2551, 2552, 2556, 2560, 2562, 2567, 2568, 2572, 2589, 2593, 2597, 2601, 2615, 2617, 2624, 2627, 2642, 2659, 2660, 2672, 2678, 2683, 2686, 2690, 2693, 2696, 2701, 2706, 2710, 2748, 2753, 2771, 2772, 2780, 2801, 2804, 2813, 2814, 2815, 2819, 2821, 2825, 2828, 2833, 2837, 2843, 2847, 2857, 2863, 2868, 2874, 2878, 2882, 2888, 2902, 2911, 2917, 2931, 2935, 2948, 2953, 2955, 2956, 2964, 2979, 2983, 2985, 2986, 2987, 2988, 2993, 3025, 3032, 3040, 3043, 3051, 3054, 3071, 3072, 3079, 3085, 3095, 3102, 3105, 3109, 3113, 3121, 3126, 3127, 3130, 3135, 3136, 3155, 3167, 3172, 3174, 3175, 3177, 3178, 3181, 3185, 3194, 3195, 3197, 3200, 3208, 3216, 3219, 3220, 3223, 3228, 3232, 3233, 3236, 3246, 3249, 3253, 3263, 3280, 3293, 3302, 3307, 3314, 3326, 3332, 3333, 3335, 3346, 3350, 3352, 3353, 3359, 3360, 3366, 3367, 3371, 3377, 3378, 3382, 3399, 3404, 3410, 3414, 3416, 3425, 3428, 3435, 3438, 3442, 3452, 3458, 3461, 3463, 3465, 3487, 3502, 3519, 3521, 3530, 3540, 3542, 3561, 3569, 3582, 3586, 3590, 3595, 3597, 3603, 3608, 3618, 3621, 3622, 3629, 3632, 3633, 3641, 3649, 3659, 3661, 3663, 3665, 3666, 3677, 3679, 3686, 3687, 3689, 3694, 3701, 3710, 3720, 3721, 3725, 3728, 3733, 3734, 3743, 3760, 3769, 3783, 3785, 3786, 3801, 3803, 3819, 3827, 3829, 3834, 3851, 3858, 3859, 3860, 3864, 3867, 3876, 3877, 3885, 3894, 3895, 3909, 3912, 3914, 3915, 3917, 3921, 3925, 3927, 3933, 3936, 3945, 3952, 3955, 3980, 3987, 4003, 4018, 4021, 4024, 4026, 4038, 4051, 4057, 4058, 4064, 4066, 4067, 4076, 4084, 4088, 4092, 4096, 4114, 4117, 4120, 4123, 4139, 4142, 4145, 4151, 4152, 4159, 4162, 4169, 4180, 4184, 4185, 4186, 4193, 4198, 4209, 4216, 4219, 4237, 4243, 4250, 4251, 4263, 4265, 4272, 4273, 4282, 4289, 4329, 4331, 4333, 4338, 4339, 4345, 4346, 4347, 4352, 4354, 4355, 4356, 4373, 4388, 4389, 4393, 4396, 4408, 4410, 4415, 4430, 4433, 4436, 4439, 4449, 4451, 4455, 4458, 4468, 4491, 4501, 4505, 4514, 4515, 4527, 4534, 4538, 4540, 4542, 4544, 4555, 4558, 4560, 4564, 4565, 4569, 4573, 4579, 4583, 4593, 4597, 4602, 4613, 4618, 4624, 4626, 4628, 4632, 4633, 4636, 4637, 4638, 4645, 4656, 4667, 4672, 4679, 4681, 4682, 4693, 4699, 4721, 4729, 4732, 4734, 4736, 4758, 4759, 4765, 4778, 4779, 4780, 4782, 4785, 4787, 4792, 4797, 4799, 4803, 4828, 4832, 4841, 4856, 4884, 4892, 4925, 4936, 4947, 4953, 4956, 4957, 4964, 4965, 4971, 4974, 4979, 4980, 4989, 5007, 5008, 5014, 5018, 5020, 5033, 5037, 5042, 5055, 5063, 5075, 5076, 5079, 5081, 5084, 5085, 5087, 5089, 5097, 5102, 5107, 5111, 5113, 5115, 5126, 5129, 5149, 5150, 5158, 5160, 5163, 5167, 15, 26, 28, 38, 56, 62, 79, 104, 106, 121, 123, 125, 171, 174, 175, 260, 278, 320, 394, 432, 433, 487, 512, 536, 538, 543, 562, 581, 590, 605, 633, 644, 666, 688, 725, 735, 748, 763, 793, 804, 815, 866, 905, 913, 925, 926, 933, 987, 990, 1053, 1106, 1123, 1138, 1145, 1196, 1218, 1225, 1255, 1256, 1265, 1293, 1307, 1337, 1356, 1364, 1378, 1419, 1422, 1450, 1494, 1529, 1549, 1628, 1633, 1649, 1659, 1683, 1686, 1744, 1747, 1765, 1774, 1778, 1788, 1809, 1822, 1826, 1843, 1849, 1859, 1880, 1894, 1907, 1910, 1996, 2049, 2058, 2062, 2115, 2155, 2198, 2236, 2282, 2296, 2305, 2336, 2346, 2350, 2385, 2426, 2516, 2557, 2610, 2644, 2660, 2709, 2725, 2748, 2821, 2873, 2902, 2912, 2938, 2946, 2964, 2984, 2997, 3020, 3034, 3035, 3051, 3065, 3068, 3083, 3089, 3154, 3168, 3200, 3207, 3223, 3236, 3273, 3292, 3325, 3335, 3370, 3371, 3387, 3404, 3414, 3423, 3451, 3513, 3521, 3587, 3595, 3598, 3608, 3619, 3637, 3646, 3653, 3667, 3675, 3739, 3752, 3758, 3774, 3775, 3829, 3862, 3904, 3914, 3915, 3921, 3928, 3934, 3948, 3967, 3990, 4005, 4038, 4049, 4061, 4094, 4107, 4114, 4157, 4179, 4202, 4220, 4222, 4259, 4264, 4270, 4274, 4288, 4312, 4337, 4351, 4393, 4424, 4426, 4449, 4479, 4506, 4540, 4550, 4555, 4564, 4569, 4590, 4619, 4630, 4635, 4640, 4654, 4656, 4672, 4710, 4711, 4723, 4740, 4745, 4927, 4929, 4952, 4989, 5037, 5042, 5065, 5082, 5112, 5143, 5144, 5148, 1, 8, 13, 15, 24, 25, 31, 32, 37, 38, 43, 68, 75, 76, 79, 85, 86, 87, 94, 103, 111, 113, 126, 128, 130, 131, 133, 135, 139, 143, 145, 154, 155, 166, 171, 172, 173, 174, 178, 185, 188, 198, 203, 206, 212, 221, 250, 252, 256, 265, 271, 272, 277, 279, 285, 286, 296, 301, 311, 326, 327, 336, 337, 340, 349, 350, 352, 361, 365, 380, 386, 405, 406, 410, 424, 425, 432, 436, 439, 441, 445, 451, 454, 460, 469, 473, 476, 477, 480, 484, 485, 490, 504, 506, 512, 514, 515, 520, 521, 524, 526, 528, 539, 541, 542, 545, 547, 555, 558, 563, 566, 570, 574, 577, 581, 588, 594, 598, 604, 615, 623, 627, 629, 640, 660, 672, 675, 679, 681, 686, 700, 707, 717, 724, 728, 731, 732, 736, 741, 754, 759, 760, 767, 768, 771, 774, 776, 784, 787, 790, 796, 823, 826, 827, 829, 831, 837, 840, 841, 842, 844, 851, 856, 860, 862, 863, 868, 873, 877, 881, 885, 890, 897, 899, 900, 914, 915, 925, 930, 941, 950, 956, 960, 964, 965, 971, 974, 977, 979, 983, 987, 988, 998, 1003, 1004, 1039, 1044, 1045, 1054, 1062, 1081, 1082, 1087, 1090, 1111, 1112, 1116, 1135, 1138, 1142, 1148, 1156, 1164, 1168, 1172, 1182, 1185, 1186, 1207, 1208, 1214, 1215, 1219, 1223, 1224, 1230, 1239, 1241, 1243, 1246, 1248, 1252, 1255, 1256, 1259, 1262, 1263, 1276, 1301, 1312, 1320, 1324, 1337, 1342, 1351, 1353, 1363, 1366, 1367, 1375, 1386, 1388, 1389, 1394, 1397, 1401, 1403, 1410, 1413, 1417, 1426, 1428, 1439, 1444, 1446, 1447, 1449, 1455, 1459, 1463, 1464, 1475, 1483, 1493, 1494, 1495, 1498, 1499, 1504, 1510, 1519, 1520, 1528, 1534, 1540, 1541, 1544, 1552, 1558, 1569, 1572, 1574, 1581, 1583, 1596, 1601, 1603, 1608, 1618, 1623, 1625, 1630, 1636, 1639, 1644, 1646, 1649, 1655, 1656, 1660, 1665, 1666, 1670, 1675, 1676, 1677, 1680, 1681, 1682, 1683, 1693, 1698, 1708, 1711, 1717, 1722, 1727, 1730, 1737, 1742, 1749, 1752, 1757, 1759, 1762, 1767, 1772, 1776, 1779, 1782, 1787, 1792, 1797, 1805, 1806, 1808, 1816, 1844, 1849, 1854, 1857, 1864, 1867, 1868, 1871, 1873, 1877, 1884, 1889, 1890, 1892, 1896, 1904, 1906, 1912, 1917, 1921, 1922, 1924, 1930, 1934, 1937, 1944, 1954, 1958, 1962, 1975, 1976, 1980, 1981, 1990, 1993, 1996, 2008, 2012, 2013, 2016, 2023, 2030, 2037, 2038, 2040, 2043, 2051, 2054, 2056, 2066, 2067, 2074, 2079, 2083, 2090, 2103, 2104, 2105, 2106, 2107, 2112, 2113, 2114, 2115, 2124, 2126, 2133, 2141, 2145, 2148, 2156, 2163, 2167, 2170, 2171, 2185, 2192, 2198, 2204, 2218, 2227, 2234, 2241, 2243, 2246, 2266, 2271, 2273, 2276, 2280, 2284, 2288, 2292, 2298, 2301, 2303, 2308, 2316, 2320, 2322, 2323, 2332, 2334, 2335, 2338, 2341, 2346, 2347, 2348, 2352, 2365, 2368, 2372, 2376, 2385, 2391, 2417, 2419, 2435, 2436, 2439, 2447, 2450, 2452, 2454, 2456, 2458, 2468, 2469, 2471, 2477, 2478, 2482, 2485, 2486, 2488, 2491, 2492, 2494, 2495, 2499, 2515, 2521, 2522, 2531, 2535, 2545, 2550, 2553, 2554, 2559, 2560, 2562, 2563, 2567, 2568, 2570, 2588, 2604, 2608, 2609, 2610, 2613, 2617, 2624, 2625, 2627, 2630, 2633, 2634, 2636, 2641, 2648, 2650, 2654, 2658, 2659, 2660, 2662, 2665, 2674, 2678, 2679, 2683, 2685, 2686, 2687, 2689, 2696, 2701, 2706, 2709, 2711, 2722, 2723, 2724, 2734, 2739, 2744, 2745, 2747, 2749, 2753, 2764, 2766, 2768, 2772, 2775, 2777, 2780, 2781, 2785, 2787, 2795, 2815, 2818, 2819, 2820, 2829, 2837, 2846, 2848, 2850, 2856, 2863, 2865, 2866, 2875, 2878, 2881, 2905, 2911, 2913, 2921, 2935, 2936, 2940, 2948, 2973, 2975, 2978, 2983, 2985, 2998, 2999, 3008, 3010, 3026, 3030, 3035, 3038, 3044, 3045, 3057, 3069, 3071, 3076, 3079, 3090, 3092, 3097, 3098, 3102, 3108, 3109, 3110, 3113, 3119, 3127, 3130, 3131, 3134, 3136, 3138, 3155, 3161, 3168, 3174, 3180, 3181, 3182, 3187, 3197, 3198, 3200, 3208, 3213, 3219, 3222, 3235, 3236, 3246, 3251, 3261, 3263, 3264, 3265, 3279, 3280, 3286, 3302, 3305, 3308, 3309, 3314, 3321, 3326, 3329, 3332, 3333, 3340, 3343, 3350, 3353, 3356, 3371, 3381, 3391, 3399, 3403, 3414, 3423, 3424, 3425, 3431, 3432, 3435, 3438, 3442, 3449, 3453, 3456, 3465, 3466, 3471, 3474, 3476, 3482, 3483, 3484, 3497, 3506, 3508, 3521, 3541, 3551, 3567, 3569, 3575, 3577, 3582, 3585, 3587, 3595, 3596, 3597, 3601, 3605, 3608, 3618, 3619, 3626, 3628, 3631, 3632, 3648, 3649, 3656, 3657, 3660, 3666, 3673, 3677, 3682, 3685, 3686, 3687, 3693, 3708, 3710, 3718, 3720, 3722, 3724, 3732, 3758, 3759, 3764, 3771, 3777, 3790, 3815, 3827, 3834, 3838, 3840, 3851, 3852, 3853, 3859, 3865, 3880, 3884, 3887, 3889, 3892, 3894, 3895, 3896, 3899, 3904, 3907, 3912, 3915, 3917, 3925, 3926, 3932, 3937, 3949, 3953, 3958, 3962, 3970, 3971, 3972, 3975, 3980, 3984, 3985, 3987, 3988, 3990, 3998, 4011, 4012, 4018, 4022, 4026, 4030, 4037, 4051, 4055, 4056, 4061, 4064, 4066, 4073, 4077, 4082, 4084, 4096, 4097, 4098, 4105, 4113, 4114, 4116, 4119, 4120, 4122, 4123, 4124, 4136, 4138, 4139, 4140, 4162, 4163, 4166, 4171, 4173, 4179, 4180, 4185, 4192, 4199, 4209, 4216, 4223, 4238, 4246, 4259, 4262, 4270, 4277, 4289, 4290, 4297, 4301, 4306, 4310, 4316, 4321, 4329, 4331, 4337, 4338, 4339, 4343, 4345, 4348, 4351, 4354, 4356, 4357, 4360, 4378, 4393, 4395, 4396, 4401, 4409, 4412, 4428, 4429, 4433, 4438, 4442, 4446, 4468, 4475, 4484, 4488, 4501, 4502, 4504, 4505, 4507, 4508, 4515, 4520, 4525, 4526, 4532, 4540, 4541, 4542, 4544, 4546, 4552, 4561, 4564, 4573, 4577, 4582, 4602, 4612, 4616, 4624, 4626, 4627, 4628, 4629, 4632, 4638, 4649, 4652, 4667, 4679, 4688, 4691, 4692, 4712, 4728, 4731, 4734, 4744, 4759, 4763, 4770, 4778, 4782, 4783, 4785, 4787, 4790, 4792, 4796, 4797, 4798, 4805, 4812, 4815, 4816, 4839, 4841, 4847, 4850, 4861, 4862, 4864, 4866, 4868, 4872, 4874, 4880, 4883, 4892, 4913, 4919, 4922, 4927, 4928, 4929, 4942, 4951, 4954, 4957, 4962, 4964, 4966, 4981, 4984, 4986, 4988, 5018, 5020, 5030, 5031, 5033, 5036, 5037, 5041, 5044, 5047, 5060, 5062, 5063, 5072, 5075, 5077, 5084, 5113, 5118, 5121, 5133, 5144, 5155, 5160, 5161, 5169, 5172, 15, 18, 26, 37, 48, 57, 80, 86, 92, 102, 104, 116, 131, 135, 139, 146, 148, 154, 157, 173, 188, 216, 218, 231, 237, 252, 265, 269, 295, 333, 335, 340, 358, 365, 368, 374, 375, 380, 385, 387, 406, 413, 425, 436, 441, 444, 445, 455, 461, 468, 477, 480, 482, 491, 498, 511, 527, 547, 583, 588, 591, 603, 612, 618, 627, 629, 636, 657, 661, 662, 669, 682, 695, 717, 748, 754, 762, 764, 776, 795, 825, 846, 848, 856, 857, 862, 863, 865, 866, 874, 884, 901, 913, 915, 1008, 1020, 1025, 1033, 1049, 1054, 1068, 1093, 1100, 1124, 1133, 1146, 1168, 1185, 1186, 1190, 1191, 1194, 1196, 1204, 1207, 1208, 1221, 1233, 1248, 1249, 1278, 1300, 1312, 1315, 1346, 1350, 1371, 1374, 1377, 1412, 1443, 1464, 1466, 1513, 1535, 1544, 1574, 1584, 1602, 1625, 1628, 1631, 1640, 1653, 1692, 1696, 1697, 1699, 1702, 1718, 1738, 1746, 1753, 1757, 1813, 1838, 1851, 1864, 1865, 1881, 1885, 1890, 1897, 1900, 1902, 1904, 1909, 1917, 1918, 1939, 1944, 1958, 1971, 1978, 1984, 1986, 2000, 2011, 2016, 2018, 2068, 2083, 2087, 2116, 2133, 2144, 2162, 2165, 2171, 2172, 2176, 2185, 2195, 2207, 2221, 2223, 2256, 2260, 2268, 2271, 2302, 2303, 2313, 2331, 2359, 2362, 2366, 2384, 2435, 2445, 2447, 2449, 2458, 2483, 2499, 2508, 2525, 2531, 2558, 2560, 2583, 2586, 2587, 2614, 2624, 2634, 2636, 2654, 2662, 2684, 2696, 2701, 2707, 2719, 2727, 2745, 2749, 2772, 2787, 2789, 2795, 2804, 2812, 2818, 2820, 2839, 2840, 2852, 2855, 2856, 2857, 2863, 2866, 2876, 2921, 2947, 2961, 2974, 2975, 2980, 2993, 3012, 3016, 3026, 3050, 3061, 3062, 3078, 3081, 3083, 3117, 3121, 3129, 3134, 3158, 3183, 3187, 3192, 3200, 3216, 3221, 3232, 3241, 3245, 3246, 3264, 3294, 3301, 3313, 3322, 3327, 3336, 3355, 3356, 3360, 3364, 3378, 3379, 3399, 3404, 3405, 3409, 3426, 3449, 3458, 3468, 3484, 3496, 3503, 3506, 3508, 3511, 3520, 3521, 3525, 3534, 3554, 3572, 3580, 3582, 3598, 3617, 3633, 3679, 3748, 3752, 3769, 3789, 3796, 3809, 3832, 3833, 3844, 3865, 3868, 3875, 3884, 3893, 3905, 3926, 3929, 3936, 3952, 3959, 3974, 3987, 3991, 4003, 4008, 4023, 4064, 4075, 4076, 4082, 4095, 4097, 4102, 4108, 4110, 4122, 4131, 4139, 4143, 4155, 4162, 4169, 4172, 4173, 4234, 4238, 4241, 4262, 4265, 4274, 4296, 4301, 4309, 4311, 4323, 4362, 4389, 4393, 4394, 4400, 4406, 4461, 4485, 4492, 4501, 4502, 4505, 4526, 4542, 4547, 4552, 4560, 4580, 4594, 4599, 4607, 4611, 4616, 4624, 4642, 4648, 4660, 4685, 4697, 4712, 4723, 4773, 4774, 4775, 4784, 4787, 4812, 4822, 4841, 4869, 4872, 4925, 4935, 4948, 4964, 4970, 4977, 4983, 4988, 5005, 5006, 5018, 5034, 5045, 5051, 5075, 5079, 5085, 5088, 5090, 5115, 5122, 5126, 5164, 5169, 5170, 111, 187, 281, 294, 300, 349, 384, 515, 584, 608, 851, 899, 1010, 1152, 1153, 1552, 1897, 2245, 2250, 2359, 2721, 2786, 2935, 3127, 3136, 3164, 3201, 3208, 3232, 3293, 3302, 3418, 3441, 3612, 4048, 4061, 4065, 4066, 4096, 4245, 4252, 4486, 4526, 4672, 4956, 5020, 5126, 5136, 29, 49, 66, 93, 98, 120, 124, 184, 187, 205, 220, 238, 245, 257, 263, 287, 345, 349, 360, 442, 457, 564, 584, 627, 657, 672, 775, 799, 818, 852, 898, 979, 1008, 1011, 1024, 1041, 1057, 1061, 1126, 1140, 1153, 1159, 1194, 1196, 1200, 1228, 1263, 1277, 1296, 1375, 1397, 1404, 1457, 1483, 1495, 1528, 1531, 1533, 1570, 1584, 1592, 1666, 1689, 1699, 1747, 1762, 1857, 1868, 1887, 1905, 1926, 1936, 1951, 1954, 1956, 1962, 1972, 1973, 2032, 2054, 2101, 2127, 2140, 2145, 2148, 2155, 2192, 2237, 2265, 2315, 2346, 2350, 2367, 2454, 2468, 2477, 2568, 2601, 2699, 2768, 2825, 2828, 2835, 2839, 2862, 2880, 2881, 2930, 3044, 3082, 3123, 3127, 3164, 3165, 3178, 3305, 3333, 3345, 3361, 3404, 3418, 3452, 3544, 3584, 3605, 3610, 3663, 3666, 3672, 3703, 3723, 3728, 3785, 3837, 3862, 3863, 3929, 3949, 3964, 4034, 4127, 4144, 4154, 4186, 4200, 4243, 4252, 4339, 4348, 4387, 4424, 4429, 4446, 4473, 4486, 4535, 4577, 4588, 4637, 4640, 4647, 4661, 4672, 4690, 4728, 4734, 4796, 4804, 4816, 4825, 4890, 4901, 4918, 4924, 4948, 4959, 5037, 5046, 5094, 5117, 5124, 5157, 38, 41, 56, 84, 89, 99, 112, 133, 136, 141, 152, 228, 257, 281, 294, 295, 321, 346, 347, 363, 424, 433, 468, 541, 544, 548, 582, 611, 631, 657, 711, 721, 760, 826, 848, 906, 988, 1028, 1034, 1052, 1061, 1071, 1107, 1113, 1131, 1138, 1145, 1150, 1153, 1186, 1188, 1191, 1210, 1250, 1281, 1292, 1300, 1324, 1353, 1384, 1393, 1414, 1417, 1438, 1443, 1482, 1510, 1530, 1589, 1632, 1652, 1707, 1747, 1749, 1774, 1782, 1810, 1835, 1861, 1877, 1903, 1912, 1928, 1940, 1954, 1975, 1991, 2044, 2094, 2118, 2147, 2166, 2226, 2231, 2261, 2266, 2303, 2342, 2364, 2369, 2390, 2429, 2436, 2437, 2449, 2483, 2539, 2556, 2560, 2608, 2614, 2634, 2651, 2652, 2685, 2699, 2715, 2722, 2742, 2759, 2764, 2771, 2784, 2816, 2838, 2840, 2889, 2916, 2919, 2938, 2941, 2944, 2957, 2960, 2972, 3025, 3057, 3077, 3089, 3124, 3126, 3159, 3161, 3167, 3175, 3183, 3248, 3327, 3341, 3345, 3390, 3396, 3409, 3431, 3451, 3452, 3456, 3515, 3517, 3551, 3559, 3561, 3569, 3610, 3617, 3627, 3669, 3685, 3693, 3694, 3698, 3739, 3741, 3827, 3859, 3863, 3873, 3874, 3919, 4003, 4083, 4118, 4128, 4150, 4177, 4220, 4316, 4343, 4410, 4412, 4426, 4446, 4483, 4486, 4492, 4500, 4520, 4527, 4535, 4569, 4579, 4589, 4602, 4616, 4645, 4667, 4689, 4690, 4697, 4717, 4732, 4734, 4790, 4803, 4849, 4853, 4872, 4873, 4878, 4887, 4890, 4919, 4964, 4992, 5018, 5027, 5031, 5035, 5047, 5051, 5059, 5163, 101, 125, 146, 225, 258, 419, 447, 528, 533, 582, 583, 712, 799, 919, 927, 940, 1066, 1201, 1223, 1531, 1569, 1586, 1692, 1875, 1919, 1976, 2002, 2032, 2092, 2133, 2191, 2193, 2244, 2325, 2342, 2440, 2518, 2533, 2549, 2613, 2652, 2668, 2692, 2702, 2704, 2828, 2873, 2887, 2999, 3017, 3044, 3062, 3231, 3302, 3388, 3452, 3821, 3877, 3901, 3910, 3964, 3965, 4004, 4049, 4112, 4175, 4283, 4384, 4586, 4709, 4810, 4817, 4888, 4997, 5016, 5098, 101, 121, 455, 538, 810, 1073, 1183, 1555, 1659, 1889, 1954, 2005, 2078, 2121, 2402, 2539, 2582, 2620, 3079, 3095, 3167, 3390, 3452, 3529, 3541, 3597, 3919, 3935, 4085, 4135, 4378, 4624, 4677, 4887, 4908, 1, 59, 70, 249, 350, 448, 537, 643, 666, 718, 761, 775, 798, 866, 873, 927, 963, 1028, 1069, 1200, 1231, 1307, 1358, 1360, 1618, 1651, 1664, 1711, 1722, 1749, 1766, 1780, 1795, 1827, 1831, 1895, 1904, 1914, 1973, 2077, 2083, 2211, 2254, 2272, 2337, 2348, 2391, 2422, 2433, 2515, 2545, 2569, 2627, 2664, 2677, 2679, 2693, 2873, 2886, 2916, 3059, 3062, 3081, 3212, 3236, 3246, 3395, 3405, 3450, 3490, 3725, 3808, 3921, 3962, 3996, 4015, 4037, 4106, 4143, 4274, 4327, 4404, 4484, 4619, 4678, 4712, 4736, 4814, 4881, 4900, 4940, 5013, 5091, 5108, 5111, 5126, 25, 101, 144, 171, 180, 186, 189, 206, 228, 276, 280, 281, 300, 327, 329, 380, 560, 582, 600, 606, 699, 763, 764, 777, 792, 815, 885, 898, 983, 997, 1041, 1189, 1231, 1256, 1274, 1280, 1305, 1362, 1393, 1415, 1438, 1458, 1475, 1493, 1495, 1621, 1680, 1698, 1733, 1774, 1775, 1802, 1812, 1827, 1835, 1861, 1883, 1954, 2111, 2127, 2150, 2158, 2162, 2166, 2234, 2343, 2364, 2422, 2439, 2474, 2504, 2513, 2539, 2587, 2662, 2664, 2693, 2771, 2777, 2782, 2785, 2806, 2816, 2835, 2860, 2953, 3006, 3015, 3020, 3135, 3159, 3249, 3280, 3302, 3315, 3345, 3355, 3420, 3448, 3531, 3551, 3610, 3625, 3638, 3640, 3663, 3689, 3694, 3724, 3728, 3744, 3837, 3877, 3891, 3900, 3934, 3944, 3966, 4034, 4048, 4093, 4149, 4164, 4169, 4333, 4378, 4392, 4429, 4442, 4451, 4579, 4602, 4607, 4624, 4717, 4742, 4749, 4763, 4786, 4798, 4830, 4872, 4906, 5001, 5013, 5023, 5126, 5156, 5159, 13, 71, 93, 94, 304, 312, 373, 413, 422, 534, 544, 595, 642, 681, 693, 721, 806, 809, 841, 1148, 1208, 1232, 1241, 1361, 1476, 1586, 1616, 1642, 1654, 1695, 1777, 1854, 1917, 1967, 1969, 1971, 1976, 1997, 2256, 2275, 2345, 2381, 2492, 2561, 2563, 2594, 2618, 2625, 2683, 2702, 2768, 2792, 2860, 2865, 2889, 3039, 3104, 3185, 3193, 3215, 3245, 3266, 3274, 3294, 3303, 3322, 3326, 3333, 3339, 3352, 3474, 3520, 3539, 3648, 3663, 3672, 3673, 3754, 3904, 3953, 3963, 4023, 4035, 4131, 4165, 4195, 4209, 4332, 4338, 4409, 4467, 4585, 4684, 4761, 4783, 4832, 4856, 4970, 4995, 5063, 5140, 58, 109, 121, 125, 146, 172, 182, 210, 258, 311, 319, 325, 375, 381, 409, 419, 422, 447, 455, 462, 485, 563, 583, 693, 810, 927, 940, 954, 1061, 1066, 1073, 1093, 1291, 1338, 1435, 1467, 1535, 1555, 1569, 1600, 1614, 1666, 1898, 1917, 1919, 1923, 1954, 2002, 2007, 2028, 2053, 2058, 2089, 2092, 2099, 2121, 2133, 2221, 2270, 2289, 2291, 2325, 2374, 2421, 2440, 2533, 2613, 2614, 2619, 2668, 2699, 2731, 2828, 2838, 2846, 2886, 2896, 2967, 3095, 3105, 3124, 3185, 3194, 3197, 3198, 3228, 3260, 3380, 3388, 3404, 3451, 3460, 3521, 3529, 3642, 3651, 3684, 3740, 3801, 3823, 3935, 3952, 3970, 3990, 4077, 4135, 4304, 4333, 4369, 4400, 4540, 4586, 4627, 4711, 4721, 4778, 4810, 4817, 4879, 4888, 5005, 84, 116, 205, 349, 422, 627, 661, 927, 932, 952, 1124, 1311, 1351, 1366, 1440, 1512, 1532, 1702, 1886, 1895, 1923, 1997, 2072, 2133, 2404, 2450, 2531, 2634, 2990, 3006, 3030, 3197, 3354, 3448, 3838, 3948, 4213, 4585, 10, 18, 37, 41, 45, 48, 49, 75, 84, 85, 105, 109, 111, 131, 140, 146, 161, 167, 172, 173, 175, 176, 179, 180, 184, 207, 211, 215, 220, 269, 279, 290, 292, 299, 311, 312, 314, 315, 320, 329, 340, 354, 358, 368, 369, 370, 372, 384, 385, 396, 400, 419, 422, 425, 433, 434, 435, 438, 440, 458, 476, 479, 514, 517, 537, 555, 563, 583, 589, 627, 631, 642, 660, 665, 669, 671, 672, 673, 686, 699, 700, 714, 716, 718, 720, 724, 737, 761, 766, 809, 831, 833, 841, 844, 846, 850, 852, 873, 874, 903, 905, 906, 918, 929, 937, 941, 955, 963, 988, 997, 1008, 1017, 1029, 1034, 1057, 1060, 1061, 1064, 1070, 1079, 1117, 1119, 1123, 1133, 1142, 1162, 1163, 1177, 1189, 1190, 1191, 1215, 1225, 1229, 1263, 1281, 1307, 1315, 1346, 1352, 1353, 1355, 1374, 1383, 1395, 1435, 1436, 1443, 1445, 1453, 1455, 1458, 1474, 1480, 1492, 1500, 1525, 1535, 1542, 1549, 1555, 1568, 1578, 1579, 1605, 1608, 1627, 1634, 1636, 1637, 1642, 1653, 1658, 1663, 1677, 1721, 1725, 1741, 1744, 1753, 1761, 1764, 1778, 1787, 1801, 1809, 1814, 1816, 1826, 1831, 1850, 1852, 1863, 1868, 1878, 1886, 1940, 1954, 1969, 1972, 1996, 2005, 2011, 2019, 2023, 2050, 2086, 2088, 2090, 2104, 2116, 2121, 2133, 2151, 2175, 2176, 2180, 2206, 2218, 2222, 2230, 2241, 2268, 2273, 2275, 2279, 2291, 2292, 2297, 2309, 2315, 2324, 2326, 2348, 2351, 2356, 2358, 2366, 2373, 2406, 2413, 2415, 2417, 2418, 2421, 2445, 2449, 2461, 2470, 2483, 2485, 2491, 2492, 2518, 2538, 2540, 2547, 2551, 2553, 2557, 2576, 2596, 2641, 2675, 2680, 2688, 2696, 2703, 2706, 2711, 2733, 2741, 2745, 2747, 2757, 2784, 2785, 2787, 2793, 2806, 2822, 2831, 2833, 2837, 2839, 2845, 2896, 2897, 2903, 2907, 2910, 2911, 2916, 2930, 2932, 2936, 2937, 2942, 2953, 2960, 2973, 2975, 2980, 2985, 2987, 2998, 3010, 3021, 3023, 3029, 3043, 3051, 3061, 3069, 3095, 3124, 3126, 3127, 3150, 3176, 3180, 3184, 3186, 3193, 3202, 3210, 3223, 3232, 3263, 3273, 3274, 3276, 3298, 3317, 3322, 3331, 3343, 3374, 3382, 3388, 3400, 3414, 3425, 3448, 3453, 3460, 3466, 3468, 3469, 3471, 3479, 3484, 3488, 3507, 3517, 3521, 3529, 3533, 3538, 3569, 3571, 3588, 3602, 3605, 3611, 3617, 3633, 3645, 3663, 3667, 3669, 3683, 3693, 3698, 3708, 3715, 3717, 3730, 3732, 3737, 3738, 3740, 3766, 3790, 3793, 3805, 3828, 3837, 3841, 3845, 3849, 3852, 3862, 3870, 3890, 3914, 3922, 3935, 3947, 3952, 3953, 3965, 3969, 3981, 3985, 3996, 4000, 4028, 4029, 4032, 4034, 4037, 4056, 4069, 4070, 4071, 4081, 4084, 4088, 4096, 4119, 4120, 4129, 4140, 4149, 4157, 4162, 4168, 4169, 4184, 4202, 4209, 4246, 4253, 4262, 4263, 4276, 4279, 4293, 4301, 4310, 4312, 4317, 4320, 4323, 4331, 4338, 4340, 4356, 4360, 4372, 4375, 4393, 4405, 4412, 4421, 4423, 4424, 4426, 4434, 4441, 4446, 4452, 4485, 4486, 4507, 4572, 4589, 4619, 4626, 4636, 4644, 4645, 4651, 4671, 4681, 4693, 4717, 4731, 4732, 4735, 4745, 4750, 4751, 4752, 4755, 4756, 4759, 4775, 4778, 4787, 4790, 4800, 4801, 4802, 4803, 4811, 4828, 4851, 4853, 4881, 4897, 4900, 4908, 4919, 4924, 4926, 4937, 4938, 4942, 4944, 4950, 4955, 4957, 4964, 4970, 4976, 4977, 4986, 4989, 5005, 5030, 5040, 5045, 5060, 5071, 5089, 5090, 5097, 5104, 5115, 5118, 5131, 5147, 5150, 5162, 5164, 5165, 5172, 7, 24, 30, 43, 45, 49, 65, 77, 90, 93, 98, 100, 118, 123, 134, 143, 147, 149, 151, 162, 163, 172, 173, 179, 180, 191, 202, 205, 208, 212, 230, 231, 241, 245, 261, 265, 267, 276, 277, 283, 286, 289, 300, 319, 330, 335, 357, 389, 390, 415, 420, 426, 432, 441, 450, 462, 474, 485, 494, 504, 514, 542, 544, 548, 563, 567, 574, 585, 588, 590, 606, 607, 627, 631, 636, 654, 662, 665, 666, 682, 707, 710, 717, 732, 736, 737, 741, 766, 771, 791, 804, 805, 808, 810, 814, 817, 824, 834, 839, 840, 842, 846, 848, 852, 864, 866, 873, 884, 891, 895, 905, 915, 919, 926, 930, 932, 933, 944, 960, 961, 965, 970, 977, 982, 989, 990, 992, 997, 1001, 1007, 1009, 1040, 1052, 1055, 1065, 1066, 1075, 1080, 1090, 1105, 1112, 1113, 1115, 1120, 1130, 1137, 1138, 1166, 1176, 1179, 1184, 1185, 1190, 1195, 1209, 1212, 1213, 1218, 1220, 1223, 1224, 1231, 1236, 1240, 1251, 1259, 1260, 1265, 1272, 1280, 1304, 1306, 1312, 1320, 1328, 1337, 1354, 1362, 1383, 1386, 1388, 1397, 1410, 1412, 1435, 1438, 1439, 1442, 1448, 1466, 1467, 1475, 1490, 1492, 1499, 1510, 1530, 1534, 1541, 1542, 1549, 1551, 1552, 1554, 1560, 1569, 1581, 1590, 1618, 1625, 1627, 1628, 1635, 1639, 1640, 1659, 1661, 1670, 1673, 1689, 1692, 1697, 1699, 1707, 1715, 1724, 1732, 1737, 1757, 1768, 1769, 1782, 1785, 1798, 1802, 1805, 1810, 1815, 1859, 1869, 1870, 1886, 1888, 1889, 1890, 1911, 1922, 1924, 1929, 1934, 1940, 1941, 1944, 1955, 1971, 1975, 1976, 1977, 1980, 1984, 1995, 2007, 2010, 2018, 2028, 2030, 2047, 2048, 2049, 2051, 2054, 2063, 2064, 2079, 2093, 2112, 2131, 2133, 2162, 2175, 2178, 2198, 2213, 2221, 2230, 2231, 2232, 2233, 2234, 2236, 2237, 2243, 2256, 2271, 2272, 2287, 2288, 2295, 2309, 2313, 2344, 2345, 2346, 2348, 2364, 2371, 2402, 2414, 2417, 2426, 2433, 2437, 2443, 2444, 2447, 2458, 2464, 2479, 2486, 2487, 2492, 2494, 2501, 2515, 2518, 2533, 2539, 2545, 2555, 2560, 2564, 2568, 2570, 2573, 2576, 2580, 2581, 2597, 2599, 2602, 2608, 2611, 2613, 2616, 2621, 2634, 2665, 2668, 2678, 2690, 2692, 2699, 2703, 2706, 2707, 2710, 2725, 2730, 2736, 2748, 2756, 2772, 2782, 2785, 2786, 2790, 2809, 2835, 2836, 2842, 2850, 2858, 2861, 2866, 2868, 2872, 2873, 2875, 2878, 2882, 2893, 2896, 2903, 2909, 2915, 2931, 2947, 2951, 2957, 2960, 2961, 2964, 2968, 2972, 2985, 2986, 2997, 3000, 3017, 3022, 3030, 3039, 3050, 3055, 3068, 3071, 3087, 3093, 3095, 3107, 3109, 3112, 3126, 3127, 3132, 3138, 3159, 3168, 3207, 3208, 3212, 3228, 3236, 3238, 3241, 3247, 3255, 3258, 3287, 3298, 3300, 3302, 3321, 3326, 3339, 3352, 3359, 3375, 3380, 3397, 3401, 3404, 3417, 3427, 3433, 3462, 3469, 3471, 3485, 3487, 3496, 3516, 3518, 3519, 3521, 3529, 3530, 3557, 3559, 3562, 3609, 3610, 3613, 3619, 3633, 3642, 3662, 3664, 3665, 3682, 3698, 3702, 3703, 3721, 3731, 3735, 3740, 3743, 3754, 3769, 3812, 3833, 3834, 3840, 3842, 3846, 3849, 3857, 3882, 3885, 3887, 3896, 3914, 3915, 3918, 3920, 3925, 3934, 3953, 3961, 3962, 3966, 3967, 3968, 3973, 3979, 4021, 4023, 4036, 4041, 4048, 4050, 4058, 4061, 4065, 4092, 4094, 4115, 4118, 4126, 4133, 4138, 4139, 4141, 4142, 4149, 4152, 4156, 4170, 4180, 4210, 4216, 4222, 4225, 4234, 4240, 4278, 4291, 4292, 4293, 4301, 4308, 4320, 4327, 4328, 4334, 4342, 4345, 4355, 4361, 4370, 4382, 4385, 4393, 4394, 4400, 4402, 4408, 4411, 4450, 4456, 4458, 4476, 4505, 4506, 4507, 4524, 4531, 4541, 4550, 4551, 4561, 4569, 4580, 4582, 4586, 4592, 4597, 4599, 4602, 4617, 4634, 4646, 4650, 4653, 4656, 4665, 4668, 4677, 4697, 4714, 4717, 4722, 4727, 4734, 4749, 4761, 4763, 4768, 4779, 4787, 4802, 4805, 4809, 4825, 4844, 4849, 4888, 4907, 4929, 4931, 4932, 4937, 4942, 4952, 4959, 4971, 5007, 5030, 5032, 5035, 5039, 5046, 5050, 5066, 5072, 5075, 5079, 5134, 5148, 5149, 5165, 205, 534, 539, 611, 809, 1519, 1954, 2270, 2898, 3190, 3604, 4137, 4329, 4520, 5151, 314, 457, 566, 912, 1030, 1181, 1409, 1459, 1467, 1630, 1797, 1967, 2084, 2099, 2164, 2207, 2239, 2364, 2433, 2483, 2495, 2665, 2765, 2941, 2945, 3061, 3088, 3132, 3192, 3199, 3352, 3807, 3824, 3867, 4034, 4193, 4201, 4498, 4741, 4773, 4805, 5126, 1, 58, 210, 281, 554, 610, 764, 979, 1012, 1185, 1194, 1383, 1517, 1528, 1541, 1620, 1774, 1980, 2178, 2221, 2226, 2369, 2538, 2583, 2614, 2737, 2768, 2770, 2847, 3063, 3088, 3354, 3498, 3564, 3625, 3638, 3867, 3952, 3972, 4536, 4803, 4852, 5008, 0, 14, 17, 18, 24, 29, 54, 56, 58, 64, 70, 83, 136, 161, 180, 186, 188, 200, 216, 237, 251, 256, 257, 277, 278, 280, 281, 321, 334, 346, 352, 354, 379, 439, 478, 485, 520, 524, 529, 530, 566, 606, 611, 621, 624, 638, 650, 668, 670, 704, 712, 723, 771, 834, 848, 890, 919, 938, 966, 1007, 1010, 1029, 1060, 1063, 1065, 1070, 1078, 1081, 1085, 1093, 1109, 1160, 1185, 1208, 1214, 1223, 1242, 1261, 1262, 1263, 1269, 1272, 1274, 1312, 1333, 1350, 1351, 1352, 1366, 1374, 1378, 1383, 1390, 1398, 1439, 1441, 1449, 1463, 1467, 1480, 1482, 1492, 1517, 1527, 1572, 1601, 1652, 1660, 1682, 1687, 1702, 1720, 1728, 1768, 1777, 1790, 1791, 1801, 1826, 1827, 1828, 1834, 1847, 1850, 1858, 1861, 1863, 1870, 1877, 1885, 1889, 1897, 1910, 1915, 1922, 1929, 1951, 1971, 2048, 2059, 2062, 2108, 2123, 2190, 2227, 2235, 2244, 2250, 2255, 2274, 2281, 2350, 2352, 2368, 2373, 2376, 2387, 2391, 2394, 2404, 2413, 2458, 2459, 2477, 2483, 2487, 2488, 2545, 2547, 2568, 2570, 2589, 2616, 2627, 2631, 2654, 2669, 2672, 2700, 2702, 2703, 2704, 2718, 2731, 2747, 2775, 2789, 2818, 2845, 2855, 2865, 2874, 2881, 2930, 2949, 2952, 2967, 2988, 3006, 3014, 3029, 3030, 3055, 3063, 3064, 3089, 3098, 3120, 3126, 3127, 3130, 3154, 3166, 3176, 3178, 3197, 3257, 3292, 3299, 3309, 3345, 3354, 3387, 3389, 3390, 3392, 3401, 3431, 3435, 3439, 3472, 3487, 3531, 3534, 3555, 3559, 3568, 3598, 3603, 3611, 3645, 3674, 3683, 3687, 3695, 3699, 3705, 3708, 3727, 3730, 3762, 3786, 3787, 3812, 3824, 3831, 3832, 3875, 3876, 3885, 3909, 3918, 3932, 3933, 3946, 3959, 3972, 3985, 4029, 4034, 4061, 4068, 4076, 4080, 4081, 4113, 4117, 4128, 4144, 4156, 4176, 4202, 4228, 4229, 4274, 4279, 4290, 4293, 4303, 4306, 4315, 4332, 4360, 4365, 4371, 4375, 4392, 4420, 4424, 4440, 4442, 4476, 4506, 4535, 4566, 4569, 4586, 4589, 4593, 4606, 4607, 4610, 4613, 4619, 4623, 4626, 4629, 4633, 4645, 4650, 4688, 4704, 4717, 4721, 4737, 4745, 4755, 4776, 4777, 4779, 4782, 4785, 4790, 4810, 4814, 4816, 4825, 4842, 4853, 4863, 4874, 4878, 4903, 4904, 4929, 4935, 4940, 4947, 4955, 4964, 4984, 5006, 5017, 5027, 5034, 5038, 5039, 5058, 5063, 5081, 5098, 5132, 5140, 5157, 5164, 5166, 5169, 42, 60, 122, 180, 189, 320, 329, 357, 410, 455, 506, 514, 517, 557, 582, 615, 637, 752, 753, 800, 808, 898, 944, 983, 1139, 1189, 1204, 1213, 1274, 1370, 1375, 1387, 1393, 1438, 1505, 1601, 1695, 1699, 1745, 1759, 1773, 1814, 1886, 1971, 2082, 2088, 2092, 2150, 2203, 2221, 2272, 2296, 2359, 2415, 2487, 2500, 2543, 2587, 2693, 2716, 2777, 2806, 2844, 2857, 2885, 2890, 2994, 3004, 3010, 3012, 3025, 3026, 3038, 3059, 3113, 3125, 3280, 3302, 3340, 3377, 3386, 3423, 3441, 3474, 3517, 3572, 3596, 3610, 3663, 3726, 3750, 3761, 3780, 3795, 3796, 3809, 3832, 3843, 3864, 3891, 3915, 3969, 3989, 4048, 4129, 4138, 4151, 4215, 4251, 4302, 4327, 4349, 4404, 4424, 4460, 4497, 4570, 4576, 4579, 4589, 4607, 4667, 4723, 4763, 4768, 4779, 4786, 4862, 5023, 5047, 5079, 5083, 5167, 0, 19, 37, 56, 59, 86, 90, 92, 98, 117, 118, 119, 131, 136, 141, 164, 167, 173, 187, 189, 190, 202, 214, 217, 227, 236, 249, 256, 263, 286, 287, 289, 291, 307, 308, 324, 326, 332, 334, 336, 347, 363, 371, 382, 389, 402, 409, 411, 425, 434, 440, 482, 507, 512, 517, 535, 561, 566, 567, 572, 577, 580, 581, 582, 597, 599, 608, 637, 642, 650, 656, 691, 692, 694, 698, 700, 703, 721, 729, 732, 743, 751, 754, 762, 777, 781, 787, 790, 831, 840, 873, 874, 877, 888, 889, 904, 905, 906, 908, 911, 923, 932, 938, 942, 944, 946, 954, 968, 976, 989, 1001, 1003, 1007, 1011, 1016, 1018, 1030, 1050, 1053, 1057, 1083, 1101, 1110, 1157, 1161, 1162, 1163, 1168, 1187, 1202, 1212, 1220, 1240, 1246, 1249, 1262, 1276, 1298, 1301, 1302, 1331, 1354, 1384, 1389, 1428, 1442, 1444, 1447, 1452, 1455, 1459, 1460, 1463, 1465, 1476, 1499, 1512, 1514, 1518, 1522, 1529, 1534, 1560, 1595, 1597, 1604, 1605, 1628, 1636, 1641, 1643, 1651, 1677, 1681, 1697, 1700, 1719, 1726, 1748, 1764, 1787, 1808, 1810, 1819, 1822, 1848, 1854, 1896, 1897, 1902, 1903, 1905, 1906, 1911, 1919, 1922, 1923, 1938, 1947, 1968, 1973, 1975, 1980, 1981, 1984, 1987, 1990, 1993, 2003, 2020, 2029, 2030, 2031, 2039, 2077, 2089, 2095, 2097, 2106, 2112, 2113, 2117, 2121, 2133, 2139, 2148, 2159, 2165, 2167, 2178, 2192, 2196, 2213, 2231, 2241, 2243, 2251, 2255, 2260, 2261, 2283, 2298, 2315, 2319, 2321, 2328, 2332, 2337, 2341, 2353, 2365, 2374, 2397, 2403, 2404, 2412, 2424, 2433, 2450, 2460, 2471, 2476, 2483, 2491, 2502, 2503, 2505, 2515, 2520, 2532, 2563, 2568, 2572, 2591, 2597, 2602, 2614, 2616, 2617, 2627, 2628, 2636, 2640, 2649, 2685, 2690, 2693, 2753, 2759, 2766, 2771, 2789, 2814, 2820, 2841, 2861, 2863, 2871, 2881, 2888, 2897, 2902, 2903, 2911, 2928, 2935, 2956, 2</t>
   </si>
   <si>
     <t>259.78999999999996</t>
@@ -535,13 +535,13 @@
     <t>MU12_6, MU12_10, MU12_13, MU12_16, MU12_20, MU12_21, MU12_29, MU12_38, MU12_43, MU12_45, MU12_46, MU12_49, MU12_68, MU12_74, MU12_75, MU12_76, MU12_77, MU12_88, MU12_94, MU12_99, MU12_102, MU12_114, MU12_119, MU12_120, MU12_122, MU12_131, MU12_136, MU12_140, MU12_144, MU12_145, MU12_152, MU12_166, MU12_176, MU12_195, MU12_197, MU12_213, MU12_230, MU12_231, MU12_237, MU12_244, MU12_245, MU12_320, MU12_323, MU12_357, MU12_404, MU12_431, MU17_6, MU17_10, MU17_13, MU17_16, MU17_20, MU17_21, MU17_29, MU17_38, MU17_43, MU17_45, MU17_46, MU17_49, MU17_68, MU17_74, MU17_75, MU17_76, MU17_77, MU17_88, MU17_94, MU17_99, MU17_102, MU17_114, MU17_119, MU17_120, MU17_122, MU17_131, MU17_136, MU17_140, MU17_144, MU17_145, MU17_152, MU17_166, MU17_176, MU17_195, MU17_197, MU17_213, MU17_230, MU17_231, MU17_237, MU17_244, MU17_245, MU17_320, MU17_323, MU17_357, MU17_404, MU17_431</t>
   </si>
   <si>
-    <t>33.769999999999996</t>
-  </si>
-  <si>
-    <t>1747</t>
-  </si>
-  <si>
-    <t>172, 238, 264, 272, 314, 457, 579, 657, 746, 847, 1121, 1319, 1432, 1650, 1972, 2237, 2337, 2340, 2590, 2599, 2987, 3251, 3530, 3703, 3818, 4033, 4097, 4136, 4234, 4394, 4396, 4484, 4651, 4655, 4724, 4755, 12, 22, 50, 51, 57, 106, 112, 125, 149, 178, 188, 200, 206, 223, 226, 247, 275, 290, 300, 305, 316, 320, 370, 432, 436, 442, 461, 472, 489, 498, 520, 534, 544, 562, 599, 611, 656, 664, 678, 698, 731, 740, 747, 783, 803, 869, 876, 877, 879, 888, 935, 945, 954, 964, 969, 987, 1003, 1029, 1034, 1035, 1038, 1057, 1068, 1080, 1089, 1094, 1116, 1125, 1128, 1136, 1165, 1190, 1191, 1207, 1249, 1254, 1341, 1363, 1367, 1373, 1432, 1443, 1450, 1460, 1474, 1488, 1518, 1538, 1543, 1562, 1563, 1574, 1585, 1589, 1592, 1598, 1600, 1677, 1679, 1682, 1695, 1705, 1719, 1725, 1743, 1793, 1818, 1819, 1822, 1833, 1869, 1877, 1903, 1931, 1937, 1939, 2016, 2085, 2137, 2195, 2244, 2271, 2306, 2311, 2335, 2346, 2350, 2361, 2368, 2395, 2446, 2449, 2453, 2458, 2485, 2491, 2523, 2558, 2599, 2609, 2626, 2629, 2660, 2665, 2694, 2715, 2744, 2772, 2776, 2779, 2787, 2806, 2827, 2833, 2842, 2845, 2862, 2899, 2978, 3026, 3063, 3091, 3102, 3117, 3133, 3155, 3226, 3299, 3306, 3310, 3324, 3328, 3333, 3334, 3359, 3390, 3394, 3395, 3403, 3432, 3439, 3467, 3508, 3530, 3539, 3542, 3543, 3555, 3561, 3578, 3588, 3615, 3620, 3627, 3628, 3641, 3659, 3667, 3698, 3703, 3705, 3721, 3738, 3883, 3901, 3925, 3953, 3979, 3980, 4004, 4021, 4087, 4104, 4105, 4175, 4179, 4207, 4216, 4266, 4272, 4297, 4313, 4350, 4384, 4389, 4396, 4438, 4486, 4507, 4511, 4519, 4534, 4551, 4565, 4649, 4675, 4681, 4717, 4718, 4732, 4747, 4778, 4842, 4861, 4872, 4937, 4947, 4987, 4997, 5022, 5029, 5054, 5058, 5061, 5103, 5150, 5157, 717, 3440, 3486, 3653, 57, 70, 200, 581, 1338, 1526, 1761, 1772, 1903, 2175, 2291, 2410, 2842, 3155, 3286, 3361, 3670, 3677, 3691, 3890, 4111, 4318, 4443, 4542, 4624, 4833, 5093, 1272, 357, 471, 675, 690, 828, 1288, 1295, 1327, 1350, 1673, 1930, 2205, 2244, 2282, 2442, 2617, 2960, 3106, 3361, 3606, 3812, 3844, 4080, 4174, 4529, 4606, 4664, 4718, 5043, 4718, 230, 446, 690, 747, 942, 1135, 1185, 2124, 2309, 2310, 2447, 2895, 3439, 4304, 4389, 4526, 130, 234, 397, 514, 1066, 1106, 1168, 1361, 1402, 1577, 1590, 1938, 1992, 2011, 2244, 2282, 2777, 2960, 2995, 3480, 3503, 3746, 4017, 4029, 4174, 4216, 4306, 4526, 4554, 4945, 5162, 219, 489, 597, 709, 1256, 1407, 1557, 1694, 2632, 2710, 2899, 3501, 4087, 4314, 4784, 4902, 150, 1518, 1536, 1952, 2470, 3689, 3851, 3869, 4247, 417, 446, 893, 915, 1066, 1402, 1614, 1687, 1930, 1938, 2011, 2125, 2198, 2442, 2662, 2680, 3181, 3338, 3818, 4029, 4306, 4308, 4439, 4551, 4554, 4596, 5111, 513, 717, 747, 923, 1011, 1098, 1145, 1265, 2065, 2710, 2987, 2992, 3063, 3323, 3845, 4389, 4562, 4570, 1288, 1465, 1518, 3414, 3503, 3583, 4171, 4316, 204, 332, 661, 700, 911, 953, 1224, 1459, 1527, 1889, 2035, 2099, 2260, 2298, 2405, 2553, 3153, 3316, 3539, 3581, 3788, 4080, 4207, 5150, 23, 353, 579, 711, 775, 935, 981, 985, 1140, 1257, 1510, 1536, 1592, 1610, 1683, 1931, 1965, 2035, 2164, 2244, 2378, 2405, 2667, 2883, 3324, 3395, 3401, 3415, 3464, 3469, 3567, 3621, 3629, 3647, 3653, 3693, 3716, 3922, 4146, 4351, 4423, 4603, 4712, 4717, 4727, 5066, 5078, 5112, 78, 411, 446, 528, 854, 1066, 1225, 2011, 2034, 2656, 2977, 3177, 3181, 3206, 4423, 4852, 125, 403, 500, 557, 597, 605, 667, 720, 864, 893, 993, 1014, 1165, 1178, 1340, 1370, 1614, 1664, 1929, 1948, 2009, 2238, 2255, 2257, 2311, 2407, 2576, 2645, 2735, 2772, 2875, 2943, 3046, 3063, 3090, 3134, 3224, 3252, 3431, 3502, 3517, 3654, 3661, 3791, 4130, 4374, 4454, 4487, 4495, 4598, 4675, 4960, 4994, 5028, 5056, 5123, 5169, 78, 209, 294, 392, 603, 686, 746, 1033, 1161, 1174, 1195, 1282, 1291, 1338, 1444, 1460, 1654, 1963, 1992, 2029, 2084, 2436, 2600, 2628, 2763, 2963, 3071, 3266, 3352, 3503, 3564, 3703, 3716, 3917, 4004, 4132, 4147, 4155, 4350, 4434, 4598, 4770, 4782, 4828, 4853, 4893, 4960, 4963, 307, 746, 758, 853, 965, 1482, 1510, 1577, 1722, 1901, 1965, 2006, 2442, 2703, 2947, 3049, 3314, 3338, 3363, 3464, 3567, 3779, 4068, 4445, 4463, 4591, 4795, 4861, 56, 969, 1538, 1639, 2346, 2442, 3063, 3177, 3286, 3885, 5111, 294, 706, 2583, 3693, 5151, 534, 1113, 1282, 2338, 2346, 2517, 2987, 3342, 3722, 3885, 3890, 4234, 1647, 3082, 3310, 51, 77, 314, 606, 926, 1817, 1822, 1827, 1960, 2198, 2865, 3156, 3517, 3634, 4029, 4306, 4918, 4967, 506, 880, 913, 950, 1159, 1502, 2161, 2512, 3147, 3406, 3644, 4097, 4494, 4839, 4923, 5013, 5042, 23, 3146, 3296, 3693, 3883, 4779, 4923, 5099, 19, 32, 56, 283, 328, 363, 446, 520, 606, 632, 699, 717, 720, 761, 778, 802, 813, 885, 918, 921, 931, 973, 1002, 1049, 1117, 1128, 1192, 1287, 1315, 1338, 1344, 1468, 1478, 1542, 1572, 1573, 1604, 1611, 1614, 1622, 1632, 1682, 1695, 1939, 1972, 2018, 2069, 2183, 2199, 2283, 2449, 2455, 2479, 2558, 2621, 2636, 2664, 2703, 2776, 2793, 2845, 2995, 3028, 3031, 3214, 3243, 3338, 3384, 3415, 3440, 3472, 3526, 3562, 3620, 3662, 3677, 3716, 3770, 3890, 3902, 3903, 3937, 4049, 4139, 4248, 4263, 4314, 4400, 4533, 4555, 4651, 4678, 4757, 4759, 4781, 4811, 4823, 5097, 5162, 307, 807, 1002, 1181, 1364, 1482, 1667, 1802, 2442, 2458, 2903, 3338, 3779, 3869, 4093, 4591, 4643, 4937, 4981, 77, 108, 267, 667, 743, 753, 812, 893, 945, 1048, 1080, 1431, 1828, 1851, 1884, 1952, 2144, 2201, 2350, 2462, 2555, 2706, 2720, 2767, 3090, 3096, 3159, 3344, 3457, 3631, 3703, 3705, 4024, 4097, 4454, 4578, 4611, 4741, 4853, 429, 2282, 2579, 2671, 2699, 2995, 3336, 3626, 4077, 4287, 4299, 4324, 4598, 4764, 143, 161, 219, 487, 567, 595, 643, 707, 709, 737, 747, 783, 990, 1034, 1128, 1169, 1288, 1737, 1936, 1938, 2115, 2198, 2205, 2410, 2814, 3031, 3431, 3432, 3434, 3503, 3552, 3572, 3582, 3705, 3801, 3818, 3838, 3864, 4033, 4389, 4660, 4942, 4991, 5140, 5144, 12, 77, 262, 518, 664, 724, 971, 1098, 1256, 1723, 2381, 2495, 2597, 3175, 3203, 3563, 3581, 3603, 3991, 4126, 4168, 4531, 4596, 5105, 18, 164, 404, 562, 1079, 1315, 2085, 2093, 2239, 2260, 3394, 3439, 3, 77, 169, 182, 237, 328, 470, 491, 570, 579, 588, 605, 639, 747, 761, 858, 877, 924, 926, 944, 977, 1064, 1192, 1224, 1455, 1523, 1694, 1822, 2018, 2023, 2097, 2362, 2464, 2770, 2790, 2878, 2948, 3004, 3048, 3074, 3082, 3167, 3258, 3457, 3555, 3603, 3634, 3637, 3883, 3932, 4199, 4245, 4365, 4396, 4446, 4554, 4568, 4598, 4779, 4856, 5029, 5105, 5163, 77, 173, 561, 636, 746, 885, 1482, 1687, 1795, 1906, 1930, 1931, 2590, 2722, 3084, 3372, 3395, 3446, 3779, 4351, 4551, 143, 278, 470, 531, 748, 753, 791, 1229, 1368, 1389, 1395, 1558, 1585, 1952, 2163, 2192, 2370, 2562, 2694, 2710, 2772, 3167, 3384, 3431, 3480, 3601, 3972, 4187, 4308, 4475, 4660, 4699, 5150, 5111, 1266, 1639, 2974, 4289, 1358, 1648, 1683, 1797, 2338, 2451, 2633, 2669, 2978, 3376, 3418, 3610, 3991, 4294, 4665, 5040, 5169, 174, 178, 389, 471, 517, 775, 882, 988, 1032, 1134, 1225, 1339, 1574, 1600, 1610, 1692, 2130, 2257, 2362, 2370, 2376, 2592, 3003, 3117, 3314, 3738, 3782, 3843, 4115, 4652, 4700, 4832, 4997, 5018, 335, 481, 595, 601, 778, 885, 917, 1117, 1144, 1251, 1427, 1811, 1827, 1846, 2604, 2646, 2667, 2753, 2779, 2815, 3356, 3528, 4095, 4248, 4928, 4960, 5043, 77, 322, 497, 636, 885, 1327, 1737, 1858, 1877, 1906, 1931, 2008, 2015, 2590, 2748, 3067, 3779, 3908, 4727, 112, 125, 367, 420, 511, 1138, 1239, 1455, 1497, 1522, 1542, 1563, 1814, 2097, 2626, 2746, 3005, 3140, 3406, 3480, 3495, 3844, 3972, 4155, 4230, 4852, 4906, 4913, 4923, 4968, 206, 223, 446, 1174, 1258, 1567, 1573, 1604, 1685, 1695, 2257, 2301, 2449, 2636, 2664, 2883, 2885, 3017, 3214, 3961, 4096, 4139, 4304, 4355, 4443, 4828, 4949, 5061, 370, 485, 797, 981, 1328, 2122, 2640, 2642, 2883, 3131, 3481, 3552, 3564, 3844, 4853, 4861, 5101, 10, 18, 40, 55, 91, 160, 164, 181, 196, 211, 227, 332, 334, 407, 414, 482, 533, 595, 675, 734, 739, 799, 803, 807, 815, 910, 971, 983, 994, 1089, 1128, 1134, 1170, 1202, 1256, 1292, 1320, 1330, 1340, 1452, 1462, 1526, 1558, 1610, 1627, 1660, 1787, 1818, 1861, 1932, 1936, 1963, 1972, 1986, 1987, 2048, 2049, 2054, 2056, 2130, 2137, 2160, 2201, 2294, 2308, 2338, 2396, 2410, 2458, 2467, 2485, 2532, 2574, 2589, 2753, 2754, 2774, 2917, 3006, 3120, 3134, 3234, 3238, 3239, 3288, 3355, 3361, 3365, 3368, 3394, 3406, 3418, 3439, 3452, 3558, 3569, 3597, 3628, 3631, 3644, 3698, 3767, 3902, 3907, 3937, 3996, 4097, 4110, 4139, 4147, 4174, 4219, 4262, 4281, 4311, 4333, 4408, 4445, 4507, 4568, 4624, 4625, 4665, 4677, 4678, 4717, 4833, 4859, 4867, 4911, 4947, 4981, 5079, 5135, 147, 1027, 2216, 3063, 4440, 4724, 4782, 11, 57, 63, 75, 77, 82, 83, 173, 192, 193, 209, 213, 270, 272, 297, 316, 319, 328, 332, 391, 418, 436, 474, 510, 562, 572, 584, 593, 628, 641, 653, 656, 690, 704, 725, 740, 743, 781, 807, 839, 847, 854, 869, 871, 888, 910, 945, 951, 989, 1027, 1049, 1084, 1134, 1136, 1144, 1157, 1170, 1179, 1225, 1258, 1309, 1314, 1321, 1361, 1369, 1449, 1465, 1501, 1519, 1545, 1563, 1573, 1577, 1616, 1677, 1726, 1758, 1772, 1786, 1792, 1796, 1818, 1827, 1854, 1864, 1869, 1904, 1909, 1952, 2006, 2018, 2045, 2066, 2110, 2134, 2137, 2148, 2175, 2180, 2283, 2291, 2310, 2350, 2352, 2368, 2407, 2472, 2482, 2507, 2511, 2517, 2523, 2535, 2552, 2565, 2585, 2646, 2661, 2667, 2688, 2699, 2705, 2706, 2758, 2779, 2806, 2813, 2817, 2866, 2869, 2874, 2933, 2945, 2947, 2978, 2983, 3002, 3004, 3017, 3031, 3039, 3048, 3057, 3085, 3093, 3134, 3141, 3143, 3148, 3170, 3177, 3186, 3245, 3266, 3328, 3352, 3356, 3357, 3361, 3386, 3406, 3434, 3457, 3491, 3502, 3529, 3553, 3564, 3640, 3643, 3648, 3653, 3664, 3709, 3739, 3745, 3801, 3803, 3808, 3837, 3855, 3865, 3890, 3896, 3904, 3908, 3910, 3917, 3953, 4002, 4068, 4171, 4181, 4195, 4247, 4274, 4304, 4306, 4314, 4316, 4331, 4440, 4450, 4463, 4478, 4571, 4606, 4613, 4649, 4665, 4739, 4777, 4778, 4784, 4799, 4823, 4841, 4849, 4876, 4906, 4928, 4947, 4964, 4981, 5022, 5046, 5077, 5133, 5143, 77, 446, 482, 497, 504, 561, 636, 734, 1082, 1261, 1280, 1376, 1687, 1876, 1930, 1931, 2065, 2125, 2198, 3047, 3063, 3395, 3441, 3446, 3472, 3678, 3908, 4351, 4664, 4809, 4841, 5035, 114, 475, 1198, 2705, 3112, 3154, 3247, 3494, 4190, 4374, 4574, 4707, 5054, 262, 482, 834, 1382, 1429, 2442, 2555, 3196, 3423, 3446, 4663</t>
+    <t>33.790000000000006</t>
+  </si>
+  <si>
+    <t>1748</t>
+  </si>
+  <si>
+    <t>172, 238, 264, 272, 314, 457, 579, 657, 746, 847, 1121, 1319, 1432, 1650, 1972, 2237, 2337, 2340, 2590, 2599, 2987, 3251, 3530, 3703, 3818, 4033, 4097, 4136, 4234, 4394, 4396, 4484, 4651, 4655, 4724, 4755, 12, 22, 50, 51, 57, 106, 112, 125, 149, 178, 188, 200, 206, 223, 226, 247, 275, 290, 300, 305, 316, 320, 370, 432, 436, 442, 461, 472, 489, 498, 520, 534, 544, 562, 599, 611, 656, 664, 678, 698, 731, 740, 747, 783, 803, 869, 876, 877, 879, 888, 935, 945, 954, 964, 969, 987, 1003, 1029, 1034, 1035, 1038, 1057, 1068, 1080, 1089, 1094, 1116, 1125, 1128, 1136, 1165, 1190, 1191, 1207, 1249, 1254, 1341, 1363, 1367, 1373, 1432, 1443, 1450, 1460, 1474, 1488, 1518, 1538, 1543, 1562, 1563, 1574, 1585, 1589, 1592, 1598, 1600, 1677, 1679, 1682, 1695, 1705, 1719, 1725, 1743, 1793, 1818, 1819, 1822, 1833, 1869, 1877, 1903, 1931, 1937, 1939, 2016, 2085, 2137, 2195, 2244, 2271, 2306, 2311, 2335, 2346, 2350, 2361, 2368, 2395, 2446, 2449, 2453, 2458, 2485, 2491, 2523, 2558, 2599, 2609, 2626, 2629, 2660, 2665, 2694, 2715, 2744, 2772, 2776, 2779, 2787, 2806, 2827, 2833, 2842, 2845, 2862, 2899, 2978, 3026, 3063, 3091, 3102, 3117, 3133, 3155, 3226, 3299, 3306, 3310, 3324, 3328, 3333, 3334, 3359, 3390, 3394, 3395, 3403, 3432, 3439, 3467, 3508, 3530, 3539, 3542, 3543, 3555, 3561, 3578, 3588, 3615, 3620, 3627, 3628, 3641, 3659, 3667, 3698, 3703, 3705, 3721, 3738, 3883, 3901, 3925, 3953, 3979, 3980, 4004, 4021, 4087, 4104, 4105, 4175, 4179, 4207, 4216, 4266, 4272, 4297, 4313, 4350, 4384, 4389, 4396, 4438, 4486, 4507, 4511, 4519, 4534, 4551, 4565, 4649, 4675, 4681, 4717, 4718, 4732, 4747, 4778, 4842, 4861, 4872, 4937, 4947, 4987, 4997, 5022, 5029, 5054, 5058, 5061, 5103, 5150, 5157, 717, 3440, 3486, 3653, 57, 70, 200, 581, 1272, 1338, 1526, 1761, 1772, 1903, 2175, 2291, 2410, 2842, 3155, 3286, 3361, 3670, 3677, 3691, 3890, 4111, 4318, 4443, 4542, 4624, 4833, 5093, 357, 471, 675, 690, 828, 1288, 1295, 1327, 1350, 1673, 1930, 2205, 2244, 2282, 2442, 2617, 2960, 3106, 3361, 3606, 3812, 3844, 4080, 4174, 4529, 4606, 4664, 4718, 5043, 230, 446, 690, 747, 942, 1135, 1185, 2124, 2309, 2310, 2447, 2895, 3439, 4304, 4389, 4526, 4718, 130, 234, 397, 514, 1066, 1106, 1168, 1361, 1402, 1577, 1590, 1938, 1992, 2011, 2244, 2282, 2777, 2960, 2995, 3480, 3503, 3746, 4017, 4029, 4174, 4216, 4306, 4526, 4554, 4945, 5162, 219, 489, 597, 709, 1256, 1407, 1557, 1694, 2632, 2710, 2899, 3501, 4087, 4314, 4784, 4902, 150, 1518, 1536, 1952, 2470, 3689, 3851, 3869, 4247, 417, 446, 893, 915, 1066, 1402, 1614, 1687, 1930, 1938, 2011, 2125, 2198, 2442, 2662, 2680, 3181, 3338, 3818, 4029, 4306, 4308, 4439, 4551, 4554, 4596, 5111, 513, 717, 747, 923, 1011, 1098, 1145, 1265, 1288, 1465, 1518, 2065, 2710, 2987, 2992, 3063, 3323, 3414, 3503, 3583, 3845, 4171, 4316, 4389, 4562, 4570, 204, 332, 661, 700, 911, 953, 1224, 1459, 1527, 1889, 2035, 2099, 2260, 2298, 2405, 2553, 3153, 3316, 3539, 3581, 3788, 4080, 4207, 5150, 23, 353, 579, 711, 775, 935, 981, 985, 1140, 1257, 1510, 1536, 1592, 1610, 1683, 1931, 1965, 2035, 2164, 2244, 2378, 2405, 2667, 2883, 3324, 3395, 3401, 3415, 3464, 3469, 3567, 3621, 3629, 3647, 3653, 3693, 3716, 3922, 4146, 4351, 4423, 4603, 4712, 4717, 4727, 5066, 5078, 5112, 78, 411, 446, 528, 854, 1066, 1225, 2011, 2034, 2656, 2977, 3177, 3181, 3206, 4423, 4852, 125, 403, 500, 557, 597, 605, 667, 720, 864, 893, 993, 1014, 1165, 1178, 1340, 1370, 1614, 1664, 1929, 1948, 2009, 2238, 2255, 2257, 2311, 2407, 2576, 2645, 2735, 2772, 2875, 2943, 3046, 3063, 3090, 3134, 3224, 3252, 3431, 3502, 3517, 3654, 3661, 3791, 4130, 4374, 4454, 4487, 4495, 4598, 4675, 4960, 4994, 5028, 5056, 5123, 5169, 78, 209, 294, 392, 603, 686, 746, 1033, 1161, 1174, 1195, 1282, 1291, 1338, 1444, 1460, 1654, 1963, 1992, 2029, 2084, 2436, 2600, 2628, 2763, 2963, 3071, 3266, 3352, 3503, 3564, 3703, 3716, 3917, 4004, 4132, 4147, 4155, 4350, 4434, 4598, 4770, 4782, 4828, 4853, 4893, 4960, 4963, 307, 746, 758, 853, 965, 1482, 1510, 1577, 1722, 1901, 1965, 2006, 2442, 2703, 2947, 3049, 3314, 3338, 3363, 3464, 3567, 3779, 4068, 4445, 4463, 4591, 4795, 4861, 56, 294, 706, 969, 1538, 1639, 2346, 2442, 2583, 3063, 3177, 3286, 3693, 3885, 5111, 5151, 534, 1113, 1282, 1647, 2338, 2346, 2517, 2987, 3082, 3310, 3342, 3722, 3885, 3890, 4234, 51, 77, 314, 606, 926, 1817, 1822, 1827, 1960, 2198, 2865, 3156, 3517, 3634, 4029, 4306, 4918, 4967, 506, 880, 913, 950, 1159, 1502, 2161, 2512, 3147, 3406, 3644, 4097, 4494, 4839, 4923, 5013, 5042, 23, 3146, 3296, 3693, 3883, 4779, 4923, 5099, 19, 32, 56, 283, 328, 363, 446, 520, 606, 632, 699, 717, 720, 761, 778, 802, 813, 885, 918, 921, 931, 973, 1002, 1049, 1117, 1128, 1192, 1287, 1315, 1338, 1344, 1468, 1478, 1542, 1572, 1573, 1604, 1611, 1614, 1622, 1632, 1682, 1695, 1939, 1972, 2018, 2069, 2183, 2199, 2283, 2449, 2455, 2479, 2558, 2621, 2636, 2664, 2703, 2776, 2793, 2845, 2995, 3028, 3031, 3214, 3243, 3338, 3384, 3415, 3440, 3472, 3526, 3562, 3620, 3662, 3677, 3716, 3770, 3890, 3902, 3903, 3937, 4049, 4139, 4248, 4263, 4314, 4400, 4533, 4555, 4651, 4678, 4757, 4759, 4781, 4811, 4823, 5097, 5162, 307, 807, 1002, 1181, 1364, 1482, 1667, 1802, 2442, 2458, 2903, 3338, 3779, 3869, 4093, 4591, 4643, 4937, 4981, 77, 108, 267, 667, 743, 753, 812, 893, 945, 1048, 1080, 1431, 1828, 1851, 1884, 1952, 2144, 2201, 2350, 2462, 2555, 2706, 2720, 2767, 3090, 3096, 3159, 3344, 3457, 3631, 3703, 3705, 4024, 4097, 4454, 4578, 4611, 4741, 4853, 429, 2282, 2579, 2671, 2699, 2995, 3336, 3626, 4077, 4287, 4299, 4324, 4598, 4764, 143, 161, 219, 487, 567, 595, 643, 707, 709, 737, 747, 783, 990, 1034, 1128, 1169, 1288, 1737, 1936, 1938, 2115, 2198, 2205, 2410, 2814, 3031, 3431, 3432, 3434, 3503, 3552, 3572, 3582, 3705, 3801, 3818, 3838, 3864, 4033, 4389, 4660, 4942, 4991, 5140, 5144, 12, 77, 262, 518, 664, 724, 971, 1098, 1256, 1723, 2381, 2495, 2597, 3175, 3203, 3563, 3581, 3603, 3991, 4126, 4168, 4531, 4596, 5105, 18, 164, 404, 562, 1079, 1315, 2085, 2093, 2239, 2260, 3394, 3439, 3, 77, 169, 182, 237, 328, 470, 491, 570, 579, 588, 605, 639, 747, 761, 858, 877, 924, 926, 944, 977, 1064, 1192, 1224, 1455, 1523, 1694, 1822, 2018, 2023, 2097, 2362, 2464, 2770, 2790, 2878, 2948, 3004, 3048, 3074, 3082, 3167, 3258, 3457, 3555, 3603, 3634, 3637, 3883, 3932, 4199, 4245, 4365, 4396, 4446, 4554, 4568, 4598, 4779, 4856, 5029, 5105, 5163, 77, 173, 561, 636, 746, 885, 1482, 1687, 1795, 1906, 1930, 1931, 2590, 2722, 3084, 3372, 3395, 3446, 3779, 4351, 4551, 143, 278, 470, 531, 748, 753, 791, 1229, 1368, 1389, 1395, 1558, 1585, 1952, 2163, 2192, 2370, 2562, 2694, 2710, 2772, 3167, 3384, 3431, 3480, 3601, 3972, 4187, 4308, 4475, 4660, 4699, 5150, 1266, 1639, 2974, 4289, 5111, 1358, 1648, 1683, 1797, 2338, 2451, 2633, 2669, 2978, 3376, 3418, 3610, 3991, 4294, 4665, 5040, 5169, 174, 178, 389, 471, 517, 775, 882, 988, 1032, 1134, 1225, 1339, 1574, 1600, 1610, 1692, 2130, 2257, 2362, 2370, 2376, 2592, 3003, 3117, 3314, 3738, 3782, 3843, 4115, 4652, 4700, 4832, 4997, 5018, 335, 481, 595, 601, 778, 885, 917, 1117, 1144, 1251, 1427, 1811, 1827, 1846, 2604, 2646, 2667, 2753, 2779, 2815, 3356, 3528, 4095, 4248, 4928, 4960, 5043, 5167, 77, 322, 497, 636, 885, 1327, 1737, 1858, 1877, 1906, 1931, 2008, 2015, 2590, 2748, 3067, 3779, 3908, 4727, 112, 125, 367, 420, 511, 1138, 1239, 1455, 1497, 1522, 1542, 1563, 1814, 2097, 2626, 2746, 3005, 3140, 3406, 3480, 3495, 3844, 3972, 4155, 4230, 4852, 4906, 4913, 4923, 4968, 206, 223, 446, 1174, 1258, 1567, 1573, 1604, 1685, 1695, 2257, 2301, 2449, 2636, 2664, 2883, 2885, 3017, 3214, 3961, 4096, 4139, 4304, 4355, 4443, 4828, 4949, 5061, 370, 485, 797, 981, 1328, 2122, 2640, 2642, 2883, 3131, 3481, 3552, 3564, 3844, 4853, 4861, 5101, 10, 18, 40, 55, 91, 160, 164, 181, 196, 211, 227, 332, 334, 407, 414, 482, 533, 595, 675, 734, 739, 799, 803, 807, 815, 910, 971, 983, 994, 1089, 1128, 1134, 1170, 1202, 1256, 1292, 1320, 1330, 1340, 1452, 1462, 1526, 1558, 1610, 1627, 1660, 1787, 1818, 1861, 1932, 1936, 1963, 1972, 1986, 1987, 2048, 2049, 2054, 2056, 2130, 2137, 2160, 2201, 2294, 2308, 2338, 2396, 2410, 2458, 2467, 2485, 2532, 2574, 2589, 2753, 2754, 2774, 2917, 3006, 3120, 3134, 3234, 3238, 3239, 3288, 3355, 3361, 3365, 3368, 3394, 3406, 3418, 3439, 3452, 3558, 3569, 3597, 3628, 3631, 3644, 3698, 3767, 3902, 3907, 3937, 3996, 4097, 4110, 4139, 4147, 4174, 4219, 4262, 4281, 4311, 4333, 4408, 4445, 4507, 4568, 4624, 4625, 4665, 4677, 4678, 4717, 4833, 4859, 4867, 4911, 4947, 4981, 5079, 5135, 147, 1027, 2216, 3063, 4440, 4724, 4782, 11, 57, 63, 75, 77, 82, 83, 173, 192, 193, 209, 213, 270, 272, 297, 316, 319, 328, 332, 391, 418, 436, 474, 510, 562, 572, 584, 593, 628, 641, 653, 656, 690, 704, 725, 740, 743, 781, 807, 839, 847, 854, 869, 871, 888, 910, 945, 951, 989, 1027, 1049, 1084, 1134, 1136, 1144, 1157, 1170, 1179, 1225, 1258, 1309, 1314, 1321, 1361, 1369, 1449, 1465, 1501, 1519, 1545, 1563, 1573, 1577, 1616, 1677, 1726, 1758, 1772, 1786, 1792, 1796, 1818, 1827, 1854, 1864, 1869, 1904, 1909, 1952, 2006, 2018, 2045, 2066, 2110, 2134, 2137, 2148, 2175, 2180, 2283, 2291, 2310, 2350, 2352, 2368, 2407, 2472, 2482, 2507, 2511, 2517, 2523, 2535, 2552, 2565, 2585, 2646, 2661, 2667, 2688, 2699, 2705, 2706, 2758, 2779, 2806, 2813, 2817, 2866, 2869, 2874, 2933, 2945, 2947, 2978, 2983, 3002, 3004, 3017, 3031, 3039, 3048, 3057, 3085, 3093, 3134, 3141, 3143, 3148, 3170, 3177, 3186, 3245, 3266, 3328, 3352, 3356, 3357, 3361, 3386, 3406, 3434, 3457, 3491, 3502, 3529, 3553, 3564, 3640, 3643, 3648, 3653, 3664, 3709, 3739, 3745, 3801, 3803, 3808, 3837, 3855, 3865, 3890, 3896, 3904, 3908, 3910, 3917, 3953, 4002, 4068, 4171, 4181, 4195, 4247, 4274, 4304, 4306, 4314, 4316, 4331, 4440, 4450, 4463, 4478, 4571, 4606, 4613, 4649, 4665, 4739, 4777, 4778, 4784, 4799, 4823, 4841, 4849, 4876, 4906, 4928, 4947, 4964, 4981, 5022, 5046, 5077, 5133, 5143, 77, 446, 482, 497, 504, 561, 636, 734, 1082, 1261, 1280, 1376, 1687, 1876, 1930, 1931, 2065, 2125, 2198, 3047, 3063, 3395, 3441, 3446, 3472, 3678, 3908, 4351, 4664, 4809, 4841, 5035, 114, 475, 1198, 2705, 3112, 3154, 3247, 3494, 4190, 4374, 4574, 4707, 5054, 262, 482, 834, 1382, 1429, 2442, 2555, 3196, 3423, 3446, 4663</t>
   </si>
   <si>
     <t>38.76</t>
@@ -559,13 +559,13 @@
     <t>FR12_2, FR12_3, FR12_4, FR12_7, FR12_14, FR12_15, FR12_17, FR12_19, FR12_20, FR12_21, FR12_23, FR12_24, FR12_26, FR12_28, FR12_31, FR12_32, FR12_33, FR12_34, FR12_36, FR12_43, FR12_46, FR12_49, FR12_51, FR12_58, FR12_59, FR12_61, FR12_63, FR12_69, FR12_71, FR12_72, FR12_78, FR12_80, FR12_81, FR12_88, FR12_89, FR12_91, FR12_93, FR12_96, FR12_97, FR12_98, FR12_100, FR12_101, FR12_104, FR12_105, FR12_106, FR12_107, FR12_113, FR12_115, FR12_119, FR12_120, FR12_121, FR12_123, FR12_124, FR12_126, FR12_128, FR12_129, FR12_131, FR12_133, FR12_136, FR12_137, FR12_143, FR12_157, FR12_162, FR12_163, FR12_164, FR12_166, FR17_2, FR17_3, FR17_4, FR17_7, FR17_14, FR17_15, FR17_17, FR17_19, FR17_20, FR17_21, FR17_23, FR17_24, FR17_26, FR17_28, FR17_31, FR17_32, FR17_33, FR17_34, FR17_36, FR17_43, FR17_46, FR17_49, FR17_51, FR17_58, FR17_59, FR17_61, FR17_63, FR17_69, FR17_71, FR17_72, FR17_78, FR17_80, FR17_81, FR17_88, FR17_89, FR17_91, FR17_93, FR17_96, FR17_97, FR17_98, FR17_100, FR17_101, FR17_104, FR17_105, FR17_106, FR17_107, FR17_113, FR17_115, FR17_119, FR17_120, FR17_121, FR17_123, FR17_124, FR17_126, FR17_128, FR17_129, FR17_131, FR17_133, FR17_136, FR17_137, FR17_143, FR17_157, FR17_162, FR17_163, FR17_164, FR17_166</t>
   </si>
   <si>
-    <t>96.66</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>287, 310, 375, 432, 852, 1205, 1564, 1613, 1735, 1834, 1997, 2042, 2425, 2460, 2465, 2708, 2782, 2849, 3270, 3273, 3513, 3531, 4262, 5024, 5032, 5106, 5112, 93, 1302, 3968, 4000, 4002, 4354, 4563, 20, 567, 635, 827, 1336, 1524, 1932, 2451, 2585, 2764, 2993, 3066, 3659, 4187, 4423, 4657, 5136, 199, 297, 883, 1057, 1177, 1362, 1484, 1496, 1716, 1846, 1879, 1954, 2046, 2100, 2346, 2404, 2419, 2449, 2590, 2616, 2646, 2653, 2659, 2788, 2833, 2952, 3059, 3126, 3156, 3205, 3249, 3464, 3501, 3624, 3767, 4153, 4366, 4466, 4569, 4733, 5009, 5113, 517, 549, 567, 640, 4053, 4079, 79, 142, 177, 467, 517, 677, 721, 737, 751, 832, 979, 1060, 1077, 1171, 1236, 1348, 1479, 1503, 1509, 1531, 1570, 1610, 1669, 1719, 1820, 1831, 1874, 1878, 1905, 1940, 2012, 2027, 2250, 2316, 2356, 2413, 2427, 2470, 2511, 2672, 2806, 2809, 2864, 3020, 3033, 3184, 3225, 3280, 3308, 3313, 3468, 3474, 3513, 3681, 3708, 3845, 3851, 3862, 3866, 3895, 3931, 4037, 4123, 4206, 4250, 4320, 4359, 4366, 4402, 4478, 4586, 4596, 4661, 4686, 4714, 4752, 4789, 4793, 4912, 4931, 5040, 5089, 5138, 3, 6, 108, 116, 187, 199, 257, 286, 331, 332, 336, 357, 365, 411, 455, 507, 510, 546, 574, 606, 607, 608, 618, 629, 672, 712, 730, 751, 805, 852, 870, 880, 897, 917, 937, 944, 945, 1024, 1060, 1096, 1102, 1150, 1155, 1239, 1245, 1251, 1298, 1306, 1337, 1373, 1396, 1401, 1455, 1473, 1491, 1494, 1499, 1511, 1515, 1533, 1537, 1549, 1564, 1592, 1609, 1637, 1688, 1691, 1712, 1844, 1878, 1890, 1911, 1929, 1944, 1967, 2053, 2074, 2090, 2125, 2128, 2131, 2143, 2149, 2230, 2256, 2262, 2344, 2345, 2346, 2354, 2449, 2461, 2479, 2504, 2578, 2615, 2619, 2627, 2630, 2650, 2671, 2741, 2757, 2763, 2801, 2825, 2861, 2872, 2876, 2893, 2922, 2928, 2944, 2950, 2964, 2977, 2998, 3022, 3036, 3087, 3099, 3135, 3198, 3323, 3326, 3339, 3340, 3348, 3350, 3367, 3375, 3380, 3487, 3512, 3536, 3604, 3605, 3612, 3635, 3692, 3741, 3762, 3771, 3776, 3821, 3836, 3895, 3908, 3917, 3962, 4039, 4052, 4053, 4065, 4089, 4111, 4133, 4141, 4154, 4213, 4254, 4269, 4271, 4318, 4382, 4395, 4408, 4413, 4435, 4478, 4525, 4550, 4561, 4565, 4568, 4573, 4603, 4637, 4640, 4669, 4693, 4736, 4768, 4775, 4817, 4910, 4940, 4969, 4978, 5007, 5018, 5043, 5101, 5122, 287, 308, 320, 331, 446, 467, 519, 545, 604, 729, 1025, 1031, 1535, 1777, 1788, 1806, 1898, 1933, 1947, 1984, 2021, 2137, 2185, 2211, 2272, 2280, 2306, 2434, 2484, 2559, 2591, 2616, 2636, 2802, 2837, 2849, 2854, 2893, 2928, 2977, 3073, 3154, 3163, 3177, 3339, 3366, 3406, 3443, 3490, 3520, 3527, 3559, 3581, 3698, 3755, 3769, 3860, 3862, 3875, 4006, 4025, 4188, 4193, 4318, 4350, 4397, 4610, 4620, 4630, 4774, 4799, 4847, 4857, 4860, 4863, 4882, 4914, 4940, 5001, 5100, 5112, 5121, 5129, 14, 48, 89, 106, 119, 120, 230, 267, 271, 273, 287, 297, 344, 360, 398, 455, 484, 536, 581, 587, 640, 777, 778, 796, 827, 923, 933, 938, 947, 979, 987, 1037, 1046, 1056, 1064, 1084, 1091, 1102, 1111, 1115, 1137, 1172, 1187, 1195, 1216, 1233, 1248, 1275, 1298, 1304, 1308, 1321, 1367, 1372, 1406, 1465, 1531, 1564, 1570, 1612, 1623, 1741, 1831, 1861, 1867, 1886, 1894, 1911, 1917, 1922, 1925, 1931, 1967, 2031, 2044, 2063, 2068, 2083, 2087, 2108, 2126, 2221, 2222, 2239, 2264, 2283, 2295, 2302, 2340, 2358, 2384, 2540, 2553, 2576, 2595, 2627, 2651, 2746, 2780, 2781, 2800, 2818, 2824, 2919, 2929, 2967, 3018, 3050, 3061, 3069, 3085, 3125, 3225, 3245, 3248, 3267, 3279, 3315, 3320, 3334, 3369, 3372, 3439, 3479, 3501, 3577, 3590, 3627, 3658, 3705, 3707, 3724, 3766, 3813, 3860, 3868, 3886, 3892, 3915, 3950, 4006, 4052, 4087, 4096, 4097, 4111, 4251, 4259, 4294, 4323, 4395, 4408, 4467, 4480, 4568, 4591, 4625, 4653, 4733, 4754, 4799, 4827, 4843, 4859, 4882, 4985, 5025, 5043, 5094, 5108, 5121, 5124, 5164, 37, 106, 160, 169, 179, 209, 228, 230, 262, 348, 350, 392, 404, 460, 541, 550, 557, 584, 600, 610, 629, 668, 671, 684, 695, 715, 771, 810, 835, 869, 934, 1011, 1081, 1095, 1105, 1139, 1205, 1401, 1445, 1463, 1475, 1492, 1515, 1533, 1565, 1625, 1635, 1669, 1814, 1940, 1955, 1959, 1970, 2054, 2080, 2084, 2098, 2118, 2131, 2171, 2194, 2230, 2234, 2241, 2246, 2283, 2371, 2374, 2473, 2500, 2560, 2622, 2660, 2727, 2736, 2746, 2928, 2934, 3173, 3245, 3317, 3384, 3405, 3410, 3421, 3507, 3512, 3542, 3552, 3594, 3634, 3645, 3656, 3707, 3740, 3768, 3779, 3844, 3874, 3893, 3894, 3943, 4002, 4074, 4078, 4091, 4231, 4235, 4250, 4261, 4348, 4410, 4419, 4550, 4570, 4584, 4601, 4668, 4669, 4672, 4704, 4710, 4744, 4750, 4793, 4857, 4920, 5103, 5143, 57, 109, 240, 885, 905, 2056, 2241, 2377, 2722, 2977, 5014, 5147, 81, 345, 405, 1105, 1269, 1492, 1954, 2160, 2241, 2491, 2690, 2928, 3071, 3190, 3302, 3655, 3893, 4235, 4857, 5103, 107, 221, 229, 266, 587, 652, 709, 778, 890, 948, 1002, 1053, 1083, 1087, 1096, 1239, 1352, 1407, 1441, 1567, 1663, 1664, 1729, 1774, 1847, 1954, 1967, 2021, 2137, 2285, 2451, 2453, 2472, 2504, 2524, 2526, 2584, 2594, 2600, 2700, 2856, 2913, 2981, 3011, 3015, 3108, 3114, 3117, 3125, 3149, 3266, 3301, 3356, 3420, 3480, 3496, 3688, 3724, 3738, 3803, 3889, 3971, 3996, 4034, 4040, 4076, 4078, 4082, 4087, 4123, 4141, 4163, 4295, 4451, 4479, 4485, 4631, 4654, 4759, 4826, 4883, 5024, 0, 28, 46, 86, 90, 99, 107, 116, 233, 343, 353, 366, 481, 495, 504, 524, 555, 567, 584, 597, 600, 623, 635, 643, 644, 652, 689, 690, 714, 744, 905, 927, 988, 1008, 1024, 1032, 1098, 1120, 1128, 1160, 1187, 1197, 1205, 1211, 1267, 1269, 1323, 1350, 1425, 1477, 1512, 1537, 1648, 1654, 1712, 1720, 1735, 1780, 1816, 1831, 1890, 1904, 1928, 1947, 2047, 2054, 2069, 2125, 2178, 2222, 2226, 2235, 2253, 2260, 2265, 2289, 2408, 2418, 2453, 2469, 2475, 2494, 2570, 2580, 2682, 2734, 2765, 2809, 2824, 2841, 2868, 2892, 2903, 2916, 2934, 2985, 2989, 3020, 3036, 3147, 3296, 3308, 3337, 3388, 3399, 3401, 3406, 3439, 3479, 3498, 3547, 3549, 3599, 3604, 3609, 3619, 3624, 3627, 3663, 3674, 3701, 3771, 3795, 3849, 3911, 3963, 3975, 4012, 4074, 4092, 4134, 4149, 4154, 4193, 4247, 4260, 4265, 4269, 4303, 4346, 4402, 4419, 4546, 4568, 4619, 4623, 4625, 4654, 4726, 4748, 4750, 4827, 4847, 4960, 4999, 5032, 5096, 5097, 5110, 5126, 5136, 5138, 5147, 308, 1032, 2210, 2250, 2714, 3276, 3552, 3908, 4317, 33, 47, 57, 90, 95, 109, 283, 309, 320, 325, 363, 369, 412, 508, 572, 590, 640, 645, 727, 737, 768, 792, 913, 930, 933, 967, 974, 982, 999, 1051, 1058, 1121, 1367, 1511, 1633, 1692, 1712, 1735, 1741, 1766, 1767, 1820, 1849, 1874, 1880, 1898, 1922, 1978, 1988, 2029, 2054, 2057, 2084, 2168, 2244, 2268, 2288, 2295, 2316, 2324, 2344, 2360, 2397, 2403, 2475, 2523, 2540, 2622, 2649, 2652, 2704, 2755, 2779, 2892, 2897, 2952, 2963, 2967, 3011, 3033, 3036, 3061, 3143, 3144, 3227, 3235, 3244, 3266, 3290, 3293, 3331, 3356, 3383, 3396, 3456, 3457, 3464, 3522, 3529, 3557, 3574, 3652, 3663, 3669, 3751, 3793, 3971, 4017, 4033, 4067, 4103, 4126, 4163, 4188, 4222, 4240, 4250, 4272, 4348, 4350, 4366, 4406, 4423, 4510, 4531, 4619, 4631, 4673, 4690, 4726, 4748, 4786, 4814, 4873, 4899, 4922, 5025, 5032, 5080, 5158, 0, 14, 47, 63, 90, 93, 102, 131, 137, 142, 152, 175, 177, 199, 219, 221, 290, 299, 392, 418, 489, 497, 517, 632, 672, 701, 760, 838, 872, 915, 919, 927, 1038, 1057, 1058, 1194, 1204, 1211, 1259, 1298, 1321, 1351, 1451, 1496, 1518, 1559, 1603, 1629, 1645, 1678, 1723, 1735, 1769, 1782, 1811, 1829, 1853, 1880, 1894, 1905, 1927, 1941, 1978, 2018, 2128, 2158, 2166, 2210, 2213, 2217, 2223, 2226, 2289, 2321, 2345, 2351, 2355, 2395, 2435, 2451, 2490, 2553, 2581, 2597, 2612, 2622, 2629, 2654, 2718, 2723, 2731, 2788, 2807, 2825, 2843, 2861, 2890, 2915, 2926, 2935, 2950, 2981, 2983, 2988, 3007, 3127, 3157, 3225, 3248, 3277, 3280, 3296, 3302, 3348, 3366, 3388, 3443, 3445, 3461, 3477, 3547, 3550, 3602, 3610, 3644, 3699, 3718, 3746, 3768, 3815, 3833, 3854, 3979, 4029, 4047, 4094, 4095, 4105, 4133, 4152, 4193, 4294, 4353, 4365, 4381, 4396, 4410, 4423, 4506, 4510, 4531, 4563, 4574, 4597, 4653, 4670, 4688, 4699, 4738, 4775, 4787, 4831, 4852, 4857, 4865, 4870, 4913, 4964, 4969, 4978, 5016, 5027, 5033, 5043, 5046, 5096, 5101, 5112, 5123, 5165, 19, 37, 74, 211, 225, 273, 336, 348, 410, 522, 538, 577, 650, 652, 952, 958, 1137, 1138, 1166, 1187, 1538, 1544, 1555, 1559, 1570, 1646, 1693, 1697, 1712, 1719, 1820, 1880, 1922, 1991, 2168, 2223, 2239, 2244, 2292, 2397, 2540, 2606, 2637, 2726, 2816, 2827, 2981, 3207, 3235, 3244, 3292, 3383, 3388, 3391, 3423, 3545, 3663, 3707, 3861, 3945, 3976, 4039, 4133, 4142, 4217, 4287, 4303, 4523, 4603, 4713, 4733, 4775, 4805, 4874, 4900, 4910, 4920, 4928, 4967, 4970, 4986, 5022, 5089, 24, 75, 118, 186, 233, 238, 258, 318, 360, 398, 796, 952, 1059, 1095, 1188, 1280, 1360, 1465, 1522, 1777, 2042, 2056, 2118, 2143, 2158, 2321, 2395, 2460, 2557, 2581, 2681, 2736, 2986, 3112, 3122, 3137, 3155, 3214, 3241, 3302, 3334, 3356, 3429, 3445, 3501, 3570, 3594, 3644, 4030, 4223, 4354, 4396, 4507, 4544, 4563, 4574, 4646, 4738, 4744, 4895, 4968, 5034, 36, 111, 229, 234, 273, 422, 423, 462, 525, 536, 564, 610, 627, 748, 795, 801, 826, 854, 866, 880, 905, 999, 1002, 1052, 1083, 1092, 1124, 1155, 1212, 1268, 1285, 1409, 1545, 1634, 1667, 1671, 1722, 1770, 1782, 1793, 1796, 1837, 1845, 1874, 1922, 2012, 2018, 2050, 2082, 2106, 2145, 2162, 2226, 2275, 2300, 2311, 2423, 2453, 2461, 2519, 2523, 2559, 2590, 2606, 2648, 2652, 2718, 2742, 2856, 2876, 2915, 2944, 2985, 3011, 3042, 3052, 3087, 3115, 3207, 3209, 3283, 3302, 3367, 3605, 3645, 3827, 3912, 3968, 4064, 4076, 4206, 4221, 4226, 4320, 4327, 4334, 4431, 4541, 4592, 4620, 4630, 4702, 4703, 4735, 4775, 4779, 4928, 4944, 5009, 31, 131, 585, 734, 831, 1042, 1058, 1451, 1489, 1799, 1948, 1996, 2018, 2173, 2508, 2537, 2541, 2597, 2716, 2718, 2722, 2975, 3068, 3449, 3816, 4060, 4439, 4526, 4563, 4572, 4883, 5025, 5046, 5094, 5117, 1581, 1782, 4119, 4171, 4669, 4708, 4729, 4810, 4813, 0, 93, 123, 218, 229, 256, 263, 291, 329, 435, 446, 481, 511, 522, 524, 549, 555, 577, 603, 607, 645, 660, 682, 948, 1060, 1076, 1086, 1215, 1244, 1394, 1549, 1660, 1689, 1711, 1828, 1881, 1905, 1919, 1987, 1995, 2069, 2116, 2210, 2247, 2362, 2404, 2413, 2415, 2501, 2534, 2561, 2629, 2837, 2849, 2933, 2967, 3008, 3054, 3126, 3212, 3318, 3337, 3397, 3513, 3594, 3624, 3666, 3719, 3755, 3908, 4051, 4079, 4087, 4119, 4147, 4171, 4199, 4316, 4353, 4385, 4389, 4498, 4506, 4513, 4710, 4821, 4994, 5057, 5112, 549, 938, 1248, 1801, 2085, 2247, 2415, 3008, 3464, 3624, 4754, 5112, 69, 145, 158, 263, 273, 283, 320, 332, 375, 482, 682, 709, 1090, 1136, 1201, 1236, 1248, 1469, 1648, 1759, 1763, 1776, 1786, 1797, 1821, 1826, 2054, 2055, 2080, 2116, 2117, 2268, 2289, 2302, 2399, 2408, 2426, 2449, 2479, 2536, 2600, 2615, 2653, 2696, 2716, 2755, 2761, 2978, 2981, 2985, 2988, 3000, 3120, 3125, 3165, 3179, 3362, 3363, 3423, 3645, 3795, 3808, 3832, 3836, 3923, 4039, 4040, 4181, 4218, 4231, 4250, 4259, 4316, 4336, 4467, 4520, 4539, 4586, 4650, 4690, 4700, 4711, 4767, 4864, 4900, 4946, 5034, 5042, 5050, 5085, 5109, 5112, 5138, 46, 85, 90, 95, 96, 167, 478, 589, 630, 699, 778, 830, 831, 866, 896, 933, 976, 1029, 1042, 1051, 1065, 1096, 1171, 1210, 1318, 1333, 1459, 1477, 1503, 1507, 1524, 1592, 1780, 1858, 1898, 2002, 2051, 2173, 2230, 2248, 2352, 2373, 2391, 2522, 2545, 2559, 2561, 2624, 2638, 2874, 3217, 3319, 3346, 3360, 3400, 3437, 3448, 3478, 3487, 3526, 3534, 3594, 3687, 3962, 4028, 4065, 4171, 4233, 4291, 4294, 4323, 4526, 4563, 4739, 4863, 4876, 4971, 4977, 5027, 5104, 89, 271, 338, 360, 777, 1205, 1321, 1463, 1623, 1984, 2320, 2786, 3230, 3245, 3248, 3705, 3861, 4653, 4750, 4783, 4843, 4857, 4931, 35, 199, 209, 227, 263, 290, 329, 353, 357, 400, 424, 481, 545, 608, 672, 696, 700, 705, 787, 792, 814, 851, 923, 987, 998, 1016, 1032, 1086, 1189, 1211, 1331, 1333, 1342, 1498, 1524, 1539, 1603, 1659, 1664, 1776, 1793, 1898, 1931, 1996, 2043, 2072, 2080, 2117, 2150, 2183, 2198, 2221, 2239, 2267, 2423, 2528, 2553, 2758, 2766, 2820, 2923, 2954, 3045, 3084, 3093, 3098, 3144, 3156, 3214, 3229, 3270, 3334, 3400, 3445, 3498, 3532, 3557, 3645, 3655, 3699, 3719, 3817, 3870, 3889, 3928, 3932, 3966, 4011, 4058, 4105, 4193, 4226, 4334, 4431, 4435, 4451, 4482, 4528, 4597, 4648, 4740, 4784, 4793, 4909, 4988, 5023, 5032, 5051, 5073, 5124, 5138, 28, 73, 75, 90, 112, 122, 137, 142, 225, 320, 410, 423, 545, 565, 604, 642, 682, 701, 725, 756, 809, 863, 1016, 1051, 1180, 1189, 1210, 1378, 1525, 1535, 1545, 1569, 1570, 1720, 1723, 1769, 1782, 1799, 1807, 1905, 2018, 2040, 2042, 2063, 2130, 2211, 2266, 2326, 2331, 2362, 2483, 2561, 2564, 2582, 2650, 2660, 2714, 2814, 2970, 2978, 3122, 3125, 3249, 3391, 3484, 3513, 3588, 3597, 3660, 3717, 3748, 3769, 3851, 3875, 4042, 4057, 4065, 4163, 4172, 4193, 4262, 4412, 4448, 4453, 4467, 4550, 4593, 4693, 4784, 4814, 4905, 4944, 4969, 4983, 5059, 5112, 5143, 5168, 411, 446, 577, 607, 715, 933, 982, 1042, 1351, 1515, 1689, 1806, 2494, 2849, 3284, 3484, 3569, 3997, 4418, 4669, 4743, 4887, 5046, 28, 107, 299, 660, 838, 1037, 1076, 1168, 1234, 1463, 1552, 1728, 1986, 2030, 2042, 2226, 2395, 2398, 2856, 3725, 3825, 3833, 4002, 4051, 4141, 4213, 4216, 4340, 4385, 4408, 4523, 4733, 4828, 4909, 5025, 5106, 32, 73, 74, 99, 121, 168, 287, 338, 366, 389, 392, 418, 443, 460, 462, 642, 727, 769, 813, 828, 860, 872, 933, 934, 959, 1158, 1177, 1212, 1260, 1290, 1502, 1567, 1641, 1690, 1759, 1796, 1807, 1839, 1847, 1855, 1894, 1912, 2038, 2061, 2128, 2144, 2183, 2353, 2490, 2493, 2514, 2555, 2582, 2680, 2706, 2801, 2824, 2837, 2949, 2981, 2995, 3008, 3026, 3060, 3070, 3118, 3161, 3184, 3276, 3326, 3391, 3397, 3461, 3474, 3576, 3658, 3831, 3836, 3872, 3880, 3916, 4155, 4259, 4354, 4359, 4385, 4563, 4618, 4669, 4690, 4717, 4844, 5021, 5108, 5113, 5169, 89, 151, 210, 555, 776, 880, 913, 979, 1011, 1103, 1115, 1372, 1484, 1712, 2030, 2221, 2408, 2761, 2837, 2963, 2966, 2984, 3043, 3059, 3110, 3265, 3365, 3486, 3762, 3997, 4064, 4097, 4254, 4269, 4274, 4526, 4582, 4736, 4743, 4837, 4838, 4841, 4844, 4865, 35, 162, 258, 343, 417, 477, 709, 860, 1186, 1259, 1297, 1308, 1645, 1675, 1927, 1995, 2084, 2167, 2194, 2217, 2260, 2320, 2346, 2484, 2581, 2585, 2659, 2786, 2817, 2842, 2868, 2938, 2989, 3103, 3136, 3201, 3301, 3427, 3486, 3513, 3738, 3790, 3802, 3886, 4091, 4092, 4213, 4284, 4440, 4515, 4633, 4774, 4831, 4882, 4894, 4960, 4968, 4982, 5021, 5100, 29, 83, 99, 151, 212, 251, 291, 296, 310, 313, 318, 481, 625, 635, 846, 1008, 1029, 1054, 1064, 1220, 1323, 1331, 1396, 1432, 1445, 1503, 1525, 1549, 1575, 1622, 1664, 1707, 1755, 1986, 2020, 2030, 2058, 2131, 2170, 2211, 2220, 2222, 2247, 2264, 2266, 2295, 2306, 2355, 2362, 2410, 2427, 2494, 2554, 2615, 2630, 2636, 2650, 2690, 2704, 2718, 2727, 2766, 2779, 2846, 2876, 2890, 3015, 3099, 3102, 3103, 3108, 3111, 3179, 3190, 3247, 3273, 3290, 3305, 3339, 3345, 3367, 3477, 3570, 3652, 3847, 3891, 3903, 3908, 3923, 3972, 4029, 4048, 4074, 4095, 4183, 4199, 4206, 4213, 4296, 4299, 4359, 4376, 4448, 4490, 4527, 4572, 4575, 4597, 4699, 4709, 4711, 4844, 4876, 4892, 4978, 4985, 5032, 5039, 5055, 5096, 5134, 5168, 64, 81, 144, 332, 396, 504, 652, 680, 771, 866, 987, 1171, 1303, 1441, 1496, 1502, 1544, 2084, 2121, 2170, 2266, 2293, 2339, 2526, 2528, 2583, 2590, 2662, 2696, 2868, 3016, 3033, 3051, 3292, 3340, 3365, 3563, 3574, 3918, 4022, 4042, 4075, 4079, 4135, 4201, 4303, 4456, 4501, 4553, 4667, 4821, 4879, 4883, 4948, 5103, 5104, 93, 111, 122, 169, 209, 210, 211, 218, 226, 238, 309, 323, 376, 385, 405, 427, 481, 488, 517, 555, 577, 584, 595, 608, 621, 642, 646, 658, 687, 712, 727, 773, 785, 829, 846, 848, 870, 933, 941, 966, 971, 985, 1024, 1037, 1073, 1105, 1147, 1217, 1233, 1259, 1275, 1323, 1364, 1374, 1409, 1443, 1453, 1479, 1480, 1514, 1559, 1567, 1596, 1649, 1654, 1675, 1691, 1720, 1780, 1804, 1810, 1834, 1868, 1874, 1885, 1905, 1944, 1945, 1948, 2049, 2061, 2063, 2070, 2088, 2093, 2126, 2223, 2239, 2268, 2271, 2327, 2489, 2560, 2590, 2624, 2685, 2700, 2724, 2756, 2766, 2843, 2848, 2857, 2879, 2919, 2933, 2935, 2954, 2964, 2997, 3029, 3043, 3070, 3084, 3099, 3108, 3111, 3116, 3146, 3157, 3237, 3264, 3356, 3391, 3397, 3457, 3472, 3478, 3504, 3541, 3570, 3582, 3660, 3701, 3740, 3746, 3795, 3821, 3827, 3875, 3884, 3912, 3929, 3934, 3970, 4028, 4074, 4091, 4103, 4162, 4170, 4200, 4201, 4206, 4214, 4256, 4260, 4286, 4306, 4382, 4388, 4413, 4429, 4439, 4533, 4541, 4550, 4633, 4661, 4668, 4705, 4713, 4726, 4769, 4784, 4870, 4886, 4928, 4948, 4994, 5027, 5043, 5057, 5097, 5113, 5123, 5124, 5138, 5156, 5163, 5168, 5170, 5172, 137, 142, 270, 363, 427, 460, 467, 590, 642, 681, 725, 744, 769, 808, 927, 998, 1016, 1024, 1041, 1045, 1051, 1098, 1108, 1172, 1233, 1290, 1325, 1342, 1374, 1378, 1441, 1463, 1538, 1546, 1565, 1570, 1645, 1678, 1799, 1810, 1814, 2036, 2129, 2147, 2149, 2426, 2431, 2541, 2572, 2697, 2717, 2736, 2820, 2870, 2890, 3244, 3249, 3339, 3367, 3375, 3396, 3437, 3472, 3481, 3498, 3663, 3708, 3727, 3769, 3811, 3875, 4028, 4076, 4091, 4103, 4122, 4222, 4226, 4312, 4449, 4550, 4624, 4733, 4787, 4811, 4814, 4816, 4857, 4967, 5094, 416, 499, 529, 549, 728, 1494, 2029, 2264, 2498, 2855, 3015, 3190, 3201, 3276, 3407, 3416, 3458, 3614, 3696, 3751, 4204, 4299, 838, 1064, 1108, 1575, 1621, 4482, 4493, 4601, 4827, 5157, 280, 291, 552, 1520, 1818, 1847, 1971, 2722, 2768, 3863, 2127, 2377, 2939, 3007, 4646, 5157, 35, 96, 256, 336, 348, 415, 443, 460, 554, 564, 685, 795, 796, 848, 875, 963, 982, 1013, 1052, 1067, 1100, 1176, 1305, 1469, 1613, 1616, 1764, 1816, 1834, 1890, 2083, 2108, 2206, 2210, 2225, 2349, 2394, 2473, 2864, 2907, 2915, 2993, 3026, 3076, 3087, 3143, 3158, 3284, 3318, 3457, 3503, 3582, 3627, 3688, 3765, 3913, 3928, 4032, 4042, 4087, 4103, 4111, 4113, 4135, 4200, 4201, 4240, 4271, 4425, 4528, 4549, 4561, 4565, 4615, 4752, 4850, 4940, 5094, 5156, 5159, 5169, 289, 1246, 2259, 3122, 4140, 814, 1604, 1668, 3020, 3880, 10, 47, 137, 266, 273, 464, 557, 566, 810, 1040, 1353, 1457, 1860, 1931, 2084, 2418, 2456, 2613, 2649, 2791, 3051, 3301, 3397, 3531, 3652, 3687, 3706, 3822, 3996, 4039, 4052, 4188, 4204, 4256, 4748, 5100, 168, 1570, 2149, 2167, 2555, 3974, 4899, 113, 273, 432, 481, 524, 554, 644, 682, 763, 971, 1040, 1087, 1348, 1409, 1489, 1514, 1532, 1567, 1579, 1609, 1612, 1721, 1851, 2042, 2068, 2085, 2097, 2271, 2583, 2672, 2717, 2738, 3149, 3334, 3619, 3836, 3851, 4207, 4278, 4481, 4506, 4542, 4750, 4976, 5134, 5149, 3917, 3968, 4055, 138, 191, 424, 1245, 1351, 1507, 1629, 1704, 1928, 2090, 2149, 2416, 2563, 2580, 2697, 3059, 3284, 3547, 3577, 3800, 4141, 4144, 4235, 4256, 4348, 4417, 4430, 4506, 4615, 4640, 4682, 4845, 4914, 4942, 4976, 4986, 48, 83, 137, 175, 202, 318, 329, 347, 350, 378, 524, 534, 570, 589, 592, 616, 680, 797, 800, 826, 1040, 1048, 1058, 1073, 1101, 1216, 1289, 1306, 1321, 1405, 1426, 1517, 1518, 1636, 1654, 1834, 1889, 1938, 2020, 2053, 2087, 2088, 2112, 2168, 2352, 2367, 2451, 2469, 2476, 2554, 2610, 2624, 2629, 2738, 2776, 2928, 2949, 2977, 2997, 3029, 3063, 3087, 3099, 3102, 3114, 3135, 3249, 3282, 3306, 3356, 3422, 3427, 3478, 3502, 3559, 3590, 3706, 3708, 3733, 3738, 3822, 3938, 3971, 3979, 4089, 4193, 4226, 4270, 4459, 4498, 4503, 4515, 4546, 4584, 4676, 4723, 4763, 4768, 4839, 4881, 4960, 5001, 0, 10, 48, 89, 99, 107, 119, 121, 137, 151, 174, 224, 271, 291, 317, 343, 379, 392, 458, 499, 523, 539, 554, 589, 593, 617, 621, 627, 643, 769, 803, 830, 851, 875, 891, 1001, 1006, 1081, 1087, 1137, 1138, 1183, 1220, 1245, 1304, 1323, 1325, 1331, 1340, 1358, 1381, 1402, 1457, 1496, 1567, 1615, 1626, 1634, 1648, 1674, 1712, 1729, 1769, 1774, 1801, 1843, 1898, 1906, 1948, 2020, 2031, 2040, 2070, 2084, 2133, 2153, 2193, 2194, 2239, 2264, 2296, 2326, 2345, 2354, 2391, 2465, 2476, 2591, 2597, 2617, 2623, 2627, 2649, 2759, 2760, 2818, 2841, 2842, 2877, 2884, 2903, 2917, 2919, 2933, 2997, 3029, 3043, 3074, 3080, 3085, 3124, 3125, 3179, 3187, 3198, 3230, 3240, 3248, 3265, 3320, 3322, 3339, 3428, 3478, 3479, 3529, 3617, 3663, 3682, 3708, 3767, 3769, 3821, 3870, 3884, 3893, 3915, 3950, 3955, 3968, 4025, 4067, 4074, 4079, 4094, 4097, 4103, 4250, 4260, 4346, 4404, 4409, 4479, 4482, 4500, 4612, 4664, 4682, 4696, 4709, 4714, 4816, 4931, 4944, 5001, 5014, 5055, 5087, 5165, 26, 74, 112, 163, 251, 314, 422, 523, 538, 642, 678, 828, 830, 906, 926, 941, 999, 1030, 1037, 1048, 1131, 1220, 1253, 1273, 1394, 1494, 1499, 1512, 1557, 1570, 1575, 1596, 1602, 1633, 1771, 1854, 1904, 1913, 1928, 1951, 1995, 2100, 2150, 2248, 2254, 2280, 2435, 2494, 2501, 2597, 2598, 2742, 2776, 2810, 2824, 2842, 2843, 2849, 2907, 2929, 2934, 3040, 3043, 3306, 3369, 3386, 3390, 3410, 3534, 3751, 3755, 3858, 3862, 3872, 3929, 4000, 4118, 4154, 4206, 4257, 4283, 4286, 4350, 4480, 4535, 4574, 4582, 4961, 4966, 4979, 5009, 5089, 5106, 10, 142, 395, 452, 546, 610, 658, 695, 800, 1095, 1119, 1143, 1187, 1298, 1381, 1535, 1615, 1646, 1727, 1776, 1803, 1922, 2038, 2040, 2082, 2121, 2145, 2198, 2226, 2430, 2524, 2587, 2786, 2827, 2856, 2864, 3043, 3400, 3445, 3473, 3513, 3553, 3560, 3577, 3667, 3724, 3878, 3914, 4105, 4111, 4408, 4418, 4430, 4439, 4459, 4542, 4748, 4750, 4779, 4845, 4968, 4999, 5007, 5025, 5055, 5146, 10, 33, 123, 131, 134, 169, 225, 235, 309, 386, 563, 630, 635, 681, 720, 797, 800, 947, 1025, 1060, 1306, 1404, 1539, 1559, 1607, 1622, 1635, 1758, 1780, 1845, 2096, 2175, 2225, 2227, 2239, 2267, 2471, 2481, 2493, 2555, 2638, 2720, 2745, 2772, 2877, 2916, 2939, 2993, 3008, 3011, 3190, 3260, 3345, 3422, 3534, 3593, 3696, 3920, 4012, 4029, 4057, 4065, 4234, 4318, 4334, 4385, 4396, 4434, 4515, 4535, 4554, 4567, 4612, 4625, 4715, 4726, 4769, 4786, 4801, 4849, 4909, 5014, 5039, 5079, 37, 85, 224, 225, 229, 238, 280, 285, 305, 395, 458, 689, 703, 752, 763, 768, 777, 801, 822, 969, 971, 1060, 1073, 1149, 1186, 1189, 1244, 1260, 1456, 1463, 1565, 1640, 1681, 1855, 1867, 1911, 1946, 1997, 2051, 2056, 2173, 2225, 2259, 2386, 2389, 2582, 2606, 2633, 2698, 2717, 2764, 2794, 2806, 2814, 2846, 2851, 2917, 2935, 3011, 3028, 3093, 3116, 3244, 3323, 3347, 3356, 3358, 3423, 3512, 3514, 3596, 3681, 3690, 3702, 3790, 3875, 3886, 3957, 4006, 4213, 4306, 4406, 4459, 4471, 4481, 4545, 4623, 4659, 4669, 4705, 4761, 4797, 4798, 4824, 4843, 4857, 4874, 4910, 4966, 4984, 5007, 5039, 79, 195, 221, 283, 289, 446, 499, 509, 590, 616, 747, 758, 832, 846, 1067, 1115, 1174, 1176, 1218, 1236, 1241, 1253, 1321, 1373, 1427, 1514, 1537, 1590, 1612, 1816, 1833, 1834, 1874, 1954, 2111, 2300, 2331, 2349, 2524, 2616, 2617, 2717, 2765, 2970, 3118, 3177, 3286, 3292, 3306, 3318, 3350, 3436, 3473, 3594, 3663, 3825, 3847, 3954, 3988, 4096, 4163, 4311, 4367, 4565, 4676, 4831, 4879, 4971, 4985, 5002, 5040, 373, 490, 534, 546, 705, 747, 751, 776, 830, 990, 1054, 1155, 1196, 1204, 1244, 1350, 1429, 1497, 1692, 1796, 1847, 1938, 1967, 2106, 2265, 2344, 2418, 2495, 2672, 2718, 2759, 2827, 2872, 2916, 3041, 3136, 3265, 3522, 3684, 3912, 4006, 4025, 4053, 4260, 4384, 4525, 4527, 4554, 4895, 4905, 4988, 5144, 5163, 104, 160, 166, 209, 229, 297, 318, 375, 378, 404, 460, 557, 629, 646, 672, 681, 813, 1016, 1025, 1029, 1032, 1052, 1105, 1124, 1128, 1171, 1195, 1205, 1218, 1220, 1350, 1466, 1499, 1522, 1525, 1538, 1604, 1664, 1668, 1678, 1704, 1771, 1786, 1793, 1928, 1944, 2042, 2080, 2206, 2210, 2223, 2311, 2320, 2371, 2394, 2490, 2493, 2561, 2564, 2704, 2780, 2828, 2888, 2897, 2954, 3000, 3016, 3079, 3227, 3273, 3277, 3396, 3397, 3429, 3461, 3493, 3512, 3513, 3520, 3555, 3582, 3666, 3672, 3682, 3697, 3698, 3746, 3793, 3807, 3808, 3816, 3825, 3851, 3908, 3957, 4065, 4095, 4134, 4284, 4294, 4349, 4412, 4529, 4541, 4571, 4605, 4633, 4640, 4657, 4660, 4676, 4709, 4742, 4767, 4793, 4867, 4883, 4988, 5013, 5018, 5024, 5034, 5045, 5103, 191, 233, 248, 592, 616, 645, 744, 758, 829, 916, 934, 979, 1383, 1404, 1427, 1514, 1588, 1615, 1683, 1867, 1885, 2057, 2061, 2323, 2327, 2371, 2597, 2609, 2674, 2809, 2891, 2892, 3080, 3120, 3235, 3294, 3326, 3363, 3513, 3582, 3604, 3699, 3724, 3971, 4012, 4148, 4188, 4240, 4300, 4345, 4361, 4593, 4601, 4633, 4657, 4690, 4697, 4814, 5043, 19, 92, 144, 170, 177, 224, 226, 232, 248, 360, 365, 385, 395, 536, 555, 556, 600, 618, 642, 696, 725, 727, 783, 808, 829, 846, 902, 926, 948, 966, 974, 1030, 1047, 1058, 1121, 1150, 1183, 1207, 1218, 1220, 1236, 1253, 1321, 1337, 1351, 1352, 1427, 1546, 1567, 1569, 1574, 1688, 1721, 1722, 1793, 1814, 1870, 1919, 1939, 2064, 2082, 2090, 2130, 2154, 2185, 2224, 2321, 2325, 2340, 2355, 2391, 2394, 2408, 2444, 2471, 2514, 2523, 2545, 2555, 2563, 2577, 2609, 2613, 2617, 2653, 2698, 2714, 2721, 2758, 2763, 2820, 2843, 2916, 2922, 2963, 2977, 3034, 3054, 3063, 3066, 3085, 3099, 3100, 3118, 3137, 3190, 3210, 3234, 3282, 3323, 3326, 3348, 3369, 3372, 3389, 3435, 3437, 3439, 3450, 3454, 3458, 3484, 3494, 3520, 3598, 3605, 3613, 3641, 3652, 3696, 3768, 3808, 3813, 3815, 3821, 3861, 3880, 3912, 3918, 4019, 4040, 4087, 4092, 4095, 4171, 4208, 4317, 4350, 4361, 4394, 4406, 4408, 4502, 4511, 4544, 4549, 4569, 4584, 4669, 4672, 4697, 4702, 4731, 4738, 4816, 4827, 4851, 4873, 4946, 4985, 5007, 5013, 5022, 5065, 5170, 323, 524, 891, 941, 1818, 2537, 2569, 2841, 2890, 3532, 3635, 4048, 4117, 4122, 4187, 4961, 5059, 5099, 175, 4359, 7, 37, 75, 95, 107, 108, 112, 160, 283, 318, 369, 376, 392, 412, 423, 457, 458, 479, 526, 549, 557, 598, 604, 635, 680, 701, 728, 747, 756, 875, 883, 885, 890, 910, 944, 963, 971, 985, 1041, 1070, 1083, 1098, 1131, 1233, 1260, 1273, 1340, 1353, 1433, 1448, 1463, 1473, 1490, 1531, 1545, 1546, 1551, 1610, 1623, 1645, 1665, 1711, 1722, 1729, 1735, 1777, 1811, 1819, 1834, 1847, 1854, 1873, 1912, 1922, 1945, 1947, 2003, 2044, 2049, 2072, 2108, 2173, 2184, 2225, 2335, 2350, 2408, 2465, 2471, 2552, 2577, 2616, 2682, 2700, 2727, 2832, 2855, 2857, 2861, 2885, 2898, 2905, 2922, 3072, 3150, 3173, 3177, 3198, 3207, 3273, 3286, 3292, 3305, 3306, 3356, 3386, 3400, 3523, 3527, 3528, 3594, 3681, 3732, 3814, 3843, 3880, 3886, 3974, 4011, 4047, 4049, 4058, 4074, 4081, 4095, 4189, 4207, 4226, 4228, 4238, 4251, 4254, 4257, 4300, 4317, 4323, 4327, 4418, 4440, 4449, 4485, 4493, 4508, 4524, 4545, 4574, 4597, 4628, 4647, 4650, 4660, 4688, 4691, 4700, 4707, 4715, 4738, 4740, 4754, 4767, 4768, 4787, 4865, 4876, 4879, 4893, 4955, 5013, 5023, 5075, 5087, 5099, 5121, 5126, 5144, 32, 35, 37, 162, 271, 290, 320, 428, 592, 671, 710, 796, 870, 923, 971, 974, 988, 998, 1013, 1060, 1066, 1111, 1135, 1241, 1244, 1271, 1323, 1337, 1367, 1401, 1406, 1455, 1530, 1565, 1625, 1660, 1664, 1683, 1704, 1723, 1847, 1855, 1872, 1907, 1932, 1991, 2024, 2031, 2036, 2288, 2298, 2346, 2419, 2526, 2565, 2606, 2609, 2617, 2671, 2674, 2694, 2833, 2846, 2851, 2864, 2919, 2954, 2985, 3040, 3041, 3050, 3116, 3315, 3323, 3490, 3557, 3566, 3579, 3606, 3667, 3690, 3699, 3702, 3751, 3781, 3793, 3795, 3868, 3895, 4094, 4250, 4323, 4336, 4382, 4384, 4412, 4549, 4586, 4629, 4653, 4764, 4771, 4789, 4831, 4864, 4870, 4874, 4938, 4989, 5045, 5079, 60, 95, 145, 209, 224, 257, 258, 511, 538, 550, 553, 585, 600, 752, 971, 1044, 1176, 1202, 1313, 1407, 1443, 1466, 1477, 1514, 1646, 1664, 1729, 1954, 2476, 2569, 2660, 2734, 2854, 3526, 3534, 3962, 4058, 4126, 4134, 4213, 4257, 4350, 4356, 4431, 4789, 4805, 4817, 4843, 4970, 4971, 5057, 2423, 2829, 3063, 4098, 2083, 2259, 4533, 138, 177, 266, 288, 313, 345, 396, 500, 645, 651, 677, 723, 747, 773, 796, 814, 827, 844, 848, 919, 969, 974, 982, 1029, 1091, 1096, 1122, 1149, 1206, 1325, 1381, 1394, 1426, 1455, 1529, 1532, 1712, 1797, 1810, 1847, 1892, 1997, 2004, 2085, 2234, 2267, 2337, 2351, 2382, 2384, 2425, 2494, 2542, 2555, 2617, 2659, 2662, 2686, 2745, 2749, 2893, 2905, 3060, 3146, 3363, 3522, 3527, 3581, 3609, 3656, 3690, 3701, 3775, 3777, 3903, 4017, 4030, 4052, 4060, 4117, 4291, 4311, 4331, 4373, 4384, 4459, 4488, 4531, 4742, 4759, 4817, 4894, 4900, 4912, 5025, 5050, 5080, 5144, 5161, 106, 217, 244, 379, 517, 536, 550, 595, 646, 715, 743, 833, 1189, 1278, 1546, 1570, 1575, 1640, 1642, 1820, 1863, 1868, 1995, 2051, 2054, 2074, 2172, 2188, 2194, 2213, 2316, 2391, 2395, 2470, 2609, 2700, 2824, 2846, 2849, 2919, 3071, 3112, 3116, 3158, 3225, 3272, 3345, 3362, 3364, 3372, 3392, 3406, 3439, 3472, 3682, 3748, 3795, 3845, 3893, 3932, 3953, 4122, 4233, 4303, 4384, 4466, 4557, 4586, 4603, 4699, 4738, 4752, 4798, 4828, 4838, 4936, 5040, 5099, 5110, 5115, 5164, 5170, 81, 235, 1273, 1539, 2768, 3364, 4576, 28, 1336, 3154, 3725, 4535, 2905, 20, 79, 151, 171, 226, 248, 266, 480, 525, 612, 690, 701, 810, 827, 848, 851, 990, 1025, 1028, 1035, 1056, 1064, 1066, 1135, 1146, 1219, 1233, 1290, 1302, 1329, 1331, 1451, 1497, 1569, 1588, 1637, 1641, 1732, 1759, 1814, 1831, 1835, 1836, 1985, 2025, 2027, 2096, 2293, 2325, 2347, 2373, 2726, 2819, 2913, 2981, 3020, 3126, 3280, 3307, 3438, 3478, 3610, 3659, 3696, 3740, 3814, 3832, 3861, 3962, 3971, 3976, 4006, 4034, 4082, 4251, 4300, 4406, 4413, 4488, 4498, 4545, 4637, 4640, 4708, 4729, 4805, 4893, 4920, 4925, 4936, 4968, 5062, 137, 240, 389, 416, 424, 443, 549, 617, 875, 1081, 1137, 1325, 1326, 1331, 1519, 1644, 1680, 1818, 1906, 2211, 2234, 2306, 2374, 2431, 2469, 2524, 2569, 2627, 2698, 2818, 2842, 2870, 2924, 2988, 2992, 3015, 3052, 3074, 3149, 3276, 3585, 3614, 3682, 3719, 3746, 4055, 4200, 4204, 4222, 4305, 4493, 4507, 4597, 4615, 4729, 4764, 4797, 5157, 5169, 93, 120, 446, 1210, 1367, 1467, 1490, 1598, 1649, 1704, 1732, 1826, 2737, 3073, 3116, 3255, 3549, 3714, 3822, 4144, 4164, 4337, 4449, 4690</t>
+    <t>96.81</t>
+  </si>
+  <si>
+    <t>5008</t>
+  </si>
+  <si>
+    <t>93, 287, 310, 375, 432, 852, 1205, 1302, 1564, 1613, 1735, 1834, 1997, 2042, 2425, 2460, 2465, 2708, 2782, 2849, 3270, 3273, 3513, 3531, 3968, 4000, 4002, 4262, 4354, 4563, 5024, 5032, 5106, 5112, 20, 567, 635, 827, 1336, 1524, 1932, 2451, 2585, 2764, 2993, 3066, 3659, 4187, 4423, 4657, 5136, 199, 297, 517, 549, 567, 640, 883, 1057, 1177, 1362, 1484, 1496, 1716, 1846, 1879, 1954, 2046, 2100, 2346, 2404, 2419, 2449, 2590, 2616, 2646, 2653, 2659, 2788, 2833, 2952, 3059, 3126, 3156, 3205, 3249, 3464, 3501, 3624, 3767, 4053, 4079, 4153, 4366, 4466, 4569, 4733, 5009, 5113, 79, 142, 177, 467, 517, 677, 721, 737, 751, 832, 979, 1060, 1077, 1171, 1236, 1348, 1479, 1503, 1509, 1531, 1570, 1610, 1669, 1719, 1820, 1831, 1874, 1878, 1905, 1940, 2012, 2027, 2250, 2316, 2356, 2413, 2427, 2470, 2511, 2672, 2806, 2809, 2864, 3020, 3033, 3184, 3225, 3280, 3308, 3313, 3468, 3474, 3513, 3681, 3708, 3845, 3851, 3862, 3866, 3895, 3931, 4037, 4123, 4206, 4250, 4320, 4359, 4366, 4402, 4478, 4586, 4596, 4661, 4686, 4714, 4752, 4789, 4793, 4912, 4931, 5040, 5089, 5138, 3, 6, 108, 116, 187, 199, 257, 286, 331, 332, 336, 357, 365, 411, 455, 507, 510, 546, 574, 606, 607, 608, 618, 629, 672, 712, 730, 751, 805, 852, 870, 880, 897, 917, 937, 944, 945, 1024, 1060, 1096, 1102, 1150, 1155, 1239, 1245, 1251, 1298, 1306, 1337, 1373, 1396, 1401, 1455, 1473, 1491, 1494, 1499, 1511, 1515, 1533, 1537, 1549, 1564, 1592, 1609, 1637, 1688, 1691, 1712, 1844, 1878, 1890, 1911, 1929, 1944, 1967, 2053, 2074, 2090, 2125, 2128, 2131, 2143, 2149, 2230, 2256, 2262, 2344, 2345, 2346, 2354, 2449, 2461, 2479, 2504, 2578, 2615, 2619, 2627, 2630, 2650, 2671, 2741, 2757, 2763, 2801, 2825, 2861, 2872, 2876, 2893, 2922, 2928, 2944, 2950, 2964, 2977, 2998, 3022, 3036, 3087, 3099, 3135, 3198, 3323, 3326, 3339, 3340, 3348, 3350, 3367, 3375, 3380, 3487, 3512, 3536, 3604, 3605, 3612, 3635, 3692, 3741, 3762, 3771, 3776, 3821, 3836, 3895, 3908, 3917, 3962, 4039, 4052, 4053, 4065, 4089, 4111, 4133, 4141, 4154, 4213, 4254, 4269, 4271, 4318, 4382, 4395, 4408, 4413, 4435, 4478, 4525, 4550, 4561, 4565, 4568, 4573, 4603, 4637, 4640, 4669, 4693, 4736, 4768, 4775, 4817, 4910, 4940, 4969, 4978, 5007, 5018, 5043, 5101, 5122, 287, 308, 320, 331, 446, 467, 519, 545, 604, 729, 1025, 1031, 1535, 1777, 1788, 1806, 1898, 1933, 1947, 1984, 2021, 2137, 2185, 2211, 2272, 2280, 2306, 2434, 2484, 2559, 2591, 2616, 2636, 2802, 2837, 2849, 2854, 2893, 2928, 2977, 3073, 3154, 3163, 3177, 3339, 3366, 3406, 3443, 3490, 3520, 3527, 3559, 3581, 3698, 3755, 3769, 3860, 3862, 3875, 4006, 4025, 4188, 4193, 4318, 4350, 4397, 4610, 4620, 4630, 4774, 4799, 4847, 4857, 4860, 4863, 4882, 4914, 4940, 5001, 5100, 5112, 5121, 5129, 14, 48, 89, 106, 119, 120, 230, 267, 271, 273, 287, 297, 344, 360, 398, 455, 484, 536, 581, 587, 640, 777, 778, 796, 827, 923, 933, 938, 947, 979, 987, 1037, 1046, 1056, 1064, 1084, 1091, 1102, 1111, 1115, 1137, 1172, 1187, 1195, 1216, 1233, 1248, 1275, 1298, 1304, 1308, 1321, 1367, 1372, 1406, 1465, 1531, 1564, 1570, 1612, 1623, 1741, 1831, 1861, 1867, 1886, 1894, 1911, 1917, 1922, 1925, 1931, 1967, 2031, 2044, 2063, 2068, 2083, 2087, 2108, 2126, 2221, 2222, 2239, 2264, 2283, 2295, 2302, 2340, 2358, 2384, 2540, 2553, 2576, 2595, 2627, 2651, 2746, 2780, 2781, 2800, 2818, 2824, 2919, 2929, 2967, 3018, 3050, 3061, 3069, 3085, 3125, 3225, 3245, 3248, 3267, 3279, 3315, 3320, 3334, 3369, 3372, 3439, 3479, 3501, 3577, 3590, 3627, 3658, 3705, 3707, 3724, 3766, 3813, 3860, 3868, 3886, 3892, 3915, 3950, 4006, 4052, 4087, 4096, 4097, 4111, 4251, 4259, 4294, 4323, 4395, 4408, 4467, 4480, 4568, 4591, 4625, 4653, 4733, 4754, 4799, 4827, 4843, 4859, 4882, 4985, 5025, 5043, 5094, 5108, 5121, 5124, 5164, 37, 106, 160, 169, 179, 209, 228, 230, 262, 348, 350, 392, 404, 460, 541, 550, 557, 584, 600, 610, 629, 668, 671, 684, 695, 715, 771, 810, 835, 869, 934, 1011, 1081, 1095, 1105, 1139, 1205, 1401, 1445, 1463, 1475, 1492, 1515, 1533, 1565, 1625, 1635, 1669, 1814, 1940, 1955, 1959, 1970, 2054, 2080, 2084, 2098, 2118, 2131, 2171, 2194, 2230, 2234, 2241, 2246, 2283, 2371, 2374, 2473, 2500, 2560, 2622, 2660, 2727, 2736, 2746, 2928, 2934, 3173, 3245, 3317, 3384, 3405, 3410, 3421, 3507, 3512, 3542, 3552, 3594, 3634, 3645, 3656, 3707, 3740, 3768, 3779, 3844, 3874, 3893, 3894, 3943, 4002, 4074, 4078, 4091, 4231, 4235, 4250, 4261, 4348, 4410, 4419, 4550, 4570, 4584, 4601, 4668, 4669, 4672, 4704, 4710, 4744, 4750, 4793, 4857, 4920, 5103, 5143, 57, 109, 240, 885, 905, 2056, 2241, 2377, 2722, 2977, 5014, 5147, 81, 345, 405, 1105, 1269, 1492, 1954, 2160, 2241, 2491, 2690, 2928, 3071, 3190, 3302, 3655, 3893, 4235, 4857, 5103, 107, 221, 229, 266, 587, 652, 709, 778, 890, 948, 1002, 1053, 1083, 1087, 1096, 1239, 1352, 1407, 1441, 1567, 1663, 1664, 1729, 1774, 1847, 1954, 1967, 2021, 2137, 2285, 2451, 2453, 2472, 2504, 2524, 2526, 2584, 2594, 2600, 2700, 2856, 2913, 2981, 3011, 3015, 3108, 3114, 3117, 3125, 3149, 3266, 3301, 3356, 3420, 3480, 3496, 3688, 3724, 3738, 3803, 3889, 3971, 3996, 4034, 4040, 4076, 4078, 4082, 4087, 4123, 4141, 4163, 4295, 4451, 4479, 4485, 4631, 4654, 4759, 4826, 4883, 5024, 0, 28, 46, 86, 90, 99, 107, 116, 233, 343, 353, 366, 481, 495, 504, 524, 555, 567, 584, 597, 600, 623, 635, 643, 644, 652, 689, 690, 714, 744, 905, 927, 988, 1008, 1024, 1032, 1098, 1120, 1128, 1160, 1187, 1197, 1205, 1211, 1267, 1269, 1323, 1350, 1425, 1477, 1512, 1537, 1648, 1654, 1712, 1720, 1735, 1780, 1816, 1831, 1890, 1904, 1928, 1947, 2047, 2054, 2069, 2125, 2178, 2222, 2226, 2235, 2253, 2260, 2265, 2289, 2408, 2418, 2453, 2469, 2475, 2494, 2570, 2580, 2682, 2734, 2765, 2809, 2824, 2841, 2868, 2892, 2903, 2916, 2934, 2985, 2989, 3020, 3036, 3147, 3296, 3308, 3337, 3388, 3399, 3401, 3406, 3439, 3479, 3498, 3547, 3549, 3599, 3604, 3609, 3619, 3624, 3627, 3663, 3674, 3701, 3771, 3795, 3849, 3911, 3963, 3975, 4012, 4074, 4092, 4134, 4149, 4154, 4193, 4247, 4260, 4265, 4269, 4303, 4346, 4402, 4419, 4546, 4568, 4619, 4623, 4625, 4654, 4726, 4748, 4750, 4827, 4847, 4960, 4999, 5032, 5096, 5097, 5110, 5126, 5136, 5138, 5147, 308, 1032, 2210, 2250, 2714, 3276, 3552, 3908, 4317, 33, 47, 57, 90, 95, 109, 283, 309, 320, 325, 363, 369, 412, 508, 572, 590, 640, 645, 727, 737, 768, 792, 913, 930, 933, 967, 974, 982, 999, 1051, 1058, 1121, 1367, 1511, 1633, 1692, 1712, 1735, 1741, 1766, 1767, 1820, 1849, 1874, 1880, 1898, 1922, 1978, 1988, 2029, 2054, 2057, 2084, 2168, 2244, 2268, 2288, 2295, 2316, 2324, 2344, 2360, 2397, 2403, 2475, 2523, 2540, 2622, 2649, 2652, 2704, 2755, 2779, 2892, 2897, 2952, 2963, 2967, 3011, 3033, 3036, 3061, 3143, 3144, 3227, 3235, 3244, 3266, 3290, 3293, 3331, 3356, 3383, 3396, 3456, 3457, 3464, 3522, 3529, 3557, 3574, 3652, 3663, 3669, 3751, 3793, 3971, 4017, 4033, 4067, 4103, 4126, 4163, 4188, 4222, 4240, 4250, 4272, 4348, 4350, 4366, 4406, 4423, 4510, 4531, 4619, 4631, 4673, 4690, 4726, 4748, 4786, 4814, 4873, 4899, 4922, 5025, 5032, 5080, 5158, 0, 14, 47, 63, 90, 93, 102, 131, 137, 142, 152, 175, 177, 199, 219, 221, 290, 299, 392, 418, 489, 497, 517, 632, 672, 701, 760, 838, 872, 915, 919, 927, 1038, 1057, 1058, 1194, 1204, 1211, 1259, 1298, 1321, 1351, 1451, 1496, 1518, 1559, 1603, 1629, 1645, 1678, 1723, 1735, 1769, 1782, 1811, 1829, 1853, 1880, 1894, 1905, 1927, 1941, 1978, 2018, 2128, 2158, 2166, 2210, 2213, 2217, 2223, 2226, 2289, 2321, 2345, 2351, 2355, 2395, 2435, 2451, 2490, 2553, 2581, 2597, 2612, 2622, 2629, 2654, 2718, 2723, 2731, 2788, 2807, 2825, 2843, 2861, 2890, 2915, 2926, 2935, 2950, 2981, 2983, 2988, 3007, 3127, 3157, 3225, 3248, 3277, 3280, 3296, 3302, 3348, 3366, 3388, 3443, 3445, 3461, 3477, 3547, 3550, 3602, 3610, 3644, 3699, 3718, 3746, 3768, 3815, 3833, 3854, 3979, 4029, 4047, 4094, 4095, 4105, 4133, 4152, 4193, 4294, 4353, 4365, 4381, 4396, 4410, 4423, 4506, 4510, 4531, 4563, 4574, 4597, 4653, 4670, 4688, 4699, 4738, 4775, 4787, 4831, 4852, 4857, 4865, 4870, 4913, 4964, 4969, 4978, 5016, 5027, 5033, 5043, 5046, 5096, 5101, 5112, 5123, 5165, 19, 37, 74, 211, 225, 273, 336, 348, 410, 522, 538, 577, 650, 652, 952, 958, 1137, 1138, 1166, 1187, 1538, 1544, 1555, 1559, 1570, 1646, 1693, 1697, 1712, 1719, 1820, 1880, 1922, 1991, 2168, 2223, 2239, 2244, 2292, 2397, 2540, 2606, 2637, 2726, 2816, 2827, 2981, 3207, 3235, 3244, 3292, 3383, 3388, 3391, 3423, 3545, 3663, 3707, 3861, 3945, 3976, 4039, 4133, 4142, 4217, 4287, 4303, 4523, 4603, 4713, 4733, 4775, 4805, 4874, 4900, 4910, 4920, 4928, 4967, 4970, 4986, 5022, 5089, 24, 75, 118, 186, 233, 238, 258, 318, 360, 398, 796, 952, 1059, 1095, 1188, 1280, 1360, 1465, 1522, 1777, 2042, 2056, 2118, 2143, 2158, 2321, 2395, 2460, 2557, 2581, 2681, 2736, 2986, 3112, 3122, 3137, 3155, 3214, 3241, 3302, 3334, 3356, 3429, 3445, 3501, 3570, 3594, 3644, 4030, 4223, 4354, 4396, 4507, 4544, 4563, 4574, 4646, 4738, 4744, 4895, 4968, 5034, 36, 111, 229, 234, 273, 422, 423, 462, 525, 536, 564, 610, 627, 748, 795, 801, 826, 854, 866, 880, 905, 999, 1002, 1052, 1083, 1092, 1124, 1155, 1212, 1268, 1285, 1409, 1545, 1634, 1667, 1671, 1722, 1770, 1782, 1793, 1796, 1837, 1845, 1874, 1922, 2012, 2018, 2050, 2082, 2106, 2145, 2162, 2226, 2275, 2300, 2311, 2423, 2453, 2461, 2519, 2523, 2559, 2590, 2606, 2648, 2652, 2718, 2742, 2856, 2876, 2915, 2944, 2985, 3011, 3042, 3052, 3087, 3115, 3207, 3209, 3283, 3302, 3367, 3605, 3645, 3827, 3912, 3968, 4064, 4076, 4206, 4221, 4226, 4320, 4327, 4334, 4431, 4541, 4592, 4620, 4630, 4702, 4703, 4735, 4775, 4779, 4928, 4944, 5009, 5163, 31, 131, 585, 734, 831, 1042, 1058, 1451, 1489, 1581, 1782, 1799, 1948, 1996, 2018, 2173, 2508, 2537, 2541, 2597, 2716, 2718, 2722, 2975, 3068, 3449, 3816, 4060, 4119, 4171, 4439, 4526, 4563, 4572, 4669, 4708, 4729, 4810, 4813, 4883, 5025, 5046, 5094, 5117, 0, 93, 123, 218, 229, 256, 263, 291, 329, 435, 446, 481, 511, 522, 524, 549, 555, 577, 603, 607, 645, 660, 682, 948, 1060, 1076, 1086, 1215, 1244, 1394, 1549, 1660, 1689, 1711, 1828, 1881, 1905, 1919, 1987, 1995, 2069, 2116, 2210, 2247, 2362, 2404, 2413, 2415, 2501, 2534, 2561, 2629, 2837, 2849, 2933, 2967, 3008, 3054, 3126, 3212, 3318, 3337, 3397, 3513, 3594, 3624, 3666, 3719, 3755, 3908, 4051, 4079, 4087, 4119, 4147, 4171, 4199, 4316, 4353, 4385, 4389, 4498, 4506, 4513, 4710, 4821, 4994, 5057, 5112, 549, 938, 1248, 1801, 2085, 2247, 2415, 3008, 3464, 3624, 4754, 5112, 69, 145, 158, 263, 273, 283, 320, 332, 375, 482, 682, 709, 1090, 1136, 1201, 1236, 1248, 1469, 1648, 1759, 1763, 1776, 1786, 1797, 1821, 1826, 2054, 2055, 2080, 2116, 2117, 2268, 2289, 2302, 2399, 2408, 2426, 2449, 2479, 2536, 2600, 2615, 2653, 2696, 2716, 2755, 2761, 2978, 2981, 2985, 2988, 3000, 3120, 3125, 3165, 3179, 3362, 3363, 3423, 3645, 3795, 3808, 3832, 3836, 3923, 4039, 4040, 4181, 4218, 4231, 4250, 4259, 4316, 4336, 4467, 4520, 4539, 4586, 4650, 4690, 4700, 4711, 4767, 4864, 4900, 4946, 5034, 5042, 5050, 5085, 5109, 5112, 5138, 46, 85, 90, 95, 96, 167, 478, 589, 630, 699, 778, 830, 831, 866, 896, 933, 976, 1029, 1042, 1051, 1065, 1096, 1171, 1210, 1318, 1333, 1459, 1477, 1503, 1507, 1524, 1592, 1780, 1858, 1898, 2002, 2051, 2173, 2230, 2248, 2352, 2373, 2391, 2522, 2545, 2559, 2561, 2624, 2638, 2874, 3217, 3319, 3346, 3360, 3400, 3437, 3448, 3478, 3487, 3526, 3534, 3594, 3687, 3962, 4028, 4065, 4171, 4233, 4291, 4294, 4323, 4526, 4563, 4739, 4863, 4876, 4971, 4977, 5027, 5104, 89, 271, 338, 360, 777, 1205, 1321, 1463, 1623, 1984, 2320, 2786, 3230, 3245, 3248, 3705, 3861, 4653, 4750, 4783, 4843, 4857, 4931, 35, 199, 209, 227, 263, 290, 329, 353, 357, 400, 424, 481, 545, 608, 672, 696, 700, 705, 787, 792, 814, 851, 923, 987, 998, 1016, 1032, 1086, 1189, 1211, 1331, 1333, 1342, 1498, 1524, 1539, 1603, 1659, 1664, 1776, 1793, 1898, 1931, 1996, 2043, 2072, 2080, 2117, 2150, 2183, 2198, 2221, 2239, 2267, 2423, 2528, 2553, 2758, 2766, 2820, 2923, 2954, 3045, 3084, 3093, 3098, 3144, 3156, 3214, 3229, 3270, 3334, 3400, 3445, 3498, 3532, 3557, 3645, 3655, 3699, 3719, 3817, 3870, 3889, 3928, 3932, 3966, 4011, 4058, 4105, 4193, 4226, 4334, 4431, 4435, 4451, 4482, 4528, 4597, 4648, 4740, 4784, 4793, 4909, 4988, 5023, 5032, 5051, 5073, 5124, 5138, 28, 73, 75, 90, 112, 122, 137, 142, 225, 320, 410, 423, 545, 565, 604, 642, 682, 701, 725, 756, 809, 863, 1016, 1051, 1180, 1189, 1210, 1378, 1525, 1535, 1545, 1569, 1570, 1720, 1723, 1769, 1782, 1799, 1807, 1905, 2018, 2040, 2042, 2063, 2130, 2211, 2266, 2326, 2331, 2362, 2483, 2561, 2564, 2582, 2650, 2660, 2714, 2814, 2970, 2978, 3122, 3125, 3249, 3391, 3484, 3513, 3588, 3597, 3660, 3717, 3748, 3769, 3851, 3875, 4042, 4057, 4065, 4163, 4172, 4193, 4262, 4412, 4448, 4453, 4467, 4550, 4593, 4693, 4784, 4814, 4905, 4944, 4969, 4983, 5059, 5112, 5143, 5168, 411, 446, 577, 607, 715, 933, 982, 1042, 1351, 1515, 1689, 1806, 2494, 2849, 3284, 3484, 3569, 3997, 4418, 4669, 4743, 4887, 5046, 28, 107, 299, 660, 838, 1037, 1076, 1168, 1234, 1463, 1552, 1728, 1986, 2030, 2042, 2226, 2395, 2398, 2856, 3725, 3825, 3833, 4002, 4051, 4141, 4213, 4216, 4340, 4385, 4408, 4523, 4733, 4828, 4909, 5025, 5106, 32, 73, 74, 99, 121, 168, 287, 338, 366, 389, 392, 418, 443, 460, 462, 642, 727, 769, 813, 828, 860, 872, 933, 934, 959, 1158, 1177, 1212, 1260, 1290, 1502, 1567, 1641, 1690, 1759, 1796, 1807, 1839, 1847, 1855, 1894, 1912, 2038, 2061, 2128, 2144, 2183, 2353, 2490, 2493, 2514, 2555, 2582, 2680, 2706, 2801, 2824, 2837, 2949, 2981, 2995, 3008, 3026, 3060, 3070, 3118, 3161, 3184, 3276, 3326, 3391, 3397, 3461, 3474, 3576, 3658, 3831, 3836, 3872, 3880, 3916, 4155, 4259, 4354, 4359, 4385, 4563, 4618, 4669, 4690, 4717, 4844, 5021, 5108, 5113, 5169, 89, 151, 210, 555, 776, 880, 913, 979, 1011, 1103, 1115, 1372, 1484, 1712, 2030, 2221, 2408, 2761, 2837, 2963, 2966, 2984, 3043, 3059, 3110, 3265, 3365, 3486, 3762, 3997, 4064, 4097, 4254, 4269, 4274, 4526, 4582, 4736, 4743, 4837, 4838, 4841, 4844, 4865, 35, 162, 258, 343, 417, 477, 709, 860, 1186, 1259, 1297, 1308, 1645, 1675, 1927, 1995, 2084, 2167, 2194, 2217, 2260, 2320, 2346, 2484, 2581, 2585, 2659, 2786, 2817, 2842, 2868, 2938, 2989, 3103, 3136, 3201, 3301, 3427, 3486, 3513, 3738, 3790, 3802, 3886, 4091, 4092, 4213, 4284, 4440, 4515, 4633, 4774, 4831, 4882, 4894, 4960, 4968, 4982, 5021, 5100, 29, 83, 99, 151, 212, 251, 291, 296, 310, 313, 318, 481, 625, 635, 846, 1008, 1029, 1054, 1064, 1220, 1323, 1331, 1396, 1432, 1445, 1503, 1525, 1549, 1575, 1622, 1664, 1707, 1755, 1986, 2020, 2030, 2058, 2131, 2170, 2211, 2220, 2222, 2247, 2264, 2266, 2295, 2306, 2355, 2362, 2410, 2427, 2494, 2554, 2615, 2630, 2636, 2650, 2690, 2704, 2718, 2727, 2766, 2779, 2846, 2876, 2890, 3015, 3099, 3102, 3103, 3108, 3111, 3179, 3190, 3247, 3273, 3290, 3305, 3339, 3345, 3367, 3477, 3570, 3652, 3847, 3891, 3903, 3908, 3923, 3972, 4029, 4048, 4074, 4095, 4183, 4199, 4206, 4213, 4296, 4299, 4359, 4376, 4448, 4490, 4527, 4572, 4575, 4597, 4699, 4709, 4711, 4844, 4876, 4892, 4978, 4985, 5032, 5039, 5055, 5096, 5134, 5168, 64, 81, 144, 332, 396, 504, 652, 680, 771, 866, 987, 1171, 1303, 1441, 1496, 1502, 1544, 1797, 1996, 2031, 2042, 2084, 2121, 2170, 2266, 2293, 2339, 2526, 2528, 2583, 2590, 2662, 2696, 2868, 3016, 3033, 3051, 3292, 3340, 3365, 3563, 3574, 3918, 4022, 4042, 4075, 4079, 4135, 4201, 4303, 4456, 4501, 4553, 4667, 4821, 4879, 4883, 4948, 5103, 5104, 5121, 93, 111, 122, 169, 209, 210, 211, 218, 226, 238, 309, 323, 376, 385, 405, 427, 481, 488, 517, 555, 577, 584, 595, 608, 621, 642, 646, 658, 687, 712, 727, 773, 785, 829, 846, 848, 870, 933, 941, 966, 971, 985, 1024, 1037, 1073, 1105, 1147, 1217, 1233, 1259, 1275, 1323, 1364, 1374, 1409, 1443, 1453, 1479, 1480, 1514, 1559, 1567, 1596, 1649, 1654, 1675, 1691, 1720, 1780, 1804, 1810, 1834, 1868, 1874, 1885, 1905, 1944, 1945, 1948, 2049, 2061, 2063, 2070, 2088, 2093, 2126, 2223, 2239, 2268, 2271, 2327, 2489, 2560, 2590, 2624, 2685, 2700, 2724, 2756, 2766, 2843, 2848, 2857, 2879, 2919, 2933, 2935, 2954, 2964, 2997, 3029, 3043, 3070, 3084, 3099, 3108, 3111, 3116, 3146, 3157, 3237, 3264, 3356, 3391, 3397, 3457, 3472, 3478, 3504, 3541, 3570, 3582, 3660, 3701, 3740, 3746, 3795, 3821, 3827, 3875, 3884, 3912, 3929, 3934, 3970, 4028, 4074, 4091, 4103, 4162, 4170, 4200, 4201, 4206, 4214, 4256, 4260, 4286, 4306, 4382, 4388, 4413, 4429, 4439, 4533, 4541, 4550, 4633, 4661, 4668, 4705, 4713, 4726, 4769, 4784, 4870, 4886, 4928, 4948, 4994, 5027, 5043, 5057, 5097, 5113, 5123, 5124, 5138, 5156, 5163, 5168, 5170, 5172, 137, 142, 270, 363, 427, 460, 467, 590, 642, 681, 725, 744, 769, 808, 927, 998, 1016, 1024, 1041, 1045, 1051, 1098, 1108, 1172, 1233, 1290, 1325, 1342, 1374, 1378, 1441, 1463, 1538, 1546, 1565, 1570, 1645, 1678, 1799, 1810, 1814, 2036, 2129, 2147, 2149, 2426, 2431, 2541, 2572, 2697, 2717, 2736, 2820, 2870, 2890, 3244, 3249, 3339, 3367, 3375, 3396, 3437, 3472, 3481, 3498, 3663, 3708, 3727, 3769, 3811, 3875, 4028, 4076, 4091, 4103, 4122, 4222, 4226, 4312, 4449, 4550, 4624, 4733, 4787, 4811, 4814, 4816, 4857, 4967, 5094, 416, 499, 529, 549, 728, 838, 1064, 1108, 1494, 1575, 1621, 2029, 2264, 2498, 2855, 3015, 3190, 3201, 3276, 3407, 3416, 3458, 3614, 3696, 3751, 4204, 4299, 4482, 4493, 4601, 4827, 5157, 280, 291, 552, 1520, 1818, 1847, 1971, 2127, 2377, 2722, 2768, 2939, 3007, 3863, 4646, 5157, 35, 96, 256, 336, 348, 415, 443, 460, 554, 564, 685, 795, 796, 848, 875, 963, 982, 1013, 1052, 1067, 1100, 1176, 1305, 1469, 1613, 1616, 1764, 1816, 1834, 1890, 2083, 2108, 2206, 2210, 2225, 2349, 2394, 2473, 2864, 2907, 2915, 2993, 3026, 3076, 3087, 3143, 3158, 3284, 3318, 3457, 3503, 3582, 3627, 3688, 3765, 3913, 3928, 4032, 4042, 4087, 4103, 4111, 4113, 4135, 4200, 4201, 4240, 4271, 4425, 4528, 4549, 4561, 4565, 4615, 4752, 4850, 4940, 5094, 5156, 5159, 5169, 289, 814, 1246, 1604, 1668, 2259, 3020, 3122, 3880, 4140, 10, 47, 137, 266, 273, 464, 557, 566, 810, 1040, 1353, 1457, 1860, 1931, 2084, 2418, 2456, 2613, 2649, 2791, 3051, 3301, 3397, 3531, 3652, 3687, 3706, 3822, 3996, 4039, 4052, 4188, 4204, 4256, 4748, 5100, 168, 1570, 2149, 2167, 2555, 3974, 4899, 113, 273, 432, 481, 524, 554, 644, 682, 763, 971, 1040, 1087, 1348, 1409, 1489, 1514, 1532, 1567, 1579, 1609, 1612, 1721, 1851, 2042, 2068, 2085, 2097, 2271, 2583, 2672, 2717, 2738, 3149, 3334, 3619, 3836, 3851, 4207, 4278, 4481, 4506, 4542, 4750, 4976, 5134, 5149, 138, 191, 424, 1245, 1351, 1507, 1629, 1704, 1928, 2090, 2149, 2416, 2563, 2580, 2697, 3059, 3284, 3547, 3577, 3800, 3917, 3968, 4055, 4141, 4144, 4235, 4256, 4348, 4417, 4430, 4506, 4615, 4640, 4682, 4845, 4914, 4942, 4976, 4986, 48, 83, 137, 175, 202, 318, 329, 347, 350, 378, 524, 534, 570, 589, 592, 616, 680, 797, 800, 826, 1040, 1048, 1058, 1073, 1101, 1216, 1289, 1306, 1321, 1405, 1426, 1517, 1518, 1636, 1654, 1834, 1889, 1938, 2020, 2053, 2087, 2088, 2112, 2168, 2352, 2367, 2451, 2469, 2476, 2554, 2610, 2624, 2629, 2738, 2776, 2928, 2949, 2977, 2997, 3029, 3063, 3087, 3099, 3102, 3114, 3135, 3249, 3282, 3306, 3356, 3422, 3427, 3478, 3502, 3559, 3590, 3706, 3708, 3733, 3738, 3822, 3938, 3971, 3979, 4089, 4193, 4226, 4270, 4459, 4498, 4503, 4515, 4546, 4584, 4676, 4723, 4763, 4768, 4839, 4881, 4960, 5001, 0, 10, 48, 89, 99, 107, 119, 121, 137, 151, 174, 224, 271, 291, 317, 343, 379, 392, 458, 499, 523, 539, 554, 589, 593, 617, 621, 627, 643, 769, 803, 830, 851, 875, 891, 1001, 1006, 1081, 1087, 1137, 1138, 1183, 1220, 1245, 1304, 1323, 1325, 1331, 1340, 1358, 1381, 1402, 1457, 1496, 1567, 1615, 1626, 1634, 1648, 1674, 1712, 1729, 1769, 1774, 1801, 1843, 1898, 1906, 1948, 2020, 2031, 2040, 2070, 2084, 2133, 2153, 2193, 2194, 2239, 2264, 2296, 2326, 2345, 2354, 2391, 2465, 2476, 2591, 2597, 2617, 2623, 2627, 2649, 2759, 2760, 2818, 2841, 2842, 2877, 2884, 2903, 2917, 2919, 2933, 2997, 3029, 3043, 3074, 3080, 3085, 3124, 3125, 3179, 3187, 3198, 3230, 3240, 3248, 3265, 3320, 3322, 3339, 3428, 3478, 3479, 3529, 3617, 3663, 3682, 3708, 3767, 3769, 3821, 3870, 3884, 3893, 3915, 3950, 3955, 3968, 4025, 4067, 4074, 4079, 4094, 4097, 4103, 4250, 4260, 4346, 4404, 4409, 4479, 4482, 4500, 4612, 4664, 4682, 4696, 4709, 4714, 4816, 4931, 4944, 5001, 5014, 5055, 5087, 5165, 26, 74, 112, 163, 251, 314, 422, 523, 538, 642, 678, 828, 830, 906, 926, 941, 999, 1030, 1037, 1048, 1131, 1220, 1253, 1273, 1394, 1494, 1499, 1512, 1557, 1570, 1575, 1596, 1602, 1633, 1771, 1854, 1904, 1913, 1928, 1951, 1995, 2100, 2150, 2248, 2254, 2280, 2435, 2494, 2501, 2597, 2598, 2742, 2776, 2810, 2824, 2842, 2843, 2849, 2907, 2929, 2934, 3040, 3043, 3306, 3369, 3386, 3390, 3410, 3534, 3751, 3755, 3858, 3862, 3872, 3929, 4000, 4118, 4154, 4206, 4257, 4283, 4286, 4350, 4480, 4535, 4574, 4582, 4961, 4966, 4979, 5009, 5089, 5106, 10, 142, 395, 452, 546, 610, 658, 695, 800, 1095, 1119, 1143, 1187, 1298, 1381, 1535, 1615, 1646, 1727, 1776, 1803, 1922, 2038, 2040, 2082, 2121, 2145, 2198, 2226, 2430, 2524, 2587, 2786, 2827, 2856, 2864, 3043, 3400, 3445, 3473, 3513, 3553, 3560, 3577, 3667, 3724, 3878, 3914, 4105, 4111, 4408, 4418, 4430, 4439, 4459, 4542, 4748, 4750, 4779, 4845, 4968, 4999, 5007, 5025, 5055, 5146, 10, 33, 123, 131, 134, 169, 225, 235, 309, 386, 563, 630, 635, 681, 720, 797, 800, 947, 1025, 1060, 1306, 1404, 1539, 1559, 1607, 1622, 1635, 1758, 1780, 1845, 2096, 2175, 2225, 2227, 2239, 2267, 2471, 2481, 2493, 2555, 2638, 2720, 2745, 2772, 2877, 2916, 2939, 2993, 3008, 3011, 3190, 3260, 3345, 3422, 3534, 3593, 3696, 3920, 4012, 4029, 4057, 4065, 4234, 4318, 4334, 4385, 4396, 4434, 4515, 4535, 4554, 4567, 4612, 4625, 4715, 4726, 4769, 4786, 4801, 4849, 4909, 5014, 5039, 5079, 37, 85, 224, 225, 229, 238, 280, 285, 305, 395, 458, 689, 703, 752, 763, 768, 777, 801, 822, 969, 971, 1060, 1073, 1149, 1186, 1189, 1244, 1260, 1456, 1463, 1565, 1640, 1681, 1855, 1867, 1911, 1946, 1997, 2051, 2056, 2173, 2225, 2259, 2386, 2389, 2582, 2606, 2633, 2698, 2717, 2764, 2794, 2806, 2814, 2846, 2851, 2917, 2935, 3011, 3028, 3093, 3116, 3244, 3323, 3347, 3356, 3358, 3423, 3512, 3514, 3596, 3681, 3690, 3702, 3790, 3875, 3886, 3957, 4006, 4213, 4306, 4406, 4459, 4471, 4481, 4545, 4623, 4659, 4669, 4705, 4761, 4797, 4798, 4824, 4843, 4857, 4874, 4910, 4966, 4984, 5007, 5039, 79, 195, 221, 283, 289, 446, 499, 509, 590, 616, 747, 758, 832, 846, 1067, 1115, 1174, 1176, 1218, 1236, 1241, 1253, 1321, 1373, 1427, 1514, 1537, 1590, 1612, 1816, 1833, 1834, 1874, 1954, 2111, 2300, 2331, 2349, 2524, 2616, 2617, 2717, 2765, 2970, 3118, 3177, 3286, 3292, 3306, 3318, 3350, 3436, 3473, 3594, 3663, 3825, 3847, 3954, 3988, 4096, 4163, 4311, 4367, 4565, 4676, 4831, 4879, 4971, 4985, 5002, 5040, 5126, 373, 490, 534, 546, 705, 747, 751, 776, 830, 990, 1054, 1155, 1196, 1204, 1244, 1350, 1429, 1497, 1692, 1796, 1847, 1938, 1967, 2106, 2265, 2344, 2418, 2495, 2672, 2718, 2759, 2827, 2872, 2916, 3041, 3136, 3265, 3522, 3684, 3912, 4006, 4025, 4053, 4260, 4384, 4525, 4527, 4554, 4895, 4905, 4988, 5144, 5163, 104, 160, 166, 209, 229, 297, 318, 375, 378, 404, 460, 557, 629, 646, 672, 681, 813, 1016, 1025, 1029, 1032, 1052, 1105, 1124, 1128, 1171, 1195, 1205, 1218, 1220, 1350, 1466, 1499, 1522, 1525, 1538, 1604, 1664, 1668, 1678, 1704, 1771, 1786, 1793, 1928, 1944, 2042, 2080, 2206, 2210, 2223, 2311, 2320, 2371, 2394, 2490, 2493, 2561, 2564, 2704, 2780, 2828, 2888, 2897, 2954, 3000, 3016, 3079, 3227, 3273, 3277, 3396, 3397, 3429, 3461, 3493, 3512, 3513, 3520, 3555, 3582, 3666, 3672, 3682, 3697, 3698, 3746, 3793, 3807, 3808, 3816, 3825, 3851, 3908, 3957, 4065, 4095, 4134, 4284, 4294, 4349, 4412, 4529, 4541, 4571, 4605, 4633, 4640, 4657, 4660, 4676, 4709, 4742, 4767, 4793, 4867, 4883, 4988, 5013, 5018, 5024, 5034, 5045, 5103, 5124, 191, 233, 248, 592, 616, 645, 744, 758, 829, 916, 934, 979, 1383, 1404, 1427, 1514, 1588, 1615, 1683, 1867, 1885, 2057, 2061, 2323, 2327, 2371, 2597, 2609, 2674, 2809, 2891, 2892, 3080, 3120, 3235, 3294, 3326, 3363, 3513, 3582, 3604, 3699, 3724, 3971, 4012, 4148, 4188, 4240, 4300, 4345, 4361, 4593, 4601, 4633, 4657, 4690, 4697, 4814, 5043, 19, 92, 144, 170, 177, 224, 226, 232, 248, 360, 365, 385, 395, 536, 555, 556, 600, 618, 642, 696, 725, 727, 783, 808, 829, 846, 902, 926, 948, 966, 974, 1030, 1047, 1058, 1121, 1150, 1183, 1207, 1218, 1220, 1236, 1253, 1321, 1337, 1351, 1352, 1427, 1546, 1567, 1569, 1574, 1688, 1721, 1722, 1793, 1814, 1870, 1919, 1939, 2064, 2082, 2090, 2130, 2154, 2185, 2224, 2321, 2325, 2340, 2355, 2391, 2394, 2408, 2444, 2471, 2514, 2523, 2545, 2555, 2563, 2577, 2609, 2613, 2617, 2653, 2698, 2714, 2721, 2758, 2763, 2820, 2843, 2916, 2922, 2963, 2977, 3034, 3054, 3063, 3066, 3085, 3099, 3100, 3118, 3137, 3190, 3210, 3234, 3282, 3323, 3326, 3348, 3369, 3372, 3389, 3435, 3437, 3439, 3450, 3454, 3458, 3484, 3494, 3520, 3598, 3605, 3613, 3641, 3652, 3696, 3768, 3808, 3813, 3815, 3821, 3861, 3880, 3912, 3918, 4019, 4040, 4087, 4092, 4095, 4171, 4208, 4317, 4350, 4361, 4394, 4406, 4408, 4502, 4511, 4544, 4549, 4569, 4584, 4669, 4672, 4697, 4702, 4731, 4738, 4816, 4827, 4851, 4873, 4946, 4985, 5007, 5013, 5022, 5065, 5170, 175, 323, 524, 891, 941, 1818, 2537, 2569, 2841, 2890, 3532, 3635, 4048, 4117, 4122, 4187, 4359, 4961, 5059, 5099, 7, 37, 75, 95, 107, 108, 112, 160, 283, 318, 369, 376, 392, 412, 423, 457, 458, 479, 526, 549, 557, 598, 604, 635, 680, 701, 728, 747, 756, 875, 883, 885, 890, 910, 944, 963, 971, 985, 1041, 1070, 1083, 1098, 1131, 1233, 1260, 1273, 1340, 1353, 1433, 1448, 1463, 1473, 1490, 1531, 1545, 1546, 1551, 1610, 1623, 1645, 1665, 1711, 1722, 1729, 1735, 1777, 1811, 1819, 1834, 1847, 1854, 1873, 1912, 1922, 1945, 1947, 2003, 2044, 2049, 2072, 2108, 2173, 2184, 2225, 2335, 2350, 2408, 2465, 2471, 2552, 2577, 2616, 2682, 2700, 2727, 2832, 2855, 2857, 2861, 2885, 2898, 2905, 2922, 3072, 3150, 3173, 3177, 3198, 3207, 3273, 3286, 3292, 3305, 3306, 3356, 3386, 3400, 3523, 3527, 3528, 3594, 3681, 3732, 3814, 3843, 3880, 3886, 3974, 4011, 4047, 4049, 4058, 4074, 4081, 4095, 4189, 4207, 4226, 4228, 4238, 4251, 4254, 4257, 4300, 4317, 4323, 4327, 4418, 4440, 4449, 4485, 4493, 4508, 4524, 4545, 4574, 4597, 4628, 4647, 4650, 4660, 4688, 4691, 4700, 4707, 4715, 4738, 4740, 4754, 4767, 4768, 4787, 4865, 4876, 4879, 4893, 4955, 5013, 5023, 5075, 5087, 5099, 5121, 5126, 5144, 32, 35, 37, 162, 271, 290, 320, 428, 592, 671, 710, 796, 870, 923, 971, 974, 988, 998, 1013, 1060, 1066, 1111, 1135, 1241, 1244, 1271, 1323, 1337, 1367, 1401, 1406, 1455, 1530, 1565, 1625, 1660, 1664, 1683, 1704, 1723, 1847, 1855, 1872, 1907, 1932, 1991, 2024, 2031, 2036, 2288, 2298, 2346, 2419, 2526, 2565, 2606, 2609, 2617, 2671, 2674, 2694, 2833, 2846, 2851, 2864, 2919, 2954, 2985, 3040, 3041, 3050, 3116, 3315, 3323, 3490, 3557, 3566, 3579, 3606, 3667, 3690, 3699, 3702, 3751, 3781, 3793, 3795, 3868, 3895, 4094, 4250, 4323, 4336, 4382, 4384, 4412, 4549, 4586, 4629, 4653, 4764, 4771, 4789, 4831, 4864, 4870, 4874, 4938, 4989, 5045, 5079, 60, 95, 145, 209, 224, 257, 258, 511, 538, 550, 553, 585, 600, 752, 971, 1044, 1176, 1202, 1313, 1407, 1443, 1466, 1477, 1514, 1646, 1664, 1729, 1954, 2476, 2569, 2660, 2734, 2854, 3526, 3534, 3962, 4058, 4126, 4134, 4213, 4257, 4350, 4356, 4431, 4789, 4805, 4817, 4843, 4970, 4971, 5057, 2083, 2259, 2423, 2829, 3063, 4098, 4533, 138, 177, 266, 288, 313, 345, 396, 500, 645, 651, 677, 723, 747, 773, 796, 814, 827, 844, 848, 919, 969, 974, 982, 1029, 1091, 1096, 1122, 1149, 1206, 1325, 1381, 1394, 1426, 1455, 1529, 1532, 1712, 1797, 1810, 1847, 1892, 1997, 2004, 2085, 2234, 2267, 2337, 2351, 2382, 2384, 2425, 2494, 2542, 2555, 2617, 2659, 2662, 2686, 2745, 2749, 2893, 2905, 3060, 3146, 3363, 3522, 3527, 3581, 3609, 3656, 3690, 3701, 3775, 3777, 3903, 4017, 4030, 4052, 4060, 4117, 4291, 4311, 4331, 4373, 4384, 4459, 4488, 4531, 4742, 4759, 4817, 4894, 4900, 4912, 5025, 5050, 5080, 5144, 5161, 106, 217, 244, 379, 517, 536, 550, 595, 646, 715, 743, 833, 1189, 1278, 1546, 1570, 1575, 1640, 1642, 1820, 1863, 1868, 1995, 2051, 2054, 2074, 2172, 2188, 2194, 2213, 2316, 2391, 2395, 2470, 2609, 2700, 2824, 2846, 2849, 2919, 3071, 3112, 3116, 3158, 3225, 3272, 3345, 3362, 3364, 3372, 3392, 3406, 3439, 3472, 3682, 3748, 3795, 3845, 3893, 3932, 3953, 4122, 4233, 4303, 4384, 4466, 4557, 4586, 4603, 4699, 4738, 4752, 4798, 4828, 4838, 4936, 5040, 5099, 5110, 5115, 5164, 5170, 81, 235, 1273, 1539, 2768, 3364, 4576, 28, 1336, 2905, 3154, 3725, 4535, 20, 79, 151, 171, 226, 248, 266, 480, 525, 612, 690, 701, 810, 827, 848, 851, 990, 1025, 1028, 1035, 1056, 1064, 1066, 1135, 1146, 1219, 1233, 1290, 1302, 1329, 1331, 1451, 1497, 1569, 1588, 1637, 1641, 1732, 1759, 1814, 1831, 1835, 1836, 1985, 2025, 2027, 2096, 2293, 2325, 2347, 2373, 2726, 2819, 2913, 2981, 3020, 3126, 3280, 3307, 3438, 3478, 3610, 3659, 3696, 3740, 3814, 3832, 3861, 3962, 3971, 3976, 4006, 4034, 4082, 4251, 4300, 4406, 4413, 4488, 4498, 4545, 4637, 4640, 4708, 4729, 4805, 4893, 4920, 4925, 4936, 4968, 5062, 137, 240, 389, 416, 424, 443, 549, 617, 875, 1081, 1137, 1325, 1326, 1331, 1519, 1644, 1680, 1818, 1906, 2211, 2234, 2306, 2374, 2431, 2469, 2524, 2569, 2627, 2698, 2818, 2842, 2870, 2924, 2988, 2992, 3015, 3052, 3074, 3149, 3276, 3585, 3614, 3682, 3719, 3746, 4055, 4200, 4204, 4222, 4305, 4493, 4507, 4597, 4615, 4729, 4764, 4797, 5157, 5169, 93, 120, 446, 1210, 1367, 1467, 1490, 1598, 1649, 1704, 1732, 1826, 2737, 3073, 3116, 3255, 3549, 3714, 3822, 4144, 4164, 4337, 4449, 4690</t>
   </si>
   <si>
     <t>98.86</t>
@@ -821,6 +821,21 @@
   </si>
   <si>
     <t>0, 2, 3, 7, 11, 12, 13, 17, 22, 26, 30, 34, 38, 39, 48, 58, 60, 65, 66, 68, 74, 78, 85, 87, 91, 93, 94, 98, 99, 100, 105, 108, 111, 112, 119, 130, 132, 135, 136, 145, 151, 157, 158, 161, 167, 168, 169, 170, 182, 186, 189, 194, 195, 196, 198, 199, 204, 206, 207, 208, 216, 217, 218, 220, 223, 225, 229, 233, 238, 239, 240, 245, 250, 255, 257, 259, 260, 266, 267, 269, 271, 275, 277, 282, 283, 288, 292, 293, 294, 298, 301, 310, 314, 315, 316, 317, 320, 329, 333, 338, 341, 346, 347, 352, 355, 358, 360, 365, 366, 367, 368, 372, 381, 382, 387, 389, 401, 407, 414, 415, 422, 423, 430, 434, 435, 436, 437, 440, 443, 445, 447, 449, 454, 456, 461, 463, 467, 469, 471, 475, 477, 479, 487, 488, 491, 493, 494, 496, 497, 500, 501, 518, 521, 528, 538, 547, 549, 550, 551, 556, 557, 563, 566, 574, 575, 576, 577, 578, 579, 582, 583, 591, 592, 604, 609, 610, 611, 612, 614, 616, 618, 620, 621, 622, 623, 626, 627, 628, 633, 638, 639, 644, 647, 651, 655, 657, 658, 662, 666, 668, 672, 680, 684, 685, 688, 694, 697, 702, 703, 707, 709, 711, 713, 716, 717, 720, 721, 732, 738, 739, 741, 742, 755, 758, 759, 766, 767, 769, 771, 772, 778, 780, 784, 787, 788, 790, 793, 797, 804, 805, 806, 809, 812, 827, 829, 833, 836, 837, 838, 840, 843, 844, 849, 856, 858, 859, 861, 862, 865, 869, 872, 874, 878, 883, 888, 889, 891, 892, 895, 902, 904, 907, 912, 914, 919, 922, 923, 924, 926, 930, 936, 937, 941, 955, 958, 962, 965, 968, 969, 971, 973, 977, 980, 994, 996, 997, 1000, 1011, 1013, 1016, 1017, 1018, 1022, 1026, 1027, 1030, 1031, 1032, 1033, 1036, 1039, 1041, 1045, 1049, 1050, 1053, 1058, 1060, 1063, 1069, 1073, 1075, 1080, 1082, 1091, 1093, 1095, 1096, 1099, 1100, 1104, 1105, 1112, 1119, 1122, 1125, 1126, 1131, 1144, 1145, 1150, 1151, 1152, 1153, 1158, 1162, 1163, 1165, 1166, 1169, 1170, 1180, 1182, 1185, 1191, 1192, 1194, 1198, 1199, 1200, 1201, 1204, 1207, 1208, 1211, 1213, 1217, 1219, 1220, 1222, 1227, 1229, 1232, 1235, 1237, 1238, 1243, 1245, 1247, 1250, 1256, 1257, 1262, 1266, 1276, 1278, 1281, 1282, 1283, 1284, 1287, 1290, 1292, 1294, 1297, 1307, 1312, 1318, 1320, 1322, 1324, 1325, 1326, 1327, 1328, 1330, 1331, 1334, 1335, 1336, 1337, 1341, 1344, 1346, 1348, 1351, 1353, 1354, 1355, 1357, 1358, 1359, 1362, 1365, 1367, 1370, 1376, 1377, 1379, 1383, 1386, 1390, 1392, 1394, 1396, 1398, 1399, 1400, 1401, 1410, 1411, 1416, 1418, 1423, 1428, 1429, 1437, 1440, 1442, 1444, 1446, 1451, 1454, 1455, 1456, 1461, 1465, 1466, 1468, 1470, 1474, 1475, 1481, 1490, 1493, 1494, 1495, 1498, 1499, 1500, 1505, 1509, 1513, 1517, 1523, 1527, 1528, 1529, 1530, 1533, 1535, 1536, 1539, 1543, 1548, 1549, 1550, 1551, 1560, 1562, 1565, 1568, 1569, 1571, 1573, 1580, 1581, 1583, 1587, 1590, 1592, 1601, 1605, 1609, 1622, 1623, 1624, 1627, 1628, 1629, 1630, 1632, 1633, 1634, 1637, 1639, 1640, 1643, 1649, 1651, 1654, 1655, 1656, 1661, 1662, 1666, 1667, 1669, 1670, 1679, 1688, 1698, 1702, 1706, 1708, 1711, 1712, 1714, 1721, 1722, 1725, 1729, 1731, 1734, 1738, 1739, 1743, 1744, 1745, 1746, 1747, 1748, 1750, 1751, 1752, 1760, 1764, 1765, 1774, 1775, 1783, 1788, 1790, 1792, 1794, 1795, 1797, 1798, 1799, 1800, 1801, 1807, 1808, 1810, 1811, 1821, 1822, 1825, 1829, 1830, 1831, 1834, 1835, 1838, 1840, 1843, 1845, 1853, 1855, 1859, 1861, 1863, 1867, 1868, 1869, 1870, 1872, 1874, 1875, 1876, 1882, 1885, 1886, 1888, 1890, 1892, 1895, 1896, 1897, 1901, 1902, 1903, 1904, 1909, 1910, 1911, 1915, 1918, 1919, 1921, 1922, 1930, 1931, 1934, 1937, 1938, 1941, 1949, 1950, 1952, 1953, 1955, 1957, 1961, 1965, 1969, 1970, 1972, 1973, 1977, 1979, 1982, 1988, 1990, 1993, 1996, 2002, 2004, 2006, 2010, 2013, 2015, 2016, 2019, 2021, 2025, 2026, 2029, 2032, 2034, 2045, 2046, 2050, 2055, 2056, 2059, 2061, 2062, 2066, 2068, 2070, 2073, 2074, 2076, 2079, 2080, 2086, 2087, 2089, 2097, 2098, 2099, 2110, 2111, 2114, 2116, 2118, 2121, 2122, 2125, 2133, 2134, 2136, 2141, 2154, 2157, 2158, 2161, 2163, 2164, 2176, 2178, 2180, 2186, 2190, 2191, 2196, 2199, 2201, 2203, 2207, 2208, 2212, 2219, 2221, 2229, 2231, 2232, 2239, 2240, 2241, 2242, 2243, 2252, 2258, 2265, 2271, 2275, 2276, 2279, 2284, 2286, 2288, 2291, 2292, 2294, 2296, 2310, 2313, 2314, 2317, 2327, 2328, 2330, 2331, 2334, 2336, 2337, 2341, 2343, 2347, 2350, 2354, 2355, 2356, 2358, 2359, 2362, 2365, 2366, 2370, 2372, 2374, 2380, 2388, 2393, 2397, 2405, 2409, 2412, 2414, 2419, 2424, 2425, 2429, 2431, 2434, 2437, 2442, 2444, 2445, 2446, 2447, 2450, 2458, 2459, 2465, 2466, 2468, 2473, 2475, 2476, 2477, 2478, 2481, 2482, 2483, 2484, 2490, 2493, 2496, 2497, 2500, 2501, 2507, 2509, 2515, 2518, 2521, 2527, 2543, 2546, 2550, 2551, 2555, 2559, 2568, 2572, 2576, 2579, 2587, 2589, 2592, 2595, 2597, 2600, 2601, 2604, 2606, 2607, 2609, 2612, 2613, 2615, 2618, 2622, 2630, 2632, 2638, 2639, 2643, 2648, 2649, 2650, 2655, 2656, 2657, 2662, 2665, 2666, 2669, 2670, 2674, 2675, 2677, 2679, 2685, 2691, 2695, 2696, 2697, 2700, 2701, 2702, 2703, 2704, 2706, 2707, 2714, 2715, 2727, 2728, 2731, 2738, 2740, 2741, 2743, 2747, 2748, 2752, 2757, 2766, 2768, 2769, 2775, 2785, 2787, 2788, 2789, 2792, 2796, 2798, 2799, 2802, 2807, 2808, 2811, 2813, 2818, 2819, 2823, 2826, 2827, 2828, 2829, 2831, 2835, 2838, 2845, 2855, 2861, 2863, 2864, 2868, 2869, 2872, 2873, 2886, 2887, 2895, 2896, 2897, 2898, 2903, 2908, 2910, 2911, 2914, 2916, 2918, 2919, 2920, 2925, 2928, 2929, 2931, 2932, 2941, 2945, 2946, 2952, 2956, 2959, 2960, 2962, 2964, 2966, 2967, 2970, 2975, 2976, 2980, 2988, 2990, 2993, 2997, 3003, 3004, 3005, 3006, 3008, 3009, 3010, 3013, 3018, 3028, 3033, 3034, 3035, 3038, 3040, 3047, 3049, 3051, 3058, 3064, 3069, 3072, 3078, 3079, 3080, 3087, 3090, 3094, 3104, 3105, 3110, 3114, 3115, 3120, 3124, 3130, 3131, 3134, 3135, 3136, 3140, 3143, 3145, 3149, 3152, 3153, 3162, 3166, 3169, 3171, 3174, 3178, 3179, 3181, 3183, 3185, 3187, 3188, 3198, 3200, 3206, 3207, 3209, 3212, 3215, 3218, 3222, 3230, 3232, 3235, 3241, 3243, 3245, 3246, 3247, 3250, 3251, 3256, 3258, 3259, 3261, 3262, 3263, 3270, 3275, 3277, 3279, 3281, 3297, 3300, 3303, 3304, 3305, 3310, 3312, 3314, 3315, 3322, 3327, 3329, 3330, 3339, 3344, 3345, 3346, 3347, 3361, 3365, 3371, 3373, 3377, 3378, 3379, 3382, 3383, 3394, 3395, 3397, 3399, 3408, 3412, 3413, 3419, 3420, 3421, 3425, 3431, 3433, 3435, 3436, 3437, 3440, 3441, 3443, 3444, 3445, 3447, 3452, 3458, 3459, 3460, 3465, 3466, 3467, 3470, 3480, 3482, 3484, 3489, 3491, 3493, 3499, 3500, 3502, 3506, 3509, 3510, 3512, 3514, 3516, 3517, 3521, 3525, 3533, 3536, 3538, 3539, 3547, 3548, 3557, 3565, 3567, 3571, 3587, 3590, 3593, 3594, 3604, 3605, 3608, 3609, 3611, 3612, 3613, 3615, 3618, 3619, 3620, 3628, 3630, 3631, 3633, 3635, 3639, 3643, 3646, 3649, 3650, 3657, 3661, 3662, 3664, 3665, 3671, 3672, 3673, 3674, 3675, 3676, 3678, 3683, 3685, 3687, 3689, 3692, 3697, 3701, 3705, 3706, 3709, 3710, 3711, 3718, 3723, 3725, 3726, 3729, 3730, 3737, 3740, 3741, 3755, 3760, 3766, 3768, 3770, 3771, 3774, 3775, 3778, 3781, 3782, 3791, 3800, 3801, 3803, 3804, 3806, 3813, 3822, 3825, 3832, 3833, 3839, 3846, 3852, 3854, 3861, 3864, 3866, 3872, 3876, 3879, 3880, 3881, 3883, 3886, 3887, 3888, 3895, 3897, 3898, 3900, 3902, 3907, 3911, 3913, 3914, 3920, 3921, 3922, 3925, 3928, 3930, 3932, 3936, 3937, 3940, 3941, 3943, 3944, 3947, 3956, 3957, 3963, 3969, 3970, 3971, 3974, 3982, 3983, 3987, 3989, 3991, 3992, 3994, 3995, 3998, 3999, 4000, 4007, 4008, 4009, 4010, 4012, 4014, 4016, 4018, 4020, 4021, 4024, 4025, 4027, 4031, 4032, 4037, 4052, 4055, 4057, 4062, 4077, 4080, 4086, 4089, 4095, 4098, 4099, 4100, 4101, 4105, 4106, 4107, 4108, 4114, 4117, 4120, 4125, 4127, 4128, 4130, 4134, 4135, 4138, 4139, 4146, 4151, 4158, 4160, 4161, 4162, 4168, 4170, 4173, 4174, 4177, 4186, 4191, 4205, 4206, 4208, 4212, 4215, 4216, 4221, 4226, 4227, 4230, 4232, 4233, 4235, 4237, 4240, 4241, 4242, 4245, 4247, 4251, 4257, 4260, 4261, 4264, 4266, 4267, 4269, 4271, 4283, 4284, 4285, 4287, 4288, 4289, 4292, 4295, 4296, 4297, 4298, 4304, 4307, 4308, 4312, 4313, 4316, 4319, 4321, 4323, 4332, 4337, 4339, 4340, 4342, 4344, 4349, 4350, 4353, 4354, 4356, 4361, 4362, 4363, 4371, 4372, 4375, 4378, 4383, 4387, 4389, 4391, 4397, 4402, 4403, 4406, 4407, 4408, 4412, 4414, 4422, 4423, 4425, 4426, 4427, 4432, 4436, 4437, 4439, 4441, 4443, 4445, 4446, 4456, 4460, 4462, 4465, 4466, 4468, 4469, 4470, 4473, 4479, 4480, 4483, 4485, 4486, 4487, 4491, 4493, 4495, 4499, 4502, 4504, 4512, 4513, 4514, 4519, 4524, 4527, 4528, 4532, 4533, 4534, 4537, 4545, 4548, 4552, 4556, 4559, 4560, 4565, 4569, 4577, 4578, 4582, 4596, 4597, 4599, 4600, 4601, 4602, 4604, 4606, 4618, 4622, 4628, 4633, 4634, 4635, 4639, 4640, 4641, 4642, 4652, 4653, 4655, 4656, 4662, 4667, 4669, 4675, 4679, 4680, 4683, 4685, 4690, 4691, 4693, 4703, 4704, 4711, 4721, 4725, 4727, 4729, 4739, 4742, 4743, 4746, 4749, 4751, 4754, 4755, 4758, 4760, 4775, 4777, 4778, 4785, 4786, 4790, 4791, 4794, 4796, 4801, 4810, 4813, 4815, 4822, 4827, 4831, 4837, 4845, 4854, 4855, 4859, 4866, 4868, 4875, 4877, 4878, 4886, 4889, 4890, 4894, 4896, 4897, 4898, 4906, 4907, 4910, 4919, 4920, 4921, 4924, 4926, 4927, 4934, 4937, 4940, 4947, 4948, 4949, 4951, 4956, 4957, 4960, 4961, 4962, 4967, 4972, 4973, 4981, 4989, 4993, 4994, 4998, 5001, 5002, 5004, 5011, 5014, 5016, 5018, 5021, 5023, 5026, 5028, 5030, 5033, 5036, 5037, 5038, 5041, 5044, 5050, 5052, 5053, 5054, 5056, 5057, 5058, 5059, 5061, 5065, 5067, 5075, 5078, 5079, 5080, 5084, 5094, 5098, 5099, 5101, 5104, 5105, 5106, 5108, 5116, 5117, 5118, 5122, 5125, 5129, 5130, 5139, 5142, 5146, 5147, 5148, 5152, 5154, 5156, 5163</t>
+  </si>
+  <si>
+    <t>ASK G6 IF (G5 &lt;&gt; “(98) None of these”)</t>
+  </si>
+  <si>
+    <t>G6.1, G6.2, G6.3, G6.4, G6.5, G6.6, G6.7, G6.8, G6.10, G6.11, G5_12</t>
+  </si>
+  <si>
+    <t>6.459999999999994</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>19, 21, 39, 47, 66, 75, 76, 96, 97, 117, 123, 135, 138, 152, 187, 194, 198, 216, 227, 248, 255, 281, 288, 297, 312, 338, 356, 413, 417, 421, 424, 434, 464, 478, 479, 486, 502, 528, 546, 561, 573, 593, 599, 639, 652, 655, 668, 671, 705, 709, 712, 714, 717, 729, 757, 774, 781, 789, 806, 807, 811, 816, 829, 864, 892, 903, 946, 948, 966, 1002, 1029, 1035, 1047, 1055, 1060, 1062, 1124, 1131, 1141, 1157, 1173, 1182, 1194, 1199, 1204, 1209, 1216, 1227, 1245, 1263, 1268, 1270, 1287, 1291, 1292, 1311, 1322, 1332, 1341, 1345, 1351, 1355, 1378, 1392, 1399, 1401, 1411, 1421, 1448, 1449, 1452, 1524, 1545, 1559, 1588, 1591, 1626, 1650, 1656, 1673, 1679, 1720, 1788, 1796, 1820, 1827, 1830, 1876, 1882, 1936, 1966, 1967, 1995, 1998, 2012, 2065, 2089, 2115, 2125, 2140, 2141, 2159, 2161, 2165, 2171, 2195, 2229, 2244, 2253, 2256, 2301, 2303, 2308, 2359, 2367, 2378, 2386, 2390, 2392, 2408, 2415, 2416, 2417, 2418, 2422, 2425, 2437, 2440, 2441, 2443, 2447, 2456, 2465, 2481, 2484, 2506, 2520, 2575, 2586, 2627, 2630, 2636, 2659, 2661, 2673, 2681, 2682, 2764, 2795, 2814, 2827, 2883, 2914, 2930, 2934, 2955, 2957, 2965, 3026, 3030, 3045, 3063, 3069, 3091, 3131, 3152, 3153, 3155, 3160, 3170, 3198, 3203, 3206, 3213, 3216, 3225, 3261, 3265, 3285, 3346, 3378, 3383, 3387, 3407, 3411, 3422, 3427, 3429, 3435, 3466, 3470, 3500, 3503, 3505, 3506, 3512, 3515, 3517, 3540, 3556, 3565, 3605, 3619, 3624, 3626, 3656, 3717, 3723, 3731, 3744, 3773, 3794, 3803, 3819, 3826, 3854, 3867, 3870, 3890, 3891, 3947, 3951, 3952, 3954, 3957, 3974, 3994, 4036, 4043, 4061, 4078, 4089, 4103, 4123, 4131, 4155, 4160, 4184, 4189, 4192, 4197, 4218, 4236, 4254, 4255, 4270, 4276, 4310, 4331, 4334, 4337, 4370, 4383, 4392, 4399, 4400, 4413, 4433, 4458, 4470, 4513, 4528, 4571, 4583, 4674, 4680, 4691, 4697, 4708, 4754, 4762, 4777, 4798, 4802, 4806, 4852, 4853, 4885, 4900, 4918, 4935, 4952, 4954, 4963, 4990, 4998, 5013, 5015, 5034, 5078, 5082, 5139, 5143, 5161</t>
   </si>
   <si>
     <t>SK1, SK7</t>
@@ -1243,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="30.7109375" customWidth="1"/>
@@ -2796,47 +2811,47 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="30" customHeight="1">
+    <row r="74" spans="2:8" ht="45" customHeight="1">
       <c r="B74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>24</v>
+        <v>269</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="20" customHeight="1">
+    <row r="75" spans="2:8" ht="30" customHeight="1">
       <c r="B75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>16</v>
@@ -2847,32 +2862,55 @@
         <v>10</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="20" customHeight="1">
+      <c r="B77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8">
-      <c r="F78" s="5" t="s">
+      <c r="D77" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>275</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="2:8">
       <c r="F79" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="F80" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
